--- a/outputs/vc-pr26-project-task-doc-map-blueprints-github-links.xlsx
+++ b/outputs/vc-pr26-project-task-doc-map-blueprints-github-links.xlsx
@@ -11,11 +11,11 @@
     <sheet name="Link Config" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Task Map'!$A$1:$K$306</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Task Map'!$A$1:$K$318</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Skill Map'!$A$1:$H$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Document Catalog'!$A$1:$E$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Task Skill Links'!$A$1:$D$219</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Task Document Links'!$A$1:$F$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Task Skill Links'!$A$1:$D$231</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Task Document Links'!$A$1:$F$198</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Link Config'!$A$1:$C$2</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -254,8 +254,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TaskMap" displayName="TaskMap" ref="A2:K306" headerRowCount="1">
-  <autoFilter ref="A2:K306"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TaskMap" displayName="TaskMap" ref="A2:K318" headerRowCount="1">
+  <autoFilter ref="A2:K318"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Owner"/>
     <tableColumn id="2" name="Project Type"/>
@@ -305,8 +305,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TaskSkillLinks" displayName="TaskSkillLinks" ref="A2:D219" headerRowCount="1">
-  <autoFilter ref="A2:D219"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TaskSkillLinks" displayName="TaskSkillLinks" ref="A2:D231" headerRowCount="1">
+  <autoFilter ref="A2:D231"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Project Type"/>
     <tableColumn id="2" name="Stage / Pseudo-stage"/>
@@ -318,8 +318,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TaskDocumentLinks" displayName="TaskDocumentLinks" ref="A2:F187" headerRowCount="1">
-  <autoFilter ref="A2:F187"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TaskDocumentLinks" displayName="TaskDocumentLinks" ref="A2:F198" headerRowCount="1">
+  <autoFilter ref="A2:F198"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Project Type"/>
     <tableColumn id="2" name="Stage / Pseudo-stage"/>
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K306"/>
+  <dimension ref="A1:K318"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="18" customWidth="1" style="12" min="1" max="2"/>
@@ -14203,11 +14203,7 @@
       </c>
     </row>
     <row r="259" ht="18" customHeight="1" s="12">
-      <c r="A259" s="15" t="inlineStr">
-        <is>
-          <t>Jay</t>
-        </is>
-      </c>
+      <c r="A259" s="15" t="inlineStr"/>
       <c r="B259" s="15" t="inlineStr">
         <is>
           <t>Origination Pipeline</t>
@@ -14215,16 +14211,16 @@
       </c>
       <c r="C259" s="15" t="inlineStr">
         <is>
-          <t>Review Backlog</t>
+          <t>Connecting On Linkedin</t>
         </is>
       </c>
       <c r="D259" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/promote-candidate-to-deal-room.md","Promote Candidate to Deal Pipeline")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/record-linkedin-connection-attempt.md","Record LinkedIn Connection Attempt")</f>
         <v/>
       </c>
       <c r="E259" s="15" t="inlineStr">
         <is>
-          <t>Prepare a reviewed promotion package for creating or updating a Deal Pipeline from an approved origination candidate.</t>
+          <t>Capture a human-approved LinkedIn connection attempt and update the outbound state without sending messages automatically.</t>
         </is>
       </c>
       <c r="F259" s="16">
@@ -14232,11 +14228,11 @@
         <v/>
       </c>
       <c r="G259" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-origination-deal-room-promotion/SKILL.md","vc-origination-deal-room-promotion")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-outreach-draft-queue/SKILL.md","vc-outreach-draft-queue")</f>
         <v/>
       </c>
       <c r="H259" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/promotion-package-template.md","Promotion Package Template (output_template, to promotion_package_artifact_id)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/outreach-queue-template.md","Outreach Queue Template (output_template, to connection_record_artifact_id)")</f>
         <v/>
       </c>
       <c r="I259" s="15" t="inlineStr">
@@ -14246,7 +14242,7 @@
       </c>
       <c r="J259" s="15" t="inlineStr">
         <is>
-          <t>promote-candidate-to-deal-room</t>
+          <t>record-linkedin-connection-attempt</t>
         </is>
       </c>
       <c r="K259" s="15" t="inlineStr">
@@ -14256,11 +14252,7 @@
       </c>
     </row>
     <row r="260" ht="18" customHeight="1" s="12">
-      <c r="A260" s="15" t="inlineStr">
-        <is>
-          <t>Jay</t>
-        </is>
-      </c>
+      <c r="A260" s="15" t="inlineStr"/>
       <c r="B260" s="15" t="inlineStr">
         <is>
           <t>Origination Pipeline</t>
@@ -14268,16 +14260,16 @@
       </c>
       <c r="C260" s="15" t="inlineStr">
         <is>
-          <t>Review Backlog</t>
+          <t>Connecting On Linkedin</t>
         </is>
       </c>
       <c r="D260" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/promote-candidate-to-deal-room.md","Promote Candidate to Deal Pipeline")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/record-linkedin-connection-attempt.md","Record LinkedIn Connection Attempt")</f>
         <v/>
       </c>
       <c r="E260" s="15" t="inlineStr">
         <is>
-          <t>Prepare a reviewed promotion package for creating or updating a Deal Pipeline from an approved origination candidate.</t>
+          <t>Capture a human-approved LinkedIn connection attempt and update the outbound state without sending messages automatically.</t>
         </is>
       </c>
       <c r="F260" s="16">
@@ -14285,11 +14277,11 @@
         <v/>
       </c>
       <c r="G260" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/founder-outreach-and-intro-paths/SKILL.md","founder-outreach-and-intro-paths")</f>
         <v/>
       </c>
       <c r="H260" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/origination-source-strategy-guide.md","Origination Source Strategy Guide (methodology)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
         <v/>
       </c>
       <c r="I260" s="15" t="inlineStr">
@@ -14299,7 +14291,7 @@
       </c>
       <c r="J260" s="15" t="inlineStr">
         <is>
-          <t>promote-candidate-to-deal-room</t>
+          <t>record-linkedin-connection-attempt</t>
         </is>
       </c>
       <c r="K260" s="15" t="inlineStr">
@@ -14309,11 +14301,7 @@
       </c>
     </row>
     <row r="261" ht="18" customHeight="1" s="12">
-      <c r="A261" s="15" t="inlineStr">
-        <is>
-          <t>Jay</t>
-        </is>
-      </c>
+      <c r="A261" s="15" t="inlineStr"/>
       <c r="B261" s="15" t="inlineStr">
         <is>
           <t>Origination Pipeline</t>
@@ -14321,16 +14309,16 @@
       </c>
       <c r="C261" s="15" t="inlineStr">
         <is>
-          <t>Review Backlog</t>
+          <t>Connecting On Linkedin</t>
         </is>
       </c>
       <c r="D261" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/promote-candidate-to-deal-room.md","Promote Candidate to Deal Pipeline")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/record-linkedin-connection-attempt.md","Record LinkedIn Connection Attempt")</f>
         <v/>
       </c>
       <c r="E261" s="15" t="inlineStr">
         <is>
-          <t>Prepare a reviewed promotion package for creating or updating a Deal Pipeline from an approved origination candidate.</t>
+          <t>Capture a human-approved LinkedIn connection attempt and update the outbound state without sending messages automatically.</t>
         </is>
       </c>
       <c r="F261" s="16">
@@ -14338,13 +14326,10 @@
         <v/>
       </c>
       <c r="G261" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/deal-room-setup-and-source-ingestion/SKILL.md","deal-room-setup-and-source-ingestion")</f>
-        <v/>
-      </c>
-      <c r="H261" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
-        <v/>
-      </c>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
+        <v/>
+      </c>
+      <c r="H261" s="15" t="inlineStr"/>
       <c r="I261" s="15" t="inlineStr">
         <is>
           <t>None declared</t>
@@ -14352,7 +14337,7 @@
       </c>
       <c r="J261" s="15" t="inlineStr">
         <is>
-          <t>promote-candidate-to-deal-room</t>
+          <t>record-linkedin-connection-attempt</t>
         </is>
       </c>
       <c r="K261" s="15" t="inlineStr">
@@ -14365,51 +14350,48 @@
       <c r="A262" s="15" t="inlineStr"/>
       <c r="B262" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="C262" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
-        </is>
-      </c>
-      <c r="D262" s="15" t="inlineStr">
-        <is>
-          <t>Project Variable Review</t>
-        </is>
+          <t>Initial Reachout Linkedin</t>
+        </is>
+      </c>
+      <c r="D262" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-linkedin-reachout.md","Prepare Initial LinkedIn Reachout")</f>
+        <v/>
       </c>
       <c r="E262" s="15" t="inlineStr">
         <is>
-          <t>Review workspace and project variables before normal execution.</t>
+          <t>Draft the first LinkedIn message after a candidate has been approved for outbound engagement.</t>
         </is>
       </c>
       <c r="F262" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
-        <v/>
-      </c>
-      <c r="G262" s="15" t="inlineStr">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-sourcing-operator.md","Sourcing Operator")</f>
+        <v/>
+      </c>
+      <c r="G262" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-outreach-draft-queue/SKILL.md","vc-outreach-draft-queue")</f>
+        <v/>
+      </c>
+      <c r="H262" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/outreach-queue-template.md","Outreach Queue Template (output_template, to initial_linkedin_reachout_artifact_id)")</f>
+        <v/>
+      </c>
+      <c r="I262" s="15" t="inlineStr">
         <is>
           <t>None declared</t>
         </is>
       </c>
-      <c r="H262" s="15" t="inlineStr">
-        <is>
-          <t>None declared</t>
-        </is>
-      </c>
-      <c r="I262" s="15" t="inlineStr">
-        <is>
-          <t>None declared</t>
-        </is>
-      </c>
       <c r="J262" s="15" t="inlineStr">
         <is>
-          <t>project-variable-review</t>
+          <t>prepare-initial-linkedin-reachout</t>
         </is>
       </c>
       <c r="K262" s="15" t="inlineStr">
         <is>
-          <t>setup</t>
+          <t>project_instance</t>
         </is>
       </c>
     </row>
@@ -14417,90 +14399,693 @@
       <c r="A263" s="15" t="inlineStr"/>
       <c r="B263" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="C263" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
-        </is>
-      </c>
-      <c r="D263" s="15" t="inlineStr">
-        <is>
-          <t>Project Team Invite Review</t>
-        </is>
+          <t>Initial Reachout Linkedin</t>
+        </is>
+      </c>
+      <c r="D263" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-linkedin-reachout.md","Prepare Initial LinkedIn Reachout")</f>
+        <v/>
       </c>
       <c r="E263" s="15" t="inlineStr">
         <is>
-          <t>Review suggested collaborators before sending invitations.</t>
+          <t>Draft the first LinkedIn message after a candidate has been approved for outbound engagement.</t>
         </is>
       </c>
       <c r="F263" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
-        <v/>
-      </c>
-      <c r="G263" s="15" t="inlineStr">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-sourcing-operator.md","Sourcing Operator")</f>
+        <v/>
+      </c>
+      <c r="G263" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/founder-outreach-and-intro-paths/SKILL.md","founder-outreach-and-intro-paths")</f>
+        <v/>
+      </c>
+      <c r="H263" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/origination-source-strategy-guide.md","Origination Source Strategy Guide (methodology)")</f>
+        <v/>
+      </c>
+      <c r="I263" s="15" t="inlineStr">
         <is>
           <t>None declared</t>
         </is>
       </c>
-      <c r="H263" s="15" t="inlineStr">
-        <is>
-          <t>None declared</t>
-        </is>
-      </c>
-      <c r="I263" s="15" t="inlineStr">
-        <is>
-          <t>None declared</t>
-        </is>
-      </c>
       <c r="J263" s="15" t="inlineStr">
         <is>
-          <t>project-team-invite</t>
+          <t>prepare-initial-linkedin-reachout</t>
         </is>
       </c>
       <c r="K263" s="15" t="inlineStr">
         <is>
-          <t>setup</t>
-        </is>
-      </c>
-    </row>
-    <row r="264" ht="90" customHeight="1" s="12">
+          <t>project_instance</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="18" customHeight="1" s="12">
       <c r="A264" s="15" t="inlineStr"/>
       <c r="B264" s="15" t="inlineStr">
         <is>
+          <t>Origination Pipeline</t>
+        </is>
+      </c>
+      <c r="C264" s="15" t="inlineStr">
+        <is>
+          <t>Initial Reachout Linkedin</t>
+        </is>
+      </c>
+      <c r="D264" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-linkedin-reachout.md","Prepare Initial LinkedIn Reachout")</f>
+        <v/>
+      </c>
+      <c r="E264" s="15" t="inlineStr">
+        <is>
+          <t>Draft the first LinkedIn message after a candidate has been approved for outbound engagement.</t>
+        </is>
+      </c>
+      <c r="F264" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-sourcing-operator.md","Sourcing Operator")</f>
+        <v/>
+      </c>
+      <c r="G264" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
+        <v/>
+      </c>
+      <c r="H264" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
+        <v/>
+      </c>
+      <c r="I264" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="J264" s="15" t="inlineStr">
+        <is>
+          <t>prepare-initial-linkedin-reachout</t>
+        </is>
+      </c>
+      <c r="K264" s="15" t="inlineStr">
+        <is>
+          <t>project_instance</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="18" customHeight="1" s="12">
+      <c r="A265" s="15" t="inlineStr"/>
+      <c r="B265" s="15" t="inlineStr">
+        <is>
+          <t>Origination Pipeline</t>
+        </is>
+      </c>
+      <c r="C265" s="15" t="inlineStr">
+        <is>
+          <t>Second Reachout Email</t>
+        </is>
+      </c>
+      <c r="D265" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-second-reachout-email.md","Prepare Second Reachout Email")</f>
+        <v/>
+      </c>
+      <c r="E265" s="15" t="inlineStr">
+        <is>
+          <t>Draft a second-touch email for candidates with LinkedIn outreach sent and no response after the configured wait period.</t>
+        </is>
+      </c>
+      <c r="F265" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-sourcing-operator.md","Sourcing Operator")</f>
+        <v/>
+      </c>
+      <c r="G265" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-outreach-draft-queue/SKILL.md","vc-outreach-draft-queue")</f>
+        <v/>
+      </c>
+      <c r="H265" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/outreach-queue-template.md","Outreach Queue Template (output_template, to second_reachout_email_artifact_id)")</f>
+        <v/>
+      </c>
+      <c r="I265" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="J265" s="15" t="inlineStr">
+        <is>
+          <t>prepare-second-reachout-email</t>
+        </is>
+      </c>
+      <c r="K265" s="15" t="inlineStr">
+        <is>
+          <t>project_instance</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="18" customHeight="1" s="12">
+      <c r="A266" s="15" t="inlineStr"/>
+      <c r="B266" s="15" t="inlineStr">
+        <is>
+          <t>Origination Pipeline</t>
+        </is>
+      </c>
+      <c r="C266" s="15" t="inlineStr">
+        <is>
+          <t>Second Reachout Email</t>
+        </is>
+      </c>
+      <c r="D266" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-second-reachout-email.md","Prepare Second Reachout Email")</f>
+        <v/>
+      </c>
+      <c r="E266" s="15" t="inlineStr">
+        <is>
+          <t>Draft a second-touch email for candidates with LinkedIn outreach sent and no response after the configured wait period.</t>
+        </is>
+      </c>
+      <c r="F266" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-sourcing-operator.md","Sourcing Operator")</f>
+        <v/>
+      </c>
+      <c r="G266" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/founder-outreach-and-intro-paths/SKILL.md","founder-outreach-and-intro-paths")</f>
+        <v/>
+      </c>
+      <c r="H266" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/origination-source-strategy-guide.md","Origination Source Strategy Guide (methodology)")</f>
+        <v/>
+      </c>
+      <c r="I266" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="J266" s="15" t="inlineStr">
+        <is>
+          <t>prepare-second-reachout-email</t>
+        </is>
+      </c>
+      <c r="K266" s="15" t="inlineStr">
+        <is>
+          <t>project_instance</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="18" customHeight="1" s="12">
+      <c r="A267" s="15" t="inlineStr"/>
+      <c r="B267" s="15" t="inlineStr">
+        <is>
+          <t>Origination Pipeline</t>
+        </is>
+      </c>
+      <c r="C267" s="15" t="inlineStr">
+        <is>
+          <t>Second Reachout Email</t>
+        </is>
+      </c>
+      <c r="D267" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-second-reachout-email.md","Prepare Second Reachout Email")</f>
+        <v/>
+      </c>
+      <c r="E267" s="15" t="inlineStr">
+        <is>
+          <t>Draft a second-touch email for candidates with LinkedIn outreach sent and no response after the configured wait period.</t>
+        </is>
+      </c>
+      <c r="F267" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-sourcing-operator.md","Sourcing Operator")</f>
+        <v/>
+      </c>
+      <c r="G267" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
+        <v/>
+      </c>
+      <c r="H267" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
+        <v/>
+      </c>
+      <c r="I267" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="J267" s="15" t="inlineStr">
+        <is>
+          <t>prepare-second-reachout-email</t>
+        </is>
+      </c>
+      <c r="K267" s="15" t="inlineStr">
+        <is>
+          <t>project_instance</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="18" customHeight="1" s="12">
+      <c r="A268" s="15" t="inlineStr"/>
+      <c r="B268" s="15" t="inlineStr">
+        <is>
+          <t>Origination Pipeline</t>
+        </is>
+      </c>
+      <c r="C268" s="15" t="inlineStr">
+        <is>
+          <t>Second Reachout Email</t>
+        </is>
+      </c>
+      <c r="D268" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-outreach-outcome.md","Review Outreach Outcome")</f>
+        <v/>
+      </c>
+      <c r="E268" s="15" t="inlineStr">
+        <is>
+          <t>Classify outbound outcomes after LinkedIn and email attempts into no response, engaged, pass, or watchlist.</t>
+        </is>
+      </c>
+      <c r="F268" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-sourcing-operator.md","Sourcing Operator")</f>
+        <v/>
+      </c>
+      <c r="G268" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-origination-deal-room-promotion/SKILL.md","vc-origination-deal-room-promotion")</f>
+        <v/>
+      </c>
+      <c r="H268" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/promotion-package-template.md","Promotion Package Template (output_template, to outreach_outcome_artifact_id)")</f>
+        <v/>
+      </c>
+      <c r="I268" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="J268" s="15" t="inlineStr">
+        <is>
+          <t>review-outreach-outcome</t>
+        </is>
+      </c>
+      <c r="K268" s="15" t="inlineStr">
+        <is>
+          <t>project_instance</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="18" customHeight="1" s="12">
+      <c r="A269" s="15" t="inlineStr"/>
+      <c r="B269" s="15" t="inlineStr">
+        <is>
+          <t>Origination Pipeline</t>
+        </is>
+      </c>
+      <c r="C269" s="15" t="inlineStr">
+        <is>
+          <t>Second Reachout Email</t>
+        </is>
+      </c>
+      <c r="D269" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-outreach-outcome.md","Review Outreach Outcome")</f>
+        <v/>
+      </c>
+      <c r="E269" s="15" t="inlineStr">
+        <is>
+          <t>Classify outbound outcomes after LinkedIn and email attempts into no response, engaged, pass, or watchlist.</t>
+        </is>
+      </c>
+      <c r="F269" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-sourcing-operator.md","Sourcing Operator")</f>
+        <v/>
+      </c>
+      <c r="G269" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-outreach-draft-queue/SKILL.md","vc-outreach-draft-queue")</f>
+        <v/>
+      </c>
+      <c r="H269" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/origination-source-strategy-guide.md","Origination Source Strategy Guide (methodology)")</f>
+        <v/>
+      </c>
+      <c r="I269" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="J269" s="15" t="inlineStr">
+        <is>
+          <t>review-outreach-outcome</t>
+        </is>
+      </c>
+      <c r="K269" s="15" t="inlineStr">
+        <is>
+          <t>project_instance</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="18" customHeight="1" s="12">
+      <c r="A270" s="15" t="inlineStr"/>
+      <c r="B270" s="15" t="inlineStr">
+        <is>
+          <t>Origination Pipeline</t>
+        </is>
+      </c>
+      <c r="C270" s="15" t="inlineStr">
+        <is>
+          <t>Second Reachout Email</t>
+        </is>
+      </c>
+      <c r="D270" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-outreach-outcome.md","Review Outreach Outcome")</f>
+        <v/>
+      </c>
+      <c r="E270" s="15" t="inlineStr">
+        <is>
+          <t>Classify outbound outcomes after LinkedIn and email attempts into no response, engaged, pass, or watchlist.</t>
+        </is>
+      </c>
+      <c r="F270" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-sourcing-operator.md","Sourcing Operator")</f>
+        <v/>
+      </c>
+      <c r="G270" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
+        <v/>
+      </c>
+      <c r="H270" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
+        <v/>
+      </c>
+      <c r="I270" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="J270" s="15" t="inlineStr">
+        <is>
+          <t>review-outreach-outcome</t>
+        </is>
+      </c>
+      <c r="K270" s="15" t="inlineStr">
+        <is>
+          <t>project_instance</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="18" customHeight="1" s="12">
+      <c r="A271" s="15" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="B271" s="15" t="inlineStr">
+        <is>
+          <t>Origination Pipeline</t>
+        </is>
+      </c>
+      <c r="C271" s="15" t="inlineStr">
+        <is>
+          <t>Engaged Added To Deal Funnel</t>
+        </is>
+      </c>
+      <c r="D271" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/promote-candidate-to-deal-room.md","Promote Candidate to Deal Pipeline")</f>
+        <v/>
+      </c>
+      <c r="E271" s="15" t="inlineStr">
+        <is>
+          <t>Prepare a reviewed promotion package for creating or updating a Deal Pipeline from an approved origination candidate.</t>
+        </is>
+      </c>
+      <c r="F271" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-sourcing-operator.md","Sourcing Operator")</f>
+        <v/>
+      </c>
+      <c r="G271" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-origination-deal-room-promotion/SKILL.md","vc-origination-deal-room-promotion")</f>
+        <v/>
+      </c>
+      <c r="H271" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/promotion-package-template.md","Promotion Package Template (output_template, to promotion_package_artifact_id)")</f>
+        <v/>
+      </c>
+      <c r="I271" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="J271" s="15" t="inlineStr">
+        <is>
+          <t>promote-candidate-to-deal-room</t>
+        </is>
+      </c>
+      <c r="K271" s="15" t="inlineStr">
+        <is>
+          <t>project_instance</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="18" customHeight="1" s="12">
+      <c r="A272" s="15" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="B272" s="15" t="inlineStr">
+        <is>
+          <t>Origination Pipeline</t>
+        </is>
+      </c>
+      <c r="C272" s="15" t="inlineStr">
+        <is>
+          <t>Engaged Added To Deal Funnel</t>
+        </is>
+      </c>
+      <c r="D272" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/promote-candidate-to-deal-room.md","Promote Candidate to Deal Pipeline")</f>
+        <v/>
+      </c>
+      <c r="E272" s="15" t="inlineStr">
+        <is>
+          <t>Prepare a reviewed promotion package for creating or updating a Deal Pipeline from an approved origination candidate.</t>
+        </is>
+      </c>
+      <c r="F272" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-sourcing-operator.md","Sourcing Operator")</f>
+        <v/>
+      </c>
+      <c r="G272" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
+        <v/>
+      </c>
+      <c r="H272" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/origination-source-strategy-guide.md","Origination Source Strategy Guide (methodology)")</f>
+        <v/>
+      </c>
+      <c r="I272" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="J272" s="15" t="inlineStr">
+        <is>
+          <t>promote-candidate-to-deal-room</t>
+        </is>
+      </c>
+      <c r="K272" s="15" t="inlineStr">
+        <is>
+          <t>project_instance</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="18" customHeight="1" s="12">
+      <c r="A273" s="15" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="B273" s="15" t="inlineStr">
+        <is>
+          <t>Origination Pipeline</t>
+        </is>
+      </c>
+      <c r="C273" s="15" t="inlineStr">
+        <is>
+          <t>Engaged Added To Deal Funnel</t>
+        </is>
+      </c>
+      <c r="D273" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/promote-candidate-to-deal-room.md","Promote Candidate to Deal Pipeline")</f>
+        <v/>
+      </c>
+      <c r="E273" s="15" t="inlineStr">
+        <is>
+          <t>Prepare a reviewed promotion package for creating or updating a Deal Pipeline from an approved origination candidate.</t>
+        </is>
+      </c>
+      <c r="F273" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-sourcing-operator.md","Sourcing Operator")</f>
+        <v/>
+      </c>
+      <c r="G273" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/deal-room-setup-and-source-ingestion/SKILL.md","deal-room-setup-and-source-ingestion")</f>
+        <v/>
+      </c>
+      <c r="H273" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
+        <v/>
+      </c>
+      <c r="I273" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="J273" s="15" t="inlineStr">
+        <is>
+          <t>promote-candidate-to-deal-room</t>
+        </is>
+      </c>
+      <c r="K273" s="15" t="inlineStr">
+        <is>
+          <t>project_instance</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="18" customHeight="1" s="12">
+      <c r="A274" s="15" t="inlineStr"/>
+      <c r="B274" s="15" t="inlineStr">
+        <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C264" s="15" t="inlineStr">
+      <c r="C274" s="15" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="D264" s="16">
+      <c r="D274" s="15" t="inlineStr">
+        <is>
+          <t>Project Variable Review</t>
+        </is>
+      </c>
+      <c r="E274" s="15" t="inlineStr">
+        <is>
+          <t>Review workspace and project variables before normal execution.</t>
+        </is>
+      </c>
+      <c r="F274" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
+        <v/>
+      </c>
+      <c r="G274" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="H274" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="I274" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="J274" s="15" t="inlineStr">
+        <is>
+          <t>project-variable-review</t>
+        </is>
+      </c>
+      <c r="K274" s="15" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="18" customHeight="1" s="12">
+      <c r="A275" s="15" t="inlineStr"/>
+      <c r="B275" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="C275" s="15" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="D275" s="15" t="inlineStr">
+        <is>
+          <t>Project Team Invite Review</t>
+        </is>
+      </c>
+      <c r="E275" s="15" t="inlineStr">
+        <is>
+          <t>Review suggested collaborators before sending invitations.</t>
+        </is>
+      </c>
+      <c r="F275" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
+        <v/>
+      </c>
+      <c r="G275" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="H275" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="I275" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="J275" s="15" t="inlineStr">
+        <is>
+          <t>project-team-invite</t>
+        </is>
+      </c>
+      <c r="K275" s="15" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="90" customHeight="1" s="12">
+      <c r="A276" s="15" t="inlineStr"/>
+      <c r="B276" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="C276" s="15" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="D276" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/vc-pack-variable-discovery.md","VC Pack Variable Discovery")</f>
         <v/>
       </c>
-      <c r="E264" s="15" t="inlineStr">
+      <c r="E276" s="15" t="inlineStr">
         <is>
           <t>Best-effort, review-only discovery for VC Pack Setup variables and invite suggestions.</t>
         </is>
       </c>
-      <c r="F264" s="16">
+      <c r="F276" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G264" s="15" t="inlineStr">
+      <c r="G276" s="15" t="inlineStr">
         <is>
           <t>None declared</t>
         </is>
       </c>
-      <c r="H264" s="15" t="inlineStr">
+      <c r="H276" s="15" t="inlineStr">
         <is>
           <t>None declared</t>
         </is>
       </c>
-      <c r="I264" s="15" t="inlineStr">
+      <c r="I276" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -14510,55 +15095,55 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J264" s="15" t="inlineStr">
+      <c r="J276" s="15" t="inlineStr">
         <is>
           <t>vc-pack-variable-discovery</t>
         </is>
       </c>
-      <c r="K264" s="15" t="inlineStr">
+      <c r="K276" s="15" t="inlineStr">
         <is>
           <t>setup</t>
         </is>
       </c>
     </row>
-    <row r="265" ht="120" customHeight="1" s="12">
-      <c r="A265" s="15" t="inlineStr">
+    <row r="277" ht="120" customHeight="1" s="12">
+      <c r="A277" s="15" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="B265" s="15" t="inlineStr">
+      <c r="B277" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C265" s="15" t="inlineStr">
+      <c r="C277" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D265" s="16">
+      <c r="D277" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-commercial-dd.md","Run Commercial DD")</f>
         <v/>
       </c>
-      <c r="E265" s="15" t="inlineStr">
+      <c r="E277" s="15" t="inlineStr">
         <is>
           <t>Run Commercial DD for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F265" s="16">
+      <c r="F277" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G265" s="16">
+      <c r="G277" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
         <v/>
       </c>
-      <c r="H265" s="16">
+      <c r="H277" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/diligence-report-template.md","Diligence Report Template (output_template, to commercial_dd_artifact_id)")</f>
         <v/>
       </c>
-      <c r="I265" s="15" t="inlineStr">
+      <c r="I277" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -14570,55 +15155,55 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J265" s="15" t="inlineStr">
+      <c r="J277" s="15" t="inlineStr">
         <is>
           <t>run-commercial-dd</t>
         </is>
       </c>
-      <c r="K265" s="15" t="inlineStr">
+      <c r="K277" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="266" ht="120" customHeight="1" s="12">
-      <c r="A266" s="15" t="inlineStr">
+    <row r="278" ht="120" customHeight="1" s="12">
+      <c r="A278" s="15" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="B266" s="15" t="inlineStr">
+      <c r="B278" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C266" s="15" t="inlineStr">
+      <c r="C278" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D266" s="16">
+      <c r="D278" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-commercial-dd.md","Run Commercial DD")</f>
         <v/>
       </c>
-      <c r="E266" s="15" t="inlineStr">
+      <c r="E278" s="15" t="inlineStr">
         <is>
           <t>Run Commercial DD for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F266" s="16">
+      <c r="F278" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G266" s="16">
+      <c r="G278" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/commercial-diligence-workstream/SKILL.md","commercial-diligence-workstream")</f>
         <v/>
       </c>
-      <c r="H266" s="16">
+      <c r="H278" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/formal-diligence-workstream-guide.md","Formal Diligence Workstream Guide (methodology)")</f>
         <v/>
       </c>
-      <c r="I266" s="15" t="inlineStr">
+      <c r="I278" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -14630,52 +15215,52 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J266" s="15" t="inlineStr">
+      <c r="J278" s="15" t="inlineStr">
         <is>
           <t>run-commercial-dd</t>
         </is>
       </c>
-      <c r="K266" s="15" t="inlineStr">
+      <c r="K278" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="267" ht="120" customHeight="1" s="12">
-      <c r="A267" s="15" t="inlineStr">
+    <row r="279" ht="120" customHeight="1" s="12">
+      <c r="A279" s="15" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="B267" s="15" t="inlineStr">
+      <c r="B279" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C267" s="15" t="inlineStr">
+      <c r="C279" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D267" s="16">
+      <c r="D279" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-commercial-dd.md","Run Commercial DD")</f>
         <v/>
       </c>
-      <c r="E267" s="15" t="inlineStr">
+      <c r="E279" s="15" t="inlineStr">
         <is>
           <t>Run Commercial DD for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F267" s="16">
+      <c r="F279" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G267" s="15" t="inlineStr"/>
-      <c r="H267" s="16">
+      <c r="G279" s="15" t="inlineStr"/>
+      <c r="H279" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/formal-diligence-checklist.md","Formal Diligence Checklist (checklist)")</f>
         <v/>
       </c>
-      <c r="I267" s="15" t="inlineStr">
+      <c r="I279" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -14687,52 +15272,52 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J267" s="15" t="inlineStr">
+      <c r="J279" s="15" t="inlineStr">
         <is>
           <t>run-commercial-dd</t>
         </is>
       </c>
-      <c r="K267" s="15" t="inlineStr">
+      <c r="K279" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="268" ht="120" customHeight="1" s="12">
-      <c r="A268" s="15" t="inlineStr">
+    <row r="280" ht="120" customHeight="1" s="12">
+      <c r="A280" s="15" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="B268" s="15" t="inlineStr">
+      <c r="B280" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C268" s="15" t="inlineStr">
+      <c r="C280" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D268" s="16">
+      <c r="D280" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-commercial-dd.md","Run Commercial DD")</f>
         <v/>
       </c>
-      <c r="E268" s="15" t="inlineStr">
+      <c r="E280" s="15" t="inlineStr">
         <is>
           <t>Run Commercial DD for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F268" s="16">
+      <c r="F280" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G268" s="15" t="inlineStr"/>
-      <c r="H268" s="16">
+      <c r="G280" s="15" t="inlineStr"/>
+      <c r="H280" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (style_guide)")</f>
         <v/>
       </c>
-      <c r="I268" s="15" t="inlineStr">
+      <c r="I280" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -14744,52 +15329,52 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J268" s="15" t="inlineStr">
+      <c r="J280" s="15" t="inlineStr">
         <is>
           <t>run-commercial-dd</t>
         </is>
       </c>
-      <c r="K268" s="15" t="inlineStr">
+      <c r="K280" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="269" ht="120" customHeight="1" s="12">
-      <c r="A269" s="15" t="inlineStr">
+    <row r="281" ht="120" customHeight="1" s="12">
+      <c r="A281" s="15" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="B269" s="15" t="inlineStr">
+      <c r="B281" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C269" s="15" t="inlineStr">
+      <c r="C281" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D269" s="16">
+      <c r="D281" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-commercial-dd.md","Run Commercial DD")</f>
         <v/>
       </c>
-      <c r="E269" s="15" t="inlineStr">
+      <c r="E281" s="15" t="inlineStr">
         <is>
           <t>Run Commercial DD for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F269" s="16">
+      <c r="F281" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G269" s="15" t="inlineStr"/>
-      <c r="H269" s="16">
+      <c r="G281" s="15" t="inlineStr"/>
+      <c r="H281" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
         <v/>
       </c>
-      <c r="I269" s="15" t="inlineStr">
+      <c r="I281" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -14801,55 +15386,55 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J269" s="15" t="inlineStr">
+      <c r="J281" s="15" t="inlineStr">
         <is>
           <t>run-commercial-dd</t>
         </is>
       </c>
-      <c r="K269" s="15" t="inlineStr">
+      <c r="K281" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="270" ht="120" customHeight="1" s="12">
-      <c r="A270" s="15" t="inlineStr">
+    <row r="282" ht="120" customHeight="1" s="12">
+      <c r="A282" s="15" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
       </c>
-      <c r="B270" s="15" t="inlineStr">
+      <c r="B282" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C270" s="15" t="inlineStr">
+      <c r="C282" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D270" s="16">
+      <c r="D282" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
         <v/>
       </c>
-      <c r="E270" s="15" t="inlineStr">
+      <c r="E282" s="15" t="inlineStr">
         <is>
           <t>Run Financial DD for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F270" s="16">
+      <c r="F282" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G270" s="16">
+      <c r="G282" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
         <v/>
       </c>
-      <c r="H270" s="16">
+      <c r="H282" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/diligence-report-template.md","Diligence Report Template (output_template, to financial_dd_artifact_id)")</f>
         <v/>
       </c>
-      <c r="I270" s="15" t="inlineStr">
+      <c r="I282" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -14861,55 +15446,55 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J270" s="15" t="inlineStr">
+      <c r="J282" s="15" t="inlineStr">
         <is>
           <t>run-financial-dd</t>
         </is>
       </c>
-      <c r="K270" s="15" t="inlineStr">
+      <c r="K282" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="271" ht="120" customHeight="1" s="12">
-      <c r="A271" s="15" t="inlineStr">
+    <row r="283" ht="120" customHeight="1" s="12">
+      <c r="A283" s="15" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
       </c>
-      <c r="B271" s="15" t="inlineStr">
+      <c r="B283" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C271" s="15" t="inlineStr">
+      <c r="C283" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D271" s="16">
+      <c r="D283" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
         <v/>
       </c>
-      <c r="E271" s="15" t="inlineStr">
+      <c r="E283" s="15" t="inlineStr">
         <is>
           <t>Run Financial DD for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F271" s="16">
+      <c r="F283" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G271" s="16">
+      <c r="G283" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/financial-diligence-workstream/SKILL.md","financial-diligence-workstream")</f>
         <v/>
       </c>
-      <c r="H271" s="16">
+      <c r="H283" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/formal-diligence-workstream-guide.md","Formal Diligence Workstream Guide (methodology)")</f>
         <v/>
       </c>
-      <c r="I271" s="15" t="inlineStr">
+      <c r="I283" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -14921,52 +15506,52 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J271" s="15" t="inlineStr">
+      <c r="J283" s="15" t="inlineStr">
         <is>
           <t>run-financial-dd</t>
         </is>
       </c>
-      <c r="K271" s="15" t="inlineStr">
+      <c r="K283" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="272" ht="120" customHeight="1" s="12">
-      <c r="A272" s="15" t="inlineStr">
+    <row r="284" ht="120" customHeight="1" s="12">
+      <c r="A284" s="15" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
       </c>
-      <c r="B272" s="15" t="inlineStr">
+      <c r="B284" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C272" s="15" t="inlineStr">
+      <c r="C284" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D272" s="16">
+      <c r="D284" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
         <v/>
       </c>
-      <c r="E272" s="15" t="inlineStr">
+      <c r="E284" s="15" t="inlineStr">
         <is>
           <t>Run Financial DD for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F272" s="16">
+      <c r="F284" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G272" s="15" t="inlineStr"/>
-      <c r="H272" s="16">
+      <c r="G284" s="15" t="inlineStr"/>
+      <c r="H284" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/formal-diligence-checklist.md","Formal Diligence Checklist (checklist)")</f>
         <v/>
       </c>
-      <c r="I272" s="15" t="inlineStr">
+      <c r="I284" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -14978,52 +15563,52 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J272" s="15" t="inlineStr">
+      <c r="J284" s="15" t="inlineStr">
         <is>
           <t>run-financial-dd</t>
         </is>
       </c>
-      <c r="K272" s="15" t="inlineStr">
+      <c r="K284" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="273" ht="120" customHeight="1" s="12">
-      <c r="A273" s="15" t="inlineStr">
+    <row r="285" ht="120" customHeight="1" s="12">
+      <c r="A285" s="15" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
       </c>
-      <c r="B273" s="15" t="inlineStr">
+      <c r="B285" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C273" s="15" t="inlineStr">
+      <c r="C285" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D273" s="16">
+      <c r="D285" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
         <v/>
       </c>
-      <c r="E273" s="15" t="inlineStr">
+      <c r="E285" s="15" t="inlineStr">
         <is>
           <t>Run Financial DD for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F273" s="16">
+      <c r="F285" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G273" s="15" t="inlineStr"/>
-      <c r="H273" s="16">
+      <c r="G285" s="15" t="inlineStr"/>
+      <c r="H285" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/diligence-report-template.md","Diligence Report Template (output_template, to unit_economics_artifact_id)")</f>
         <v/>
       </c>
-      <c r="I273" s="15" t="inlineStr">
+      <c r="I285" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -15035,52 +15620,52 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J273" s="15" t="inlineStr">
+      <c r="J285" s="15" t="inlineStr">
         <is>
           <t>run-financial-dd</t>
         </is>
       </c>
-      <c r="K273" s="15" t="inlineStr">
+      <c r="K285" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="274" ht="120" customHeight="1" s="12">
-      <c r="A274" s="15" t="inlineStr">
+    <row r="286" ht="120" customHeight="1" s="12">
+      <c r="A286" s="15" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
       </c>
-      <c r="B274" s="15" t="inlineStr">
+      <c r="B286" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C274" s="15" t="inlineStr">
+      <c r="C286" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D274" s="16">
+      <c r="D286" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
         <v/>
       </c>
-      <c r="E274" s="15" t="inlineStr">
+      <c r="E286" s="15" t="inlineStr">
         <is>
           <t>Run Financial DD for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F274" s="16">
+      <c r="F286" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G274" s="15" t="inlineStr"/>
-      <c r="H274" s="16">
+      <c r="G286" s="15" t="inlineStr"/>
+      <c r="H286" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (style_guide)")</f>
         <v/>
       </c>
-      <c r="I274" s="15" t="inlineStr">
+      <c r="I286" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -15092,52 +15677,52 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J274" s="15" t="inlineStr">
+      <c r="J286" s="15" t="inlineStr">
         <is>
           <t>run-financial-dd</t>
         </is>
       </c>
-      <c r="K274" s="15" t="inlineStr">
+      <c r="K286" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="275" ht="120" customHeight="1" s="12">
-      <c r="A275" s="15" t="inlineStr">
+    <row r="287" ht="120" customHeight="1" s="12">
+      <c r="A287" s="15" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
       </c>
-      <c r="B275" s="15" t="inlineStr">
+      <c r="B287" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C275" s="15" t="inlineStr">
+      <c r="C287" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D275" s="16">
+      <c r="D287" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
         <v/>
       </c>
-      <c r="E275" s="15" t="inlineStr">
+      <c r="E287" s="15" t="inlineStr">
         <is>
           <t>Run Financial DD for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F275" s="16">
+      <c r="F287" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G275" s="15" t="inlineStr"/>
-      <c r="H275" s="16">
+      <c r="G287" s="15" t="inlineStr"/>
+      <c r="H287" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
         <v/>
       </c>
-      <c r="I275" s="15" t="inlineStr">
+      <c r="I287" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -15149,55 +15734,55 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J275" s="15" t="inlineStr">
+      <c r="J287" s="15" t="inlineStr">
         <is>
           <t>run-financial-dd</t>
         </is>
       </c>
-      <c r="K275" s="15" t="inlineStr">
+      <c r="K287" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="276" ht="120" customHeight="1" s="12">
-      <c r="A276" s="15" t="inlineStr">
+    <row r="288" ht="120" customHeight="1" s="12">
+      <c r="A288" s="15" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
       </c>
-      <c r="B276" s="15" t="inlineStr">
+      <c r="B288" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C276" s="15" t="inlineStr">
+      <c r="C288" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D276" s="16">
+      <c r="D288" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
         <v/>
       </c>
-      <c r="E276" s="15" t="inlineStr">
+      <c r="E288" s="15" t="inlineStr">
         <is>
           <t>Run Founder Evaluation for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F276" s="16">
+      <c r="F288" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G276" s="16">
+      <c r="G288" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/team-and-hiring-assessment/SKILL.md","team-and-hiring-assessment")</f>
         <v/>
       </c>
-      <c r="H276" s="16">
+      <c r="H288" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/diligence-report-template.md","Diligence Report Template (output_template, to founder_evaluation_artifact_id)")</f>
         <v/>
       </c>
-      <c r="I276" s="15" t="inlineStr">
+      <c r="I288" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -15209,55 +15794,55 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J276" s="15" t="inlineStr">
+      <c r="J288" s="15" t="inlineStr">
         <is>
           <t>run-founder-evaluation</t>
         </is>
       </c>
-      <c r="K276" s="15" t="inlineStr">
+      <c r="K288" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="277" ht="120" customHeight="1" s="12">
-      <c r="A277" s="15" t="inlineStr">
+    <row r="289" ht="120" customHeight="1" s="12">
+      <c r="A289" s="15" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
       </c>
-      <c r="B277" s="15" t="inlineStr">
+      <c r="B289" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C277" s="15" t="inlineStr">
+      <c r="C289" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D277" s="16">
+      <c r="D289" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
         <v/>
       </c>
-      <c r="E277" s="15" t="inlineStr">
+      <c r="E289" s="15" t="inlineStr">
         <is>
           <t>Run Founder Evaluation for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F277" s="16">
+      <c r="F289" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G277" s="16">
+      <c r="G289" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/red-flags-scanner/SKILL.md","red-flags-scanner")</f>
         <v/>
       </c>
-      <c r="H277" s="16">
+      <c r="H289" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/formal-diligence-workstream-guide.md","Formal Diligence Workstream Guide (methodology)")</f>
         <v/>
       </c>
-      <c r="I277" s="15" t="inlineStr">
+      <c r="I289" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -15269,55 +15854,55 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J277" s="15" t="inlineStr">
+      <c r="J289" s="15" t="inlineStr">
         <is>
           <t>run-founder-evaluation</t>
         </is>
       </c>
-      <c r="K277" s="15" t="inlineStr">
+      <c r="K289" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="278" ht="120" customHeight="1" s="12">
-      <c r="A278" s="15" t="inlineStr">
+    <row r="290" ht="120" customHeight="1" s="12">
+      <c r="A290" s="15" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
       </c>
-      <c r="B278" s="15" t="inlineStr">
+      <c r="B290" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C278" s="15" t="inlineStr">
+      <c r="C290" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D278" s="16">
+      <c r="D290" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
         <v/>
       </c>
-      <c r="E278" s="15" t="inlineStr">
+      <c r="E290" s="15" t="inlineStr">
         <is>
           <t>Run Founder Evaluation for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F278" s="16">
+      <c r="F290" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G278" s="16">
+      <c r="G290" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
         <v/>
       </c>
-      <c r="H278" s="16">
+      <c r="H290" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/formal-diligence-checklist.md","Formal Diligence Checklist (checklist)")</f>
         <v/>
       </c>
-      <c r="I278" s="15" t="inlineStr">
+      <c r="I290" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -15329,55 +15914,55 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J278" s="15" t="inlineStr">
+      <c r="J290" s="15" t="inlineStr">
         <is>
           <t>run-founder-evaluation</t>
         </is>
       </c>
-      <c r="K278" s="15" t="inlineStr">
+      <c r="K290" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="279" ht="120" customHeight="1" s="12">
-      <c r="A279" s="15" t="inlineStr">
+    <row r="291" ht="120" customHeight="1" s="12">
+      <c r="A291" s="15" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
       </c>
-      <c r="B279" s="15" t="inlineStr">
+      <c r="B291" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C279" s="15" t="inlineStr">
+      <c r="C291" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D279" s="16">
+      <c r="D291" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
         <v/>
       </c>
-      <c r="E279" s="15" t="inlineStr">
+      <c r="E291" s="15" t="inlineStr">
         <is>
           <t>Run Founder Evaluation for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F279" s="16">
+      <c r="F291" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G279" s="16">
+      <c r="G291" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/founder-evaluation-and-reference-checking/SKILL.md","founder-evaluation-and-reference-checking")</f>
         <v/>
       </c>
-      <c r="H279" s="16">
+      <c r="H291" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (style_guide)")</f>
         <v/>
       </c>
-      <c r="I279" s="15" t="inlineStr">
+      <c r="I291" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -15389,52 +15974,52 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J279" s="15" t="inlineStr">
+      <c r="J291" s="15" t="inlineStr">
         <is>
           <t>run-founder-evaluation</t>
         </is>
       </c>
-      <c r="K279" s="15" t="inlineStr">
+      <c r="K291" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="280" ht="120" customHeight="1" s="12">
-      <c r="A280" s="15" t="inlineStr">
+    <row r="292" ht="120" customHeight="1" s="12">
+      <c r="A292" s="15" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
       </c>
-      <c r="B280" s="15" t="inlineStr">
+      <c r="B292" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C280" s="15" t="inlineStr">
+      <c r="C292" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D280" s="16">
+      <c r="D292" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
         <v/>
       </c>
-      <c r="E280" s="15" t="inlineStr">
+      <c r="E292" s="15" t="inlineStr">
         <is>
           <t>Run Founder Evaluation for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F280" s="16">
+      <c r="F292" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G280" s="15" t="inlineStr"/>
-      <c r="H280" s="16">
+      <c r="G292" s="15" t="inlineStr"/>
+      <c r="H292" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
         <v/>
       </c>
-      <c r="I280" s="15" t="inlineStr">
+      <c r="I292" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -15446,55 +16031,55 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J280" s="15" t="inlineStr">
+      <c r="J292" s="15" t="inlineStr">
         <is>
           <t>run-founder-evaluation</t>
         </is>
       </c>
-      <c r="K280" s="15" t="inlineStr">
+      <c r="K292" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="281" ht="120" customHeight="1" s="12">
-      <c r="A281" s="15" t="inlineStr">
+    <row r="293" ht="120" customHeight="1" s="12">
+      <c r="A293" s="15" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
       </c>
-      <c r="B281" s="15" t="inlineStr">
+      <c r="B293" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C281" s="15" t="inlineStr">
+      <c r="C293" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D281" s="16">
+      <c r="D293" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
         <v/>
       </c>
-      <c r="E281" s="15" t="inlineStr">
+      <c r="E293" s="15" t="inlineStr">
         <is>
           <t>Run Technical DD for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F281" s="16">
+      <c r="F293" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G281" s="16">
+      <c r="G293" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/team-and-hiring-assessment/SKILL.md","team-and-hiring-assessment")</f>
         <v/>
       </c>
-      <c r="H281" s="16">
+      <c r="H293" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/diligence-report-template.md","Diligence Report Template (output_template, to technical_dd_artifact_id)")</f>
         <v/>
       </c>
-      <c r="I281" s="15" t="inlineStr">
+      <c r="I293" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -15506,55 +16091,55 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J281" s="15" t="inlineStr">
+      <c r="J293" s="15" t="inlineStr">
         <is>
           <t>run-technical-dd</t>
         </is>
       </c>
-      <c r="K281" s="15" t="inlineStr">
+      <c r="K293" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="282" ht="120" customHeight="1" s="12">
-      <c r="A282" s="15" t="inlineStr">
+    <row r="294" ht="120" customHeight="1" s="12">
+      <c r="A294" s="15" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
       </c>
-      <c r="B282" s="15" t="inlineStr">
+      <c r="B294" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C282" s="15" t="inlineStr">
+      <c r="C294" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D282" s="16">
+      <c r="D294" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
         <v/>
       </c>
-      <c r="E282" s="15" t="inlineStr">
+      <c r="E294" s="15" t="inlineStr">
         <is>
           <t>Run Technical DD for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F282" s="16">
+      <c r="F294" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G282" s="16">
+      <c r="G294" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/red-flags-scanner/SKILL.md","red-flags-scanner")</f>
         <v/>
       </c>
-      <c r="H282" s="16">
+      <c r="H294" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/formal-diligence-workstream-guide.md","Formal Diligence Workstream Guide (methodology)")</f>
         <v/>
       </c>
-      <c r="I282" s="15" t="inlineStr">
+      <c r="I294" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -15566,55 +16151,55 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J282" s="15" t="inlineStr">
+      <c r="J294" s="15" t="inlineStr">
         <is>
           <t>run-technical-dd</t>
         </is>
       </c>
-      <c r="K282" s="15" t="inlineStr">
+      <c r="K294" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="283" ht="120" customHeight="1" s="12">
-      <c r="A283" s="15" t="inlineStr">
+    <row r="295" ht="120" customHeight="1" s="12">
+      <c r="A295" s="15" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
       </c>
-      <c r="B283" s="15" t="inlineStr">
+      <c r="B295" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C283" s="15" t="inlineStr">
+      <c r="C295" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D283" s="16">
+      <c r="D295" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
         <v/>
       </c>
-      <c r="E283" s="15" t="inlineStr">
+      <c r="E295" s="15" t="inlineStr">
         <is>
           <t>Run Technical DD for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F283" s="16">
+      <c r="F295" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G283" s="16">
+      <c r="G295" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
         <v/>
       </c>
-      <c r="H283" s="16">
+      <c r="H295" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/formal-diligence-checklist.md","Formal Diligence Checklist (checklist)")</f>
         <v/>
       </c>
-      <c r="I283" s="15" t="inlineStr">
+      <c r="I295" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -15626,55 +16211,55 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J283" s="15" t="inlineStr">
+      <c r="J295" s="15" t="inlineStr">
         <is>
           <t>run-technical-dd</t>
         </is>
       </c>
-      <c r="K283" s="15" t="inlineStr">
+      <c r="K295" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="284" ht="120" customHeight="1" s="12">
-      <c r="A284" s="15" t="inlineStr">
+    <row r="296" ht="120" customHeight="1" s="12">
+      <c r="A296" s="15" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
       </c>
-      <c r="B284" s="15" t="inlineStr">
+      <c r="B296" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C284" s="15" t="inlineStr">
+      <c r="C296" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D284" s="16">
+      <c r="D296" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
         <v/>
       </c>
-      <c r="E284" s="15" t="inlineStr">
+      <c r="E296" s="15" t="inlineStr">
         <is>
           <t>Run Technical DD for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F284" s="16">
+      <c r="F296" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G284" s="16">
+      <c r="G296" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/technical-diligence-workstream/SKILL.md","technical-diligence-workstream")</f>
         <v/>
       </c>
-      <c r="H284" s="16">
+      <c r="H296" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (style_guide)")</f>
         <v/>
       </c>
-      <c r="I284" s="15" t="inlineStr">
+      <c r="I296" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -15686,52 +16271,52 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J284" s="15" t="inlineStr">
+      <c r="J296" s="15" t="inlineStr">
         <is>
           <t>run-technical-dd</t>
         </is>
       </c>
-      <c r="K284" s="15" t="inlineStr">
+      <c r="K296" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="285" ht="120" customHeight="1" s="12">
-      <c r="A285" s="15" t="inlineStr">
+    <row r="297" ht="120" customHeight="1" s="12">
+      <c r="A297" s="15" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
       </c>
-      <c r="B285" s="15" t="inlineStr">
+      <c r="B297" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C285" s="15" t="inlineStr">
+      <c r="C297" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D285" s="16">
+      <c r="D297" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
         <v/>
       </c>
-      <c r="E285" s="15" t="inlineStr">
+      <c r="E297" s="15" t="inlineStr">
         <is>
           <t>Run Technical DD for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F285" s="16">
+      <c r="F297" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-diligence-analyst.md","Diligence Analyst")</f>
         <v/>
       </c>
-      <c r="G285" s="15" t="inlineStr"/>
-      <c r="H285" s="16">
+      <c r="G297" s="15" t="inlineStr"/>
+      <c r="H297" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
         <v/>
       </c>
-      <c r="I285" s="15" t="inlineStr">
+      <c r="I297" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -15743,51 +16328,51 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J285" s="15" t="inlineStr">
+      <c r="J297" s="15" t="inlineStr">
         <is>
           <t>run-technical-dd</t>
         </is>
       </c>
-      <c r="K285" s="15" t="inlineStr">
+      <c r="K297" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="286" ht="90" customHeight="1" s="12">
-      <c r="A286" s="15" t="inlineStr"/>
-      <c r="B286" s="15" t="inlineStr">
+    <row r="298" ht="90" customHeight="1" s="12">
+      <c r="A298" s="15" t="inlineStr"/>
+      <c r="B298" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C286" s="15" t="inlineStr">
+      <c r="C298" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D286" s="16">
+      <c r="D298" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
         <v/>
       </c>
-      <c r="E286" s="15" t="inlineStr">
+      <c r="E298" s="15" t="inlineStr">
         <is>
           <t>Coordinate legal diligence document indexing, issue tracking, counsel questions, and showstopper-risk review support without providing legal advice.</t>
         </is>
       </c>
-      <c r="F286" s="16">
+      <c r="F298" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G286" s="16">
+      <c r="G298" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/legal-diligence-coordination/SKILL.md","legal-diligence-coordination")</f>
         <v/>
       </c>
-      <c r="H286" s="16">
+      <c r="H298" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/legal-diligence-tracker-template.md","Legal Diligence Tracker Template (output_template, to legal_diligence_artifact_id)")</f>
         <v/>
       </c>
-      <c r="I286" s="15" t="inlineStr">
+      <c r="I298" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -15797,51 +16382,51 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J286" s="15" t="inlineStr">
+      <c r="J298" s="15" t="inlineStr">
         <is>
           <t>run-legal-diligence</t>
         </is>
       </c>
-      <c r="K286" s="15" t="inlineStr">
+      <c r="K298" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="287" ht="90" customHeight="1" s="12">
-      <c r="A287" s="15" t="inlineStr"/>
-      <c r="B287" s="15" t="inlineStr">
+    <row r="299" ht="90" customHeight="1" s="12">
+      <c r="A299" s="15" t="inlineStr"/>
+      <c r="B299" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C287" s="15" t="inlineStr">
+      <c r="C299" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D287" s="16">
+      <c r="D299" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
         <v/>
       </c>
-      <c r="E287" s="15" t="inlineStr">
+      <c r="E299" s="15" t="inlineStr">
         <is>
           <t>Coordinate legal diligence document indexing, issue tracking, counsel questions, and showstopper-risk review support without providing legal advice.</t>
         </is>
       </c>
-      <c r="F287" s="16">
+      <c r="F299" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G287" s="16">
+      <c r="G299" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/red-flags-scanner/SKILL.md","red-flags-scanner")</f>
         <v/>
       </c>
-      <c r="H287" s="16">
+      <c r="H299" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/legal-diligence-guide.md","Legal Diligence Guide (methodology)")</f>
         <v/>
       </c>
-      <c r="I287" s="15" t="inlineStr">
+      <c r="I299" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -15851,51 +16436,51 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J287" s="15" t="inlineStr">
+      <c r="J299" s="15" t="inlineStr">
         <is>
           <t>run-legal-diligence</t>
         </is>
       </c>
-      <c r="K287" s="15" t="inlineStr">
+      <c r="K299" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="288" ht="90" customHeight="1" s="12">
-      <c r="A288" s="15" t="inlineStr"/>
-      <c r="B288" s="15" t="inlineStr">
+    <row r="300" ht="90" customHeight="1" s="12">
+      <c r="A300" s="15" t="inlineStr"/>
+      <c r="B300" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C288" s="15" t="inlineStr">
+      <c r="C300" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D288" s="16">
+      <c r="D300" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
         <v/>
       </c>
-      <c r="E288" s="15" t="inlineStr">
+      <c r="E300" s="15" t="inlineStr">
         <is>
           <t>Coordinate legal diligence document indexing, issue tracking, counsel questions, and showstopper-risk review support without providing legal advice.</t>
         </is>
       </c>
-      <c r="F288" s="16">
+      <c r="F300" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G288" s="16">
+      <c r="G300" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
         <v/>
       </c>
-      <c r="H288" s="16">
+      <c r="H300" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/formal-diligence-workstream-guide.md","Formal Diligence Workstream Guide (methodology)")</f>
         <v/>
       </c>
-      <c r="I288" s="15" t="inlineStr">
+      <c r="I300" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -15905,48 +16490,48 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J288" s="15" t="inlineStr">
+      <c r="J300" s="15" t="inlineStr">
         <is>
           <t>run-legal-diligence</t>
         </is>
       </c>
-      <c r="K288" s="15" t="inlineStr">
+      <c r="K300" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="289" ht="90" customHeight="1" s="12">
-      <c r="A289" s="15" t="inlineStr"/>
-      <c r="B289" s="15" t="inlineStr">
+    <row r="301" ht="90" customHeight="1" s="12">
+      <c r="A301" s="15" t="inlineStr"/>
+      <c r="B301" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C289" s="15" t="inlineStr">
+      <c r="C301" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D289" s="16">
+      <c r="D301" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
         <v/>
       </c>
-      <c r="E289" s="15" t="inlineStr">
+      <c r="E301" s="15" t="inlineStr">
         <is>
           <t>Coordinate legal diligence document indexing, issue tracking, counsel questions, and showstopper-risk review support without providing legal advice.</t>
         </is>
       </c>
-      <c r="F289" s="16">
+      <c r="F301" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G289" s="15" t="inlineStr"/>
-      <c r="H289" s="16">
+      <c r="G301" s="15" t="inlineStr"/>
+      <c r="H301" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/formal-diligence-checklist.md","Formal Diligence Checklist (checklist)")</f>
         <v/>
       </c>
-      <c r="I289" s="15" t="inlineStr">
+      <c r="I301" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -15956,48 +16541,48 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J289" s="15" t="inlineStr">
+      <c r="J301" s="15" t="inlineStr">
         <is>
           <t>run-legal-diligence</t>
         </is>
       </c>
-      <c r="K289" s="15" t="inlineStr">
+      <c r="K301" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="290" ht="90" customHeight="1" s="12">
-      <c r="A290" s="15" t="inlineStr"/>
-      <c r="B290" s="15" t="inlineStr">
+    <row r="302" ht="90" customHeight="1" s="12">
+      <c r="A302" s="15" t="inlineStr"/>
+      <c r="B302" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C290" s="15" t="inlineStr">
+      <c r="C302" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D290" s="16">
+      <c r="D302" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
         <v/>
       </c>
-      <c r="E290" s="15" t="inlineStr">
+      <c r="E302" s="15" t="inlineStr">
         <is>
           <t>Coordinate legal diligence document indexing, issue tracking, counsel questions, and showstopper-risk review support without providing legal advice.</t>
         </is>
       </c>
-      <c r="F290" s="16">
+      <c r="F302" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G290" s="15" t="inlineStr"/>
-      <c r="H290" s="16">
+      <c r="G302" s="15" t="inlineStr"/>
+      <c r="H302" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (style_guide)")</f>
         <v/>
       </c>
-      <c r="I290" s="15" t="inlineStr">
+      <c r="I302" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -16007,48 +16592,48 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J290" s="15" t="inlineStr">
+      <c r="J302" s="15" t="inlineStr">
         <is>
           <t>run-legal-diligence</t>
         </is>
       </c>
-      <c r="K290" s="15" t="inlineStr">
+      <c r="K302" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="291" ht="90" customHeight="1" s="12">
-      <c r="A291" s="15" t="inlineStr"/>
-      <c r="B291" s="15" t="inlineStr">
+    <row r="303" ht="90" customHeight="1" s="12">
+      <c r="A303" s="15" t="inlineStr"/>
+      <c r="B303" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C291" s="15" t="inlineStr">
+      <c r="C303" s="15" t="inlineStr">
         <is>
           <t>Formal Diligence</t>
         </is>
       </c>
-      <c r="D291" s="16">
+      <c r="D303" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
         <v/>
       </c>
-      <c r="E291" s="15" t="inlineStr">
+      <c r="E303" s="15" t="inlineStr">
         <is>
           <t>Coordinate legal diligence document indexing, issue tracking, counsel questions, and showstopper-risk review support without providing legal advice.</t>
         </is>
       </c>
-      <c r="F291" s="16">
+      <c r="F303" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G291" s="15" t="inlineStr"/>
-      <c r="H291" s="16">
+      <c r="G303" s="15" t="inlineStr"/>
+      <c r="H303" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
         <v/>
       </c>
-      <c r="I291" s="15" t="inlineStr">
+      <c r="I303" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -16058,51 +16643,51 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J291" s="15" t="inlineStr">
+      <c r="J303" s="15" t="inlineStr">
         <is>
           <t>run-legal-diligence</t>
         </is>
       </c>
-      <c r="K291" s="15" t="inlineStr">
+      <c r="K303" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="292" ht="90" customHeight="1" s="12">
-      <c r="A292" s="15" t="inlineStr"/>
-      <c r="B292" s="15" t="inlineStr">
+    <row r="304" ht="90" customHeight="1" s="12">
+      <c r="A304" s="15" t="inlineStr"/>
+      <c r="B304" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C292" s="15" t="inlineStr">
+      <c r="C304" s="15" t="inlineStr">
         <is>
           <t>Contracts</t>
         </is>
       </c>
-      <c r="D292" s="16">
+      <c r="D304" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-investment-documents.md","Review Investment Documents")</f>
         <v/>
       </c>
-      <c r="E292" s="15" t="inlineStr">
+      <c r="E304" s="15" t="inlineStr">
         <is>
           <t>Coordinate post-term-sheet investment document review, disclosure-letter issues, counsel questions, and closing readiness notes without providing legal advice.</t>
         </is>
       </c>
-      <c r="F292" s="16">
+      <c r="F304" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G292" s="16">
+      <c r="G304" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/legal-diligence-coordination/SKILL.md","legal-diligence-coordination")</f>
         <v/>
       </c>
-      <c r="H292" s="16">
+      <c r="H304" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/investment-document-review-template.md","Investment Document Review Template (output_template, to investment_document_review_artifact_id)")</f>
         <v/>
       </c>
-      <c r="I292" s="15" t="inlineStr">
+      <c r="I304" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -16112,51 +16697,51 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J292" s="15" t="inlineStr">
+      <c r="J304" s="15" t="inlineStr">
         <is>
           <t>review-investment-documents</t>
         </is>
       </c>
-      <c r="K292" s="15" t="inlineStr">
+      <c r="K304" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="293" ht="90" customHeight="1" s="12">
-      <c r="A293" s="15" t="inlineStr"/>
-      <c r="B293" s="15" t="inlineStr">
+    <row r="305" ht="90" customHeight="1" s="12">
+      <c r="A305" s="15" t="inlineStr"/>
+      <c r="B305" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C293" s="15" t="inlineStr">
+      <c r="C305" s="15" t="inlineStr">
         <is>
           <t>Contracts</t>
         </is>
       </c>
-      <c r="D293" s="16">
+      <c r="D305" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-investment-documents.md","Review Investment Documents")</f>
         <v/>
       </c>
-      <c r="E293" s="15" t="inlineStr">
+      <c r="E305" s="15" t="inlineStr">
         <is>
           <t>Coordinate post-term-sheet investment document review, disclosure-letter issues, counsel questions, and closing readiness notes without providing legal advice.</t>
         </is>
       </c>
-      <c r="F293" s="16">
+      <c r="F305" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G293" s="16">
+      <c r="G305" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/closing-coordination-and-cp-tracking/SKILL.md","closing-coordination-and-cp-tracking")</f>
         <v/>
       </c>
-      <c r="H293" s="16">
+      <c r="H305" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/legal-diligence-guide.md","Legal Diligence Guide (methodology)")</f>
         <v/>
       </c>
-      <c r="I293" s="15" t="inlineStr">
+      <c r="I305" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -16166,51 +16751,51 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J293" s="15" t="inlineStr">
+      <c r="J305" s="15" t="inlineStr">
         <is>
           <t>review-investment-documents</t>
         </is>
       </c>
-      <c r="K293" s="15" t="inlineStr">
+      <c r="K305" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="294" ht="90" customHeight="1" s="12">
-      <c r="A294" s="15" t="inlineStr"/>
-      <c r="B294" s="15" t="inlineStr">
+    <row r="306" ht="90" customHeight="1" s="12">
+      <c r="A306" s="15" t="inlineStr"/>
+      <c r="B306" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C294" s="15" t="inlineStr">
+      <c r="C306" s="15" t="inlineStr">
         <is>
           <t>Contracts</t>
         </is>
       </c>
-      <c r="D294" s="16">
+      <c r="D306" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-investment-documents.md","Review Investment Documents")</f>
         <v/>
       </c>
-      <c r="E294" s="15" t="inlineStr">
+      <c r="E306" s="15" t="inlineStr">
         <is>
           <t>Coordinate post-term-sheet investment document review, disclosure-letter issues, counsel questions, and closing readiness notes without providing legal advice.</t>
         </is>
       </c>
-      <c r="F294" s="16">
+      <c r="F306" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G294" s="16">
+      <c r="G306" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
         <v/>
       </c>
-      <c r="H294" s="16">
+      <c r="H306" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (style_guide)")</f>
         <v/>
       </c>
-      <c r="I294" s="15" t="inlineStr">
+      <c r="I306" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -16220,48 +16805,48 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J294" s="15" t="inlineStr">
+      <c r="J306" s="15" t="inlineStr">
         <is>
           <t>review-investment-documents</t>
         </is>
       </c>
-      <c r="K294" s="15" t="inlineStr">
+      <c r="K306" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="295" ht="90" customHeight="1" s="12">
-      <c r="A295" s="15" t="inlineStr"/>
-      <c r="B295" s="15" t="inlineStr">
+    <row r="307" ht="90" customHeight="1" s="12">
+      <c r="A307" s="15" t="inlineStr"/>
+      <c r="B307" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C295" s="15" t="inlineStr">
+      <c r="C307" s="15" t="inlineStr">
         <is>
           <t>Contracts</t>
         </is>
       </c>
-      <c r="D295" s="16">
+      <c r="D307" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-investment-documents.md","Review Investment Documents")</f>
         <v/>
       </c>
-      <c r="E295" s="15" t="inlineStr">
+      <c r="E307" s="15" t="inlineStr">
         <is>
           <t>Coordinate post-term-sheet investment document review, disclosure-letter issues, counsel questions, and closing readiness notes without providing legal advice.</t>
         </is>
       </c>
-      <c r="F295" s="16">
+      <c r="F307" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G295" s="15" t="inlineStr"/>
-      <c r="H295" s="16">
+      <c r="G307" s="15" t="inlineStr"/>
+      <c r="H307" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
         <v/>
       </c>
-      <c r="I295" s="15" t="inlineStr">
+      <c r="I307" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -16271,51 +16856,51 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J295" s="15" t="inlineStr">
+      <c r="J307" s="15" t="inlineStr">
         <is>
           <t>review-investment-documents</t>
         </is>
       </c>
-      <c r="K295" s="15" t="inlineStr">
+      <c r="K307" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="296" ht="90" customHeight="1" s="12">
-      <c r="A296" s="15" t="inlineStr"/>
-      <c r="B296" s="15" t="inlineStr">
+    <row r="308" ht="90" customHeight="1" s="12">
+      <c r="A308" s="15" t="inlineStr"/>
+      <c r="B308" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C296" s="15" t="inlineStr">
+      <c r="C308" s="15" t="inlineStr">
         <is>
           <t>Closing</t>
         </is>
       </c>
-      <c r="D296" s="16">
+      <c r="D308" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/manage-closing-checklist.md","Manage Closing Checklist")</f>
         <v/>
       </c>
-      <c r="E296" s="15" t="inlineStr">
+      <c r="E308" s="15" t="inlineStr">
         <is>
           <t>Manage Closing Checklist for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F296" s="16">
+      <c r="F308" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G296" s="16">
+      <c r="G308" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
         <v/>
       </c>
-      <c r="H296" s="16">
+      <c r="H308" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/closing-checklist.md","Closing Checklist (output_template, to closing_checklist_artifact_id)")</f>
         <v/>
       </c>
-      <c r="I296" s="15" t="inlineStr">
+      <c r="I308" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -16325,51 +16910,51 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J296" s="15" t="inlineStr">
+      <c r="J308" s="15" t="inlineStr">
         <is>
           <t>manage-closing-checklist</t>
         </is>
       </c>
-      <c r="K296" s="15" t="inlineStr">
+      <c r="K308" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="297" ht="90" customHeight="1" s="12">
-      <c r="A297" s="15" t="inlineStr"/>
-      <c r="B297" s="15" t="inlineStr">
+    <row r="309" ht="90" customHeight="1" s="12">
+      <c r="A309" s="15" t="inlineStr"/>
+      <c r="B309" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C297" s="15" t="inlineStr">
+      <c r="C309" s="15" t="inlineStr">
         <is>
           <t>Closing</t>
         </is>
       </c>
-      <c r="D297" s="16">
+      <c r="D309" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/manage-closing-checklist.md","Manage Closing Checklist")</f>
         <v/>
       </c>
-      <c r="E297" s="15" t="inlineStr">
+      <c r="E309" s="15" t="inlineStr">
         <is>
           <t>Manage Closing Checklist for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F297" s="16">
+      <c r="F309" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G297" s="16">
+      <c r="G309" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/closing-coordination-and-cp-tracking/SKILL.md","closing-coordination-and-cp-tracking")</f>
         <v/>
       </c>
-      <c r="H297" s="16">
+      <c r="H309" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/legal-diligence-guide.md","Legal Diligence Guide (methodology)")</f>
         <v/>
       </c>
-      <c r="I297" s="15" t="inlineStr">
+      <c r="I309" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -16379,51 +16964,51 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J297" s="15" t="inlineStr">
+      <c r="J309" s="15" t="inlineStr">
         <is>
           <t>manage-closing-checklist</t>
         </is>
       </c>
-      <c r="K297" s="15" t="inlineStr">
+      <c r="K309" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="298" ht="90" customHeight="1" s="12">
-      <c r="A298" s="15" t="inlineStr"/>
-      <c r="B298" s="15" t="inlineStr">
+    <row r="310" ht="90" customHeight="1" s="12">
+      <c r="A310" s="15" t="inlineStr"/>
+      <c r="B310" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C298" s="15" t="inlineStr">
+      <c r="C310" s="15" t="inlineStr">
         <is>
           <t>Closing</t>
         </is>
       </c>
-      <c r="D298" s="16">
+      <c r="D310" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/manage-closing-checklist.md","Manage Closing Checklist")</f>
         <v/>
       </c>
-      <c r="E298" s="15" t="inlineStr">
+      <c r="E310" s="15" t="inlineStr">
         <is>
           <t>Manage Closing Checklist for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F298" s="16">
+      <c r="F310" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G298" s="16">
+      <c r="G310" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-task-and-next-step-generation/SKILL.md","vc-task-and-next-step-generation")</f>
         <v/>
       </c>
-      <c r="H298" s="16">
+      <c r="H310" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
         <v/>
       </c>
-      <c r="I298" s="15" t="inlineStr">
+      <c r="I310" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -16433,51 +17018,51 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J298" s="15" t="inlineStr">
+      <c r="J310" s="15" t="inlineStr">
         <is>
           <t>manage-closing-checklist</t>
         </is>
       </c>
-      <c r="K298" s="15" t="inlineStr">
+      <c r="K310" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="299" ht="90" customHeight="1" s="12">
-      <c r="A299" s="15" t="inlineStr"/>
-      <c r="B299" s="15" t="inlineStr">
+    <row r="311" ht="90" customHeight="1" s="12">
+      <c r="A311" s="15" t="inlineStr"/>
+      <c r="B311" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C299" s="15" t="inlineStr">
+      <c r="C311" s="15" t="inlineStr">
         <is>
           <t>Closing</t>
         </is>
       </c>
-      <c r="D299" s="16">
+      <c r="D311" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/verify-conditions-precedent.md","Verify Conditions Precedent")</f>
         <v/>
       </c>
-      <c r="E299" s="15" t="inlineStr">
+      <c r="E311" s="15" t="inlineStr">
         <is>
           <t>Verify Conditions Precedent for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F299" s="16">
+      <c r="F311" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G299" s="16">
+      <c r="G311" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
         <v/>
       </c>
-      <c r="H299" s="16">
+      <c r="H311" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/conditions-precedent-tracker-template.md","Conditions Precedent Tracker Template (output_template, to conditions_precedent_verification_artifact_id)")</f>
         <v/>
       </c>
-      <c r="I299" s="15" t="inlineStr">
+      <c r="I311" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -16487,51 +17072,51 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J299" s="15" t="inlineStr">
+      <c r="J311" s="15" t="inlineStr">
         <is>
           <t>verify-conditions-precedent</t>
         </is>
       </c>
-      <c r="K299" s="15" t="inlineStr">
+      <c r="K311" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="300" ht="90" customHeight="1" s="12">
-      <c r="A300" s="15" t="inlineStr"/>
-      <c r="B300" s="15" t="inlineStr">
+    <row r="312" ht="90" customHeight="1" s="12">
+      <c r="A312" s="15" t="inlineStr"/>
+      <c r="B312" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C300" s="15" t="inlineStr">
+      <c r="C312" s="15" t="inlineStr">
         <is>
           <t>Closing</t>
         </is>
       </c>
-      <c r="D300" s="16">
+      <c r="D312" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/verify-conditions-precedent.md","Verify Conditions Precedent")</f>
         <v/>
       </c>
-      <c r="E300" s="15" t="inlineStr">
+      <c r="E312" s="15" t="inlineStr">
         <is>
           <t>Verify Conditions Precedent for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F300" s="16">
+      <c r="F312" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G300" s="16">
+      <c r="G312" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/closing-coordination-and-cp-tracking/SKILL.md","closing-coordination-and-cp-tracking")</f>
         <v/>
       </c>
-      <c r="H300" s="16">
+      <c r="H312" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/legal-diligence-guide.md","Legal Diligence Guide (methodology)")</f>
         <v/>
       </c>
-      <c r="I300" s="15" t="inlineStr">
+      <c r="I312" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -16541,48 +17126,48 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J300" s="15" t="inlineStr">
+      <c r="J312" s="15" t="inlineStr">
         <is>
           <t>verify-conditions-precedent</t>
         </is>
       </c>
-      <c r="K300" s="15" t="inlineStr">
+      <c r="K312" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="301" ht="90" customHeight="1" s="12">
-      <c r="A301" s="15" t="inlineStr"/>
-      <c r="B301" s="15" t="inlineStr">
+    <row r="313" ht="90" customHeight="1" s="12">
+      <c r="A313" s="15" t="inlineStr"/>
+      <c r="B313" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C301" s="15" t="inlineStr">
+      <c r="C313" s="15" t="inlineStr">
         <is>
           <t>Closing</t>
         </is>
       </c>
-      <c r="D301" s="16">
+      <c r="D313" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/verify-conditions-precedent.md","Verify Conditions Precedent")</f>
         <v/>
       </c>
-      <c r="E301" s="15" t="inlineStr">
+      <c r="E313" s="15" t="inlineStr">
         <is>
           <t>Verify Conditions Precedent for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F301" s="16">
+      <c r="F313" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G301" s="15" t="inlineStr"/>
-      <c r="H301" s="16">
+      <c r="G313" s="15" t="inlineStr"/>
+      <c r="H313" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
         <v/>
       </c>
-      <c r="I301" s="15" t="inlineStr">
+      <c r="I313" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -16592,51 +17177,51 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J301" s="15" t="inlineStr">
+      <c r="J313" s="15" t="inlineStr">
         <is>
           <t>verify-conditions-precedent</t>
         </is>
       </c>
-      <c r="K301" s="15" t="inlineStr">
+      <c r="K313" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="302" ht="90" customHeight="1" s="12">
-      <c r="A302" s="15" t="inlineStr"/>
-      <c r="B302" s="15" t="inlineStr">
+    <row r="314" ht="90" customHeight="1" s="12">
+      <c r="A314" s="15" t="inlineStr"/>
+      <c r="B314" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C302" s="15" t="inlineStr">
+      <c r="C314" s="15" t="inlineStr">
         <is>
           <t>Closing</t>
         </is>
       </c>
-      <c r="D302" s="16">
+      <c r="D314" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/coordinate-capital-call-and-completion.md","Coordinate Capital Call And Completion")</f>
         <v/>
       </c>
-      <c r="E302" s="15" t="inlineStr">
+      <c r="E314" s="15" t="inlineStr">
         <is>
           <t>Track final closing administration, capital call status, funds transfer readiness, share-certificate receipt, and portfolio handoff triggers without initiating banking or legal completion actions.</t>
         </is>
       </c>
-      <c r="F302" s="16">
+      <c r="F314" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G302" s="16">
+      <c r="G314" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/closing-coordination-and-cp-tracking/SKILL.md","closing-coordination-and-cp-tracking")</f>
         <v/>
       </c>
-      <c r="H302" s="16">
+      <c r="H314" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/completion-tracker-template.md","Completion Tracker Template (output_template, to completion_tracker_artifact_id)")</f>
         <v/>
       </c>
-      <c r="I302" s="15" t="inlineStr">
+      <c r="I314" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -16646,51 +17231,51 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J302" s="15" t="inlineStr">
+      <c r="J314" s="15" t="inlineStr">
         <is>
           <t>coordinate-capital-call-and-completion</t>
         </is>
       </c>
-      <c r="K302" s="15" t="inlineStr">
+      <c r="K314" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="303" ht="90" customHeight="1" s="12">
-      <c r="A303" s="15" t="inlineStr"/>
-      <c r="B303" s="15" t="inlineStr">
+    <row r="315" ht="90" customHeight="1" s="12">
+      <c r="A315" s="15" t="inlineStr"/>
+      <c r="B315" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C303" s="15" t="inlineStr">
+      <c r="C315" s="15" t="inlineStr">
         <is>
           <t>Closing</t>
         </is>
       </c>
-      <c r="D303" s="16">
+      <c r="D315" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/coordinate-capital-call-and-completion.md","Coordinate Capital Call And Completion")</f>
         <v/>
       </c>
-      <c r="E303" s="15" t="inlineStr">
+      <c r="E315" s="15" t="inlineStr">
         <is>
           <t>Track final closing administration, capital call status, funds transfer readiness, share-certificate receipt, and portfolio handoff triggers without initiating banking or legal completion actions.</t>
         </is>
       </c>
-      <c r="F303" s="16">
+      <c r="F315" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G303" s="16">
+      <c r="G315" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-task-and-next-step-generation/SKILL.md","vc-task-and-next-step-generation")</f>
         <v/>
       </c>
-      <c r="H303" s="16">
+      <c r="H315" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (style_guide)")</f>
         <v/>
       </c>
-      <c r="I303" s="15" t="inlineStr">
+      <c r="I315" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -16700,51 +17285,51 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J303" s="15" t="inlineStr">
+      <c r="J315" s="15" t="inlineStr">
         <is>
           <t>coordinate-capital-call-and-completion</t>
         </is>
       </c>
-      <c r="K303" s="15" t="inlineStr">
+      <c r="K315" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="304" ht="90" customHeight="1" s="12">
-      <c r="A304" s="15" t="inlineStr"/>
-      <c r="B304" s="15" t="inlineStr">
+    <row r="316" ht="90" customHeight="1" s="12">
+      <c r="A316" s="15" t="inlineStr"/>
+      <c r="B316" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C304" s="15" t="inlineStr">
+      <c r="C316" s="15" t="inlineStr">
         <is>
           <t>Closing</t>
         </is>
       </c>
-      <c r="D304" s="16">
+      <c r="D316" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/coordinate-capital-call-and-completion.md","Coordinate Capital Call And Completion")</f>
         <v/>
       </c>
-      <c r="E304" s="15" t="inlineStr">
+      <c r="E316" s="15" t="inlineStr">
         <is>
           <t>Track final closing administration, capital call status, funds transfer readiness, share-certificate receipt, and portfolio handoff triggers without initiating banking or legal completion actions.</t>
         </is>
       </c>
-      <c r="F304" s="16">
+      <c r="F316" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G304" s="16">
+      <c r="G316" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
         <v/>
       </c>
-      <c r="H304" s="16">
+      <c r="H316" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
         <v/>
       </c>
-      <c r="I304" s="15" t="inlineStr">
+      <c r="I316" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -16754,51 +17339,51 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J304" s="15" t="inlineStr">
+      <c r="J316" s="15" t="inlineStr">
         <is>
           <t>coordinate-capital-call-and-completion</t>
         </is>
       </c>
-      <c r="K304" s="15" t="inlineStr">
+      <c r="K316" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="305" ht="90" customHeight="1" s="12">
-      <c r="A305" s="15" t="inlineStr"/>
-      <c r="B305" s="15" t="inlineStr">
+    <row r="317" ht="90" customHeight="1" s="12">
+      <c r="A317" s="15" t="inlineStr"/>
+      <c r="B317" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C305" s="15" t="inlineStr">
+      <c r="C317" s="15" t="inlineStr">
         <is>
           <t>Closing</t>
         </is>
       </c>
-      <c r="D305" s="16">
+      <c r="D317" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-portfolio-onboarding.md","Prepare Portfolio Onboarding")</f>
         <v/>
       </c>
-      <c r="E305" s="15" t="inlineStr">
+      <c r="E317" s="15" t="inlineStr">
         <is>
           <t>Prepare Portfolio Onboarding for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F305" s="16">
+      <c r="F317" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G305" s="16">
+      <c r="G317" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
         <v/>
       </c>
-      <c r="H305" s="16">
+      <c r="H317" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/portfolio-onboarding-plan-template.md","Portfolio Onboarding Plan Template (output_template, to portfolio_onboarding_plan_artifact_id)")</f>
         <v/>
       </c>
-      <c r="I305" s="15" t="inlineStr">
+      <c r="I317" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -16808,51 +17393,51 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J305" s="15" t="inlineStr">
+      <c r="J317" s="15" t="inlineStr">
         <is>
           <t>prepare-portfolio-onboarding</t>
         </is>
       </c>
-      <c r="K305" s="15" t="inlineStr">
+      <c r="K317" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="306" ht="90" customHeight="1" s="12">
-      <c r="A306" s="15" t="inlineStr"/>
-      <c r="B306" s="15" t="inlineStr">
+    <row r="318" ht="90" customHeight="1" s="12">
+      <c r="A318" s="15" t="inlineStr"/>
+      <c r="B318" s="15" t="inlineStr">
         <is>
           <t>Investment Management</t>
         </is>
       </c>
-      <c r="C306" s="15" t="inlineStr">
+      <c r="C318" s="15" t="inlineStr">
         <is>
           <t>Closing</t>
         </is>
       </c>
-      <c r="D306" s="16">
+      <c r="D318" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-portfolio-onboarding.md","Prepare Portfolio Onboarding")</f>
         <v/>
       </c>
-      <c r="E306" s="15" t="inlineStr">
+      <c r="E318" s="15" t="inlineStr">
         <is>
           <t>Prepare Portfolio Onboarding for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F306" s="16">
+      <c r="F318" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-legal-compliance-desk.md","Legal &amp; Compliance Desk")</f>
         <v/>
       </c>
-      <c r="G306" s="16">
+      <c r="G318" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/portfolio-onboarding-and-100-day-plan/SKILL.md","portfolio-onboarding-and-100-day-plan")</f>
         <v/>
       </c>
-      <c r="H306" s="16">
+      <c r="H318" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
         <v/>
       </c>
-      <c r="I306" s="15" t="inlineStr">
+      <c r="I318" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -16862,29 +17447,17 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J306" s="15" t="inlineStr">
+      <c r="J318" s="15" t="inlineStr">
         <is>
           <t>prepare-portfolio-onboarding</t>
         </is>
       </c>
-      <c r="K306" s="15" t="inlineStr">
+      <c r="K318" s="15" t="inlineStr">
         <is>
           <t>project_instance</t>
         </is>
       </c>
     </row>
-    <row r="307" ht="15.75" customHeight="1" s="12"/>
-    <row r="308" ht="15.75" customHeight="1" s="12"/>
-    <row r="309" ht="15.75" customHeight="1" s="12"/>
-    <row r="310" ht="15.75" customHeight="1" s="12"/>
-    <row r="311" ht="15.75" customHeight="1" s="12"/>
-    <row r="312" ht="15.75" customHeight="1" s="12"/>
-    <row r="313" ht="15.75" customHeight="1" s="12"/>
-    <row r="314" ht="15.75" customHeight="1" s="12"/>
-    <row r="315" ht="15.75" customHeight="1" s="12"/>
-    <row r="316" ht="15.75" customHeight="1" s="12"/>
-    <row r="317" ht="15.75" customHeight="1" s="12"/>
-    <row r="318" ht="15.75" customHeight="1" s="12"/>
     <row r="319" ht="15.75" customHeight="1" s="12"/>
     <row r="320" ht="15.75" customHeight="1" s="12"/>
     <row r="321" ht="15.75" customHeight="1" s="12"/>
@@ -17568,7 +18141,7 @@
     <row r="999" ht="15.75" customHeight="1" s="12"/>
     <row r="1000" ht="15.75" customHeight="1" s="12"/>
   </sheetData>
-  <autoFilter ref="A1:K306"/>
+  <autoFilter ref="A1:K318"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
   <tableParts count="1">
@@ -17691,10 +18264,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="15" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F3" s="15" t="n">
         <v>44</v>
@@ -17749,11 +18322,13 @@
 Manage Closing Checklist
 Prepare Deal Flow Agenda
 Prepare IC Agenda
+Prepare Initial LinkedIn Reachout
 Prepare Lead Gen Packet
 Prepare Meeting
 Prepare Outreach Draft Queue
 Prepare Partner Review Pack
 Prepare Portfolio Onboarding
+Prepare Second Reachout Email
 Prepare Sourcing IC Summary
 Prepare Team Review Pack
 Preview Affinity Pipeline Import
@@ -17765,10 +18340,12 @@
 Preview Slack Deal Context
 Promote Candidate to Deal Pipeline
 Record IC Decision
+Record LinkedIn Connection Attempt
 Request Founder Materials
 Review IC Memo
 Review Investment Documents
 Review Opportunity Status
+Review Outreach Outcome
 Review Portfolio Overlap
 Review Reddit Candidate Inbox
 Review Source Errors and Spend
@@ -17951,27 +18528,94 @@
     <row r="8" ht="75" customHeight="1" s="12">
       <c r="A8" s="15" t="inlineStr"/>
       <c r="B8" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-sourcing-dedupe-and-novelty-check/SKILL.md","vc-sourcing-dedupe-and-novelty-check")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/founder-outreach-and-intro-paths/SKILL.md","founder-outreach-and-intro-paths")</f>
         <v/>
       </c>
       <c r="C8" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>5</v>
       </c>
       <c r="E8" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>Origination Scout
+Sourcing Operator</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Prepare Initial LinkedIn Reachout
+Prepare Outreach Draft Queue
+Prepare Second Reachout Email
+Record LinkedIn Connection Attempt
+Source Thesis Targets</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="75" customHeight="1" s="12">
+      <c r="A9" s="15" t="inlineStr"/>
+      <c r="B9" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-outreach-draft-queue/SKILL.md","vc-outreach-draft-queue")</f>
+        <v/>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="15" t="n">
+      <c r="E9" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>Sourcing Operator</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>Prepare Initial LinkedIn Reachout
+Prepare Outreach Draft Queue
+Prepare Second Reachout Email
+Record LinkedIn Connection Attempt
+Review Outreach Outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="75" customHeight="1" s="12">
+      <c r="A10" s="15" t="inlineStr"/>
+      <c r="B10" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-sourcing-dedupe-and-novelty-check/SKILL.md","vc-sourcing-dedupe-and-novelty-check")</f>
+        <v/>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>Sourcing Operator</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="H10" s="15" t="inlineStr">
         <is>
           <t>Enrich Sourcing Candidates
 Ingest Manual Sourcing Tip
@@ -17981,25 +18625,25 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="120" customHeight="1" s="12">
-      <c r="A9" s="15" t="inlineStr"/>
-      <c r="B9" s="16">
+    <row r="11" ht="120" customHeight="1" s="12">
+      <c r="A11" s="15" t="inlineStr"/>
+      <c r="B11" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/company-research-and-enrichment/SKILL.md","company-research-and-enrichment")</f>
         <v/>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C11" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D11" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E11" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="F11" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>Dealflow Concierge
 Diligence Analyst
@@ -18011,7 +18655,7 @@
 Sourcing Operator</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr">
         <is>
           <t>Capture Opportunity Intake
 Prepare Lead Gen Packet
@@ -18020,31 +18664,31 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1" s="12">
-      <c r="A10" s="15" t="inlineStr"/>
-      <c r="B10" s="16">
+    <row r="12" ht="60" customHeight="1" s="12">
+      <c r="A12" s="15" t="inlineStr"/>
+      <c r="B12" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/ic-memo-assembly/SKILL.md","ic-memo-assembly")</f>
         <v/>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C12" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D12" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E12" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="15" t="n">
+      <c r="F12" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="15" t="inlineStr">
+      <c r="G12" s="15" t="inlineStr">
         <is>
           <t>Diligence Analyst
 IC Prep Producer</t>
         </is>
       </c>
-      <c r="H10" s="15" t="inlineStr">
+      <c r="H12" s="15" t="inlineStr">
         <is>
           <t>Create IC Memo
 Prepare Partner Review Pack
@@ -18053,30 +18697,30 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1" s="12">
-      <c r="A11" s="15" t="inlineStr"/>
-      <c r="B11" s="16">
+    <row r="13" ht="60" customHeight="1" s="12">
+      <c r="A13" s="15" t="inlineStr"/>
+      <c r="B13" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/ic-risk-checklist-and-decision-log/SKILL.md","ic-risk-checklist-and-decision-log")</f>
         <v/>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C13" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D13" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E13" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="15" t="n">
+      <c r="F13" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G13" s="15" t="inlineStr">
         <is>
           <t>IC Prep Producer</t>
         </is>
       </c>
-      <c r="H11" s="15" t="inlineStr">
+      <c r="H13" s="15" t="inlineStr">
         <is>
           <t>Create IC Memo
 Prepare IC Agenda
@@ -18085,32 +18729,32 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="45" customHeight="1" s="12">
-      <c r="A12" s="15" t="inlineStr"/>
-      <c r="B12" s="16">
+    <row r="14" ht="45" customHeight="1" s="12">
+      <c r="A14" s="15" t="inlineStr"/>
+      <c r="B14" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/deal-room-setup-and-source-ingestion/SKILL.md","deal-room-setup-and-source-ingestion")</f>
         <v/>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C14" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D14" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="E14" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="15" t="n">
+      <c r="F14" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t>Deal Pipeline Setup Guide
 Dealflow Concierge
 Sourcing Operator</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="H14" s="15" t="inlineStr">
         <is>
           <t>Capture Opportunity Intake
 Import Affinity Deal Pipeline Seed
@@ -18118,31 +18762,31 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="45" customHeight="1" s="12">
-      <c r="A13" s="15" t="inlineStr"/>
-      <c r="B13" s="16">
+    <row r="15" ht="45" customHeight="1" s="12">
+      <c r="A15" s="15" t="inlineStr"/>
+      <c r="B15" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/meeting-prep-and-summary/SKILL.md","meeting-prep-and-summary")</f>
         <v/>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C15" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D15" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E15" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="15" t="n">
+      <c r="F15" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="15" t="inlineStr">
+      <c r="G15" s="15" t="inlineStr">
         <is>
           <t>IC Prep Producer
 Meeting Operator</t>
         </is>
       </c>
-      <c r="H13" s="15" t="inlineStr">
+      <c r="H15" s="15" t="inlineStr">
         <is>
           <t>Prepare IC Agenda
 Prepare Meeting
@@ -18150,31 +18794,31 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="45" customHeight="1" s="12">
-      <c r="A14" s="15" t="inlineStr"/>
-      <c r="B14" s="16">
+    <row r="16" ht="45" customHeight="1" s="12">
+      <c r="A16" s="15" t="inlineStr"/>
+      <c r="B16" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-sync-read/SKILL.md","vc-affinity-sync-read")</f>
         <v/>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C16" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D16" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="15" t="n">
+      <c r="E16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="15" t="n">
+      <c r="F16" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="15" t="inlineStr">
+      <c r="G16" s="15" t="inlineStr">
         <is>
           <t>Deal Pipeline Setup Guide
 Integration Operator</t>
         </is>
       </c>
-      <c r="H14" s="15" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>Import Affinity Deal Pipeline Seed
 Preview Affinity Pipeline Import
@@ -18182,31 +18826,31 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="45" customHeight="1" s="12">
-      <c r="A15" s="15" t="inlineStr"/>
-      <c r="B15" s="16">
+    <row r="17" ht="45" customHeight="1" s="12">
+      <c r="A17" s="15" t="inlineStr"/>
+      <c r="B17" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-companies-house-sourcing/SKILL.md","vc-companies-house-sourcing")</f>
         <v/>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C17" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D17" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="E17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="15" t="n">
+      <c r="F17" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="G17" s="15" t="inlineStr">
         <is>
           <t>Integration Operator
 Sourcing Operator</t>
         </is>
       </c>
-      <c r="H15" s="15" t="inlineStr">
+      <c r="H17" s="15" t="inlineStr">
         <is>
           <t>Configure Companies House Public Register Preview
 Discover Companies House Candidates
@@ -18214,31 +18858,31 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="45" customHeight="1" s="12">
-      <c r="A16" s="15" t="inlineStr"/>
-      <c r="B16" s="16">
+    <row r="18" ht="45" customHeight="1" s="12">
+      <c r="A18" s="15" t="inlineStr"/>
+      <c r="B18" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-sync-write/SKILL.md","vc-notion-sync-write")</f>
         <v/>
       </c>
-      <c r="C16" s="15" t="n">
+      <c r="C18" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D18" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="15" t="n">
+      <c r="E18" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="15" t="n">
+      <c r="F18" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G16" s="15" t="inlineStr">
+      <c r="G18" s="15" t="inlineStr">
         <is>
           <t>Integration Operator
 Sourcing Operator</t>
         </is>
       </c>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>Draft Notion Update Proposals
 Set Up Notion for Deal Pipelines
@@ -18246,75 +18890,14 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" s="12">
-      <c r="A17" s="15" t="inlineStr"/>
-      <c r="B17" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/deal-terms-analysis/SKILL.md","deal-terms-analysis")</f>
-        <v/>
-      </c>
-      <c r="C17" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="15" t="inlineStr">
-        <is>
-          <t>Legal &amp; Compliance Desk</t>
-        </is>
-      </c>
-      <c r="H17" s="15" t="inlineStr">
-        <is>
-          <t>Analyze Deal Terms
-Track Term Sheet Negotiation</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1" s="12">
-      <c r="A18" s="15" t="inlineStr"/>
-      <c r="B18" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/founder-outreach-and-intro-paths/SKILL.md","founder-outreach-and-intro-paths")</f>
-        <v/>
-      </c>
-      <c r="C18" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="15" t="inlineStr">
-        <is>
-          <t>Origination Scout
-Sourcing Operator</t>
-        </is>
-      </c>
-      <c r="H18" s="15" t="inlineStr">
-        <is>
-          <t>Prepare Outreach Draft Queue
-Source Thesis Targets</t>
-        </is>
-      </c>
-    </row>
     <row r="19" ht="30" customHeight="1" s="12">
       <c r="A19" s="15" t="inlineStr"/>
       <c r="B19" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/investment-diligence-question-framework/SKILL.md","investment-diligence-question-framework")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/deal-terms-analysis/SKILL.md","deal-terms-analysis")</f>
         <v/>
       </c>
       <c r="C19" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>2</v>
@@ -18327,36 +18910,66 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
+          <t>Legal &amp; Compliance Desk</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>Analyze Deal Terms
+Track Term Sheet Negotiation</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="12">
+      <c r="A20" s="15" t="inlineStr"/>
+      <c r="B20" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/investment-diligence-question-framework/SKILL.md","investment-diligence-question-framework")</f>
+        <v/>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
           <t>Diligence Analyst
 Evaluation Analyst</t>
         </is>
       </c>
-      <c r="H19" s="15" t="inlineStr">
+      <c r="H20" s="15" t="inlineStr">
         <is>
           <t>Generate Diligence Questions
 Run Opportunity Evaluation</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="75" customHeight="1" s="12">
-      <c r="A20" s="15" t="inlineStr"/>
-      <c r="B20" s="16">
+    <row r="21" ht="75" customHeight="1" s="12">
+      <c r="A21" s="15" t="inlineStr"/>
+      <c r="B21" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/investment-screening-framework/SKILL.md","investment-screening-framework")</f>
         <v/>
       </c>
-      <c r="C20" s="15" t="n">
+      <c r="C21" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D21" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="E20" s="15" t="n">
+      <c r="E21" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="15" t="n">
+      <c r="F21" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="15" t="inlineStr">
+      <c r="G21" s="15" t="inlineStr">
         <is>
           <t>Dealflow Concierge
 First Look Analyst
@@ -18365,139 +18978,108 @@
 Sourcing Operator</t>
         </is>
       </c>
-      <c r="H20" s="15" t="inlineStr">
+      <c r="H21" s="15" t="inlineStr">
         <is>
           <t>Run Investment Fit Screen
 Screen Active Sourcing Candidates</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1" s="12">
-      <c r="A21" s="15" t="inlineStr"/>
-      <c r="B21" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/legal-diligence-coordination/SKILL.md","legal-diligence-coordination")</f>
-        <v/>
-      </c>
-      <c r="C21" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="15" t="inlineStr">
-        <is>
-          <t>Legal &amp; Compliance Desk</t>
-        </is>
-      </c>
-      <c r="H21" s="15" t="inlineStr">
-        <is>
-          <t>Review Investment Documents
-Run Legal Diligence</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="12">
       <c r="A22" s="15" t="inlineStr"/>
       <c r="B22" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/pitch-deck-explainer/SKILL.md","pitch-deck-explainer")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/legal-diligence-coordination/SKILL.md","legal-diligence-coordination")</f>
         <v/>
       </c>
       <c r="C22" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="15" t="inlineStr">
         <is>
-          <t>Dealflow Concierge
-Meeting Operator</t>
+          <t>Legal &amp; Compliance Desk</t>
         </is>
       </c>
       <c r="H22" s="15" t="inlineStr">
         <is>
-          <t>Capture Opportunity Intake
-Prepare Meeting</t>
+          <t>Review Investment Documents
+Run Legal Diligence</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" s="12">
       <c r="A23" s="15" t="inlineStr"/>
       <c r="B23" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/team-and-hiring-assessment/SKILL.md","team-and-hiring-assessment")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/pitch-deck-explainer/SKILL.md","pitch-deck-explainer")</f>
         <v/>
       </c>
       <c r="C23" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="15" t="inlineStr">
         <is>
-          <t>Diligence Analyst</t>
+          <t>Dealflow Concierge
+Meeting Operator</t>
         </is>
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>Run Founder Evaluation
-Run Technical DD</t>
+          <t>Capture Opportunity Intake
+Prepare Meeting</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="12">
       <c r="A24" s="15" t="inlineStr"/>
       <c r="B24" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-discovery/SKILL.md","vc-affinity-discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/team-and-hiring-assessment/SKILL.md","team-and-hiring-assessment")</f>
         <v/>
       </c>
       <c r="C24" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E24" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="15" t="n">
-        <v>2</v>
-      </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
-          <t>Deal Pipeline Setup Guide
-Integration Operator</t>
+          <t>Diligence Analyst</t>
         </is>
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>Explore Affinity Lists and Stages
-Set Up Affinity for Deal Pipelines</t>
+          <t>Run Founder Evaluation
+Run Technical DD</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="12">
       <c r="A25" s="15" t="inlineStr"/>
       <c r="B25" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-sync-write/SKILL.md","vc-affinity-sync-write")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-discovery/SKILL.md","vc-affinity-discovery")</f>
         <v/>
       </c>
       <c r="C25" s="15" t="n">
@@ -18520,7 +19102,7 @@
       </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
-          <t>Draft Affinity Write-Back Proposals
+          <t>Explore Affinity Lists and Stages
 Set Up Affinity for Deal Pipelines</t>
         </is>
       </c>
@@ -18528,11 +19110,11 @@
     <row r="26" ht="30" customHeight="1" s="12">
       <c r="A26" s="15" t="inlineStr"/>
       <c r="B26" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-apify-discovery/SKILL.md","vc-apify-discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-sync-write/SKILL.md","vc-affinity-sync-write")</f>
         <v/>
       </c>
       <c r="C26" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="15" t="n">
         <v>2</v>
@@ -18545,20 +19127,21 @@
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
-          <t>Integration Operator</t>
+          <t>Deal Pipeline Setup Guide
+Integration Operator</t>
         </is>
       </c>
       <c r="H26" s="15" t="inlineStr">
         <is>
-          <t>Explore Apify Origination Sources
-Set Up Apify for Origination</t>
+          <t>Draft Affinity Write-Back Proposals
+Set Up Affinity for Deal Pipelines</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="12">
       <c r="A27" s="15" t="inlineStr"/>
       <c r="B27" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-apify-sync-read/SKILL.md","vc-apify-sync-read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-apify-discovery/SKILL.md","vc-apify-discovery")</f>
         <v/>
       </c>
       <c r="C27" s="15" t="n">
@@ -18580,7 +19163,7 @@
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>Preview Apify Origination Results
+          <t>Explore Apify Origination Sources
 Set Up Apify for Origination</t>
         </is>
       </c>
@@ -18588,7 +19171,7 @@
     <row r="28" ht="30" customHeight="1" s="12">
       <c r="A28" s="15" t="inlineStr"/>
       <c r="B28" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-companies-house-sync-read/SKILL.md","vc-companies-house-sync-read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-apify-sync-read/SKILL.md","vc-apify-sync-read")</f>
         <v/>
       </c>
       <c r="C28" s="15" t="n">
@@ -18610,15 +19193,15 @@
       </c>
       <c r="H28" s="15" t="inlineStr">
         <is>
-          <t>Configure Companies House Public Register Preview
-Preview Companies House Public Register Results</t>
+          <t>Preview Apify Origination Results
+Set Up Apify for Origination</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" s="12">
       <c r="A29" s="15" t="inlineStr"/>
       <c r="B29" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-discovery/SKILL.md","vc-google-drive-discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-companies-house-sync-read/SKILL.md","vc-companies-house-sync-read")</f>
         <v/>
       </c>
       <c r="C29" s="15" t="n">
@@ -18640,15 +19223,15 @@
       </c>
       <c r="H29" s="15" t="inlineStr">
         <is>
-          <t>Explore Google Drive Sources
-Set Up Google Drive for Deal Pipelines</t>
+          <t>Configure Companies House Public Register Preview
+Preview Companies House Public Register Results</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" s="12">
       <c r="A30" s="15" t="inlineStr"/>
       <c r="B30" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-sync-read/SKILL.md","vc-google-drive-sync-read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-discovery/SKILL.md","vc-google-drive-discovery")</f>
         <v/>
       </c>
       <c r="C30" s="15" t="n">
@@ -18670,7 +19253,7 @@
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>Preview Google Drive Context
+          <t>Explore Google Drive Sources
 Set Up Google Drive for Deal Pipelines</t>
         </is>
       </c>
@@ -18678,7 +19261,7 @@
     <row r="31" ht="30" customHeight="1" s="12">
       <c r="A31" s="15" t="inlineStr"/>
       <c r="B31" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-sync-write/SKILL.md","vc-google-drive-sync-write")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-sync-read/SKILL.md","vc-google-drive-sync-read")</f>
         <v/>
       </c>
       <c r="C31" s="15" t="n">
@@ -18700,7 +19283,7 @@
       </c>
       <c r="H31" s="15" t="inlineStr">
         <is>
-          <t>Draft Google Drive File Proposals
+          <t>Preview Google Drive Context
 Set Up Google Drive for Deal Pipelines</t>
         </is>
       </c>
@@ -18708,7 +19291,7 @@
     <row r="32" ht="30" customHeight="1" s="12">
       <c r="A32" s="15" t="inlineStr"/>
       <c r="B32" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-harmonic-discovery/SKILL.md","vc-harmonic-discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-sync-write/SKILL.md","vc-google-drive-sync-write")</f>
         <v/>
       </c>
       <c r="C32" s="15" t="n">
@@ -18730,15 +19313,15 @@
       </c>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>Explore Harmonic Source Scopes
-Set Up Harmonic for Deal Pipelines</t>
+          <t>Draft Google Drive File Proposals
+Set Up Google Drive for Deal Pipelines</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" s="12">
       <c r="A33" s="15" t="inlineStr"/>
       <c r="B33" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-harmonic-sync-read/SKILL.md","vc-harmonic-sync-read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-harmonic-discovery/SKILL.md","vc-harmonic-discovery")</f>
         <v/>
       </c>
       <c r="C33" s="15" t="n">
@@ -18760,7 +19343,7 @@
       </c>
       <c r="H33" s="15" t="inlineStr">
         <is>
-          <t>Preview Harmonic Search Results
+          <t>Explore Harmonic Source Scopes
 Set Up Harmonic for Deal Pipelines</t>
         </is>
       </c>
@@ -18768,7 +19351,7 @@
     <row r="34" ht="30" customHeight="1" s="12">
       <c r="A34" s="15" t="inlineStr"/>
       <c r="B34" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-discovery/SKILL.md","vc-notion-discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-harmonic-sync-read/SKILL.md","vc-harmonic-sync-read")</f>
         <v/>
       </c>
       <c r="C34" s="15" t="n">
@@ -18790,15 +19373,15 @@
       </c>
       <c r="H34" s="15" t="inlineStr">
         <is>
-          <t>Explore Notion Pages and Databases
-Set Up Notion for Deal Pipelines</t>
+          <t>Preview Harmonic Search Results
+Set Up Harmonic for Deal Pipelines</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1" s="12">
       <c r="A35" s="15" t="inlineStr"/>
       <c r="B35" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-sync-read/SKILL.md","vc-notion-sync-read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-discovery/SKILL.md","vc-notion-discovery")</f>
         <v/>
       </c>
       <c r="C35" s="15" t="n">
@@ -18820,7 +19403,7 @@
       </c>
       <c r="H35" s="15" t="inlineStr">
         <is>
-          <t>Preview Notion Context
+          <t>Explore Notion Pages and Databases
 Set Up Notion for Deal Pipelines</t>
         </is>
       </c>
@@ -18828,7 +19411,7 @@
     <row r="36" ht="30" customHeight="1" s="12">
       <c r="A36" s="15" t="inlineStr"/>
       <c r="B36" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-origination-pipeline-orchestration/SKILL.md","vc-origination-pipeline-orchestration")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-sync-read/SKILL.md","vc-notion-sync-read")</f>
         <v/>
       </c>
       <c r="C36" s="15" t="n">
@@ -18838,27 +19421,27 @@
         <v>2</v>
       </c>
       <c r="E36" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" s="15" t="inlineStr">
         <is>
-          <t>Sourcing Operator</t>
+          <t>Integration Operator</t>
         </is>
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>Configure Origination Pipeline
-Run VC Sourcing Pipeline</t>
+          <t>Preview Notion Context
+Set Up Notion for Deal Pipelines</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1" s="12">
       <c r="A37" s="15" t="inlineStr"/>
       <c r="B37" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-relationship-context-check/SKILL.md","vc-relationship-context-check")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-origination-deal-room-promotion/SKILL.md","vc-origination-deal-room-promotion")</f>
         <v/>
       </c>
       <c r="C37" s="15" t="n">
@@ -18868,10 +19451,10 @@
         <v>2</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
@@ -18880,15 +19463,15 @@
       </c>
       <c r="H37" s="15" t="inlineStr">
         <is>
-          <t>Check Affinity Relationship Context
-Review Portfolio Overlap</t>
+          <t>Promote Candidate to Deal Pipeline
+Review Outreach Outcome</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1" s="12">
       <c r="A38" s="15" t="inlineStr"/>
       <c r="B38" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-discovery/SKILL.md","vc-slack-discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-origination-pipeline-orchestration/SKILL.md","vc-origination-pipeline-orchestration")</f>
         <v/>
       </c>
       <c r="C38" s="15" t="n">
@@ -18898,27 +19481,27 @@
         <v>2</v>
       </c>
       <c r="E38" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38" s="15" t="inlineStr">
         <is>
-          <t>Integration Operator</t>
+          <t>Sourcing Operator</t>
         </is>
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>Explore Slack Channels for VC Context
-Set Up Slack for Deal Pipelines</t>
+          <t>Configure Origination Pipeline
+Run VC Sourcing Pipeline</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1" s="12">
       <c r="A39" s="15" t="inlineStr"/>
       <c r="B39" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-sync-read/SKILL.md","vc-slack-sync-read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-relationship-context-check/SKILL.md","vc-relationship-context-check")</f>
         <v/>
       </c>
       <c r="C39" s="15" t="n">
@@ -18928,27 +19511,27 @@
         <v>2</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39" s="15" t="inlineStr">
         <is>
-          <t>Integration Operator</t>
+          <t>Sourcing Operator</t>
         </is>
       </c>
       <c r="H39" s="15" t="inlineStr">
         <is>
-          <t>Preview Slack Deal Context
-Set Up Slack for Deal Pipelines</t>
+          <t>Check Affinity Relationship Context
+Review Portfolio Overlap</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1" s="12">
       <c r="A40" s="15" t="inlineStr"/>
       <c r="B40" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-sync-write/SKILL.md","vc-slack-sync-write")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-discovery/SKILL.md","vc-slack-discovery")</f>
         <v/>
       </c>
       <c r="C40" s="15" t="n">
@@ -18970,7 +19553,7 @@
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>Draft Slack Handoff Notifications
+          <t>Explore Slack Channels for VC Context
 Set Up Slack for Deal Pipelines</t>
         </is>
       </c>
@@ -18978,7 +19561,7 @@
     <row r="41" ht="30" customHeight="1" s="12">
       <c r="A41" s="15" t="inlineStr"/>
       <c r="B41" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-sourcing-verdict-and-screening/SKILL.md","vc-sourcing-verdict-and-screening")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-sync-read/SKILL.md","vc-slack-sync-read")</f>
         <v/>
       </c>
       <c r="C41" s="15" t="n">
@@ -18988,85 +19571,87 @@
         <v>2</v>
       </c>
       <c r="E41" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" s="15" t="inlineStr">
+        <is>
+          <t>Integration Operator</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="inlineStr">
+        <is>
+          <t>Preview Slack Deal Context
+Set Up Slack for Deal Pipelines</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1" s="12">
+      <c r="A42" s="15" t="inlineStr"/>
+      <c r="B42" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-sync-write/SKILL.md","vc-slack-sync-write")</f>
+        <v/>
+      </c>
+      <c r="C42" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F41" s="15" t="n">
+      <c r="D42" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="15" t="inlineStr">
+        <is>
+          <t>Integration Operator</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="inlineStr">
+        <is>
+          <t>Draft Slack Handoff Notifications
+Set Up Slack for Deal Pipelines</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1" s="12">
+      <c r="A43" s="15" t="inlineStr"/>
+      <c r="B43" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-sourcing-verdict-and-screening/SKILL.md","vc-sourcing-verdict-and-screening")</f>
+        <v/>
+      </c>
+      <c r="C43" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="15" t="inlineStr">
+      <c r="D43" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="15" t="inlineStr">
         <is>
           <t>Sourcing Operator</t>
         </is>
       </c>
-      <c r="H41" s="15" t="inlineStr">
+      <c r="H43" s="15" t="inlineStr">
         <is>
           <t>Score Sourcing Candidates
 Screen Active Sourcing Candidates</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1" s="12">
-      <c r="A42" s="15" t="inlineStr"/>
-      <c r="B42" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/commercial-diligence-workstream/SKILL.md","commercial-diligence-workstream")</f>
-        <v/>
-      </c>
-      <c r="C42" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="15" t="inlineStr">
-        <is>
-          <t>Diligence Analyst</t>
-        </is>
-      </c>
-      <c r="H42" s="15" t="inlineStr">
-        <is>
-          <t>Run Commercial DD</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1" s="12">
-      <c r="A43" s="15" t="inlineStr"/>
-      <c r="B43" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/commercial-evaluation-and-market-risk/SKILL.md","commercial-evaluation-and-market-risk")</f>
-        <v/>
-      </c>
-      <c r="C43" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="15" t="inlineStr">
-        <is>
-          <t>Evaluation Analyst</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="inlineStr">
-        <is>
-          <t>Run Commercial Evaluation</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1" s="12">
       <c r="A44" s="15" t="inlineStr"/>
       <c r="B44" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/financial-diligence-workstream/SKILL.md","financial-diligence-workstream")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/commercial-diligence-workstream/SKILL.md","commercial-diligence-workstream")</f>
         <v/>
       </c>
       <c r="C44" s="15" t="n">
@@ -19088,14 +19673,14 @@
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>Run Financial DD</t>
+          <t>Run Commercial DD</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1" s="12">
       <c r="A45" s="15" t="inlineStr"/>
       <c r="B45" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/financial-evaluation-and-financing-risk/SKILL.md","financial-evaluation-and-financing-risk")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/commercial-evaluation-and-market-risk/SKILL.md","commercial-evaluation-and-market-risk")</f>
         <v/>
       </c>
       <c r="C45" s="15" t="n">
@@ -19117,14 +19702,14 @@
       </c>
       <c r="H45" s="15" t="inlineStr">
         <is>
-          <t>Run Financial Evaluation</t>
+          <t>Run Commercial Evaluation</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1" s="12">
       <c r="A46" s="15" t="inlineStr"/>
       <c r="B46" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/founder-evaluation-and-reference-checking/SKILL.md","founder-evaluation-and-reference-checking")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/financial-diligence-workstream/SKILL.md","financial-diligence-workstream")</f>
         <v/>
       </c>
       <c r="C46" s="15" t="n">
@@ -19146,14 +19731,14 @@
       </c>
       <c r="H46" s="15" t="inlineStr">
         <is>
-          <t>Run Founder Evaluation</t>
+          <t>Run Financial DD</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1" s="12">
       <c r="A47" s="15" t="inlineStr"/>
       <c r="B47" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/founder-materials-request/SKILL.md","founder-materials-request")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/financial-evaluation-and-financing-risk/SKILL.md","financial-evaluation-and-financing-risk")</f>
         <v/>
       </c>
       <c r="C47" s="15" t="n">
@@ -19163,26 +19748,26 @@
         <v>1</v>
       </c>
       <c r="E47" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F47" s="15" t="n">
-        <v>1</v>
-      </c>
       <c r="G47" s="15" t="inlineStr">
         <is>
-          <t>Dealflow Concierge</t>
+          <t>Evaluation Analyst</t>
         </is>
       </c>
       <c r="H47" s="15" t="inlineStr">
         <is>
-          <t>Request Founder Materials</t>
+          <t>Run Financial Evaluation</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1" s="12">
       <c r="A48" s="15" t="inlineStr"/>
       <c r="B48" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/portfolio-onboarding-and-100-day-plan/SKILL.md","portfolio-onboarding-and-100-day-plan")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/founder-evaluation-and-reference-checking/SKILL.md","founder-evaluation-and-reference-checking")</f>
         <v/>
       </c>
       <c r="C48" s="15" t="n">
@@ -19199,19 +19784,19 @@
       </c>
       <c r="G48" s="15" t="inlineStr">
         <is>
-          <t>Legal &amp; Compliance Desk</t>
+          <t>Diligence Analyst</t>
         </is>
       </c>
       <c r="H48" s="15" t="inlineStr">
         <is>
-          <t>Prepare Portfolio Onboarding</t>
+          <t>Run Founder Evaluation</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1" s="12">
       <c r="A49" s="15" t="inlineStr"/>
       <c r="B49" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/team-evaluation-and-founder-risk/SKILL.md","team-evaluation-and-founder-risk")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/founder-materials-request/SKILL.md","founder-materials-request")</f>
         <v/>
       </c>
       <c r="C49" s="15" t="n">
@@ -19221,26 +19806,26 @@
         <v>1</v>
       </c>
       <c r="E49" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="15" t="n">
-        <v>0</v>
-      </c>
       <c r="G49" s="15" t="inlineStr">
         <is>
-          <t>Evaluation Analyst</t>
+          <t>Dealflow Concierge</t>
         </is>
       </c>
       <c r="H49" s="15" t="inlineStr">
         <is>
-          <t>Run Team Evaluation</t>
+          <t>Request Founder Materials</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1" s="12">
       <c r="A50" s="15" t="inlineStr"/>
       <c r="B50" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/technical-diligence-workstream/SKILL.md","technical-diligence-workstream")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/portfolio-onboarding-and-100-day-plan/SKILL.md","portfolio-onboarding-and-100-day-plan")</f>
         <v/>
       </c>
       <c r="C50" s="15" t="n">
@@ -19257,19 +19842,19 @@
       </c>
       <c r="G50" s="15" t="inlineStr">
         <is>
-          <t>Diligence Analyst</t>
+          <t>Legal &amp; Compliance Desk</t>
         </is>
       </c>
       <c r="H50" s="15" t="inlineStr">
         <is>
-          <t>Run Technical DD</t>
+          <t>Prepare Portfolio Onboarding</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1" s="12">
       <c r="A51" s="15" t="inlineStr"/>
       <c r="B51" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/technical-evaluation-and-product-risk/SKILL.md","technical-evaluation-and-product-risk")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/team-evaluation-and-founder-risk/SKILL.md","team-evaluation-and-founder-risk")</f>
         <v/>
       </c>
       <c r="C51" s="15" t="n">
@@ -19291,14 +19876,14 @@
       </c>
       <c r="H51" s="15" t="inlineStr">
         <is>
-          <t>Run Technical Evaluation</t>
+          <t>Run Team Evaluation</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1" s="12">
       <c r="A52" s="15" t="inlineStr"/>
       <c r="B52" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/term-sheet-negotiation-brief/SKILL.md","term-sheet-negotiation-brief")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/technical-diligence-workstream/SKILL.md","technical-diligence-workstream")</f>
         <v/>
       </c>
       <c r="C52" s="15" t="n">
@@ -19315,19 +19900,19 @@
       </c>
       <c r="G52" s="15" t="inlineStr">
         <is>
-          <t>Legal &amp; Compliance Desk</t>
+          <t>Diligence Analyst</t>
         </is>
       </c>
       <c r="H52" s="15" t="inlineStr">
         <is>
-          <t>Track Term Sheet Negotiation</t>
+          <t>Run Technical DD</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1" s="12">
       <c r="A53" s="15" t="inlineStr"/>
       <c r="B53" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-deal-room-import/SKILL.md","vc-affinity-deal-room-import")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/technical-evaluation-and-product-risk/SKILL.md","technical-evaluation-and-product-risk")</f>
         <v/>
       </c>
       <c r="C53" s="15" t="n">
@@ -19337,26 +19922,26 @@
         <v>1</v>
       </c>
       <c r="E53" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F53" s="15" t="n">
-        <v>1</v>
-      </c>
       <c r="G53" s="15" t="inlineStr">
         <is>
-          <t>Deal Pipeline Setup Guide</t>
+          <t>Evaluation Analyst</t>
         </is>
       </c>
       <c r="H53" s="15" t="inlineStr">
         <is>
-          <t>Import Affinity Deal Pipeline Seed</t>
+          <t>Run Technical Evaluation</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1" s="12">
       <c r="A54" s="15" t="inlineStr"/>
       <c r="B54" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-apify-linkedin-founder-discovery/SKILL.md","vc-apify-linkedin-founder-discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/term-sheet-negotiation-brief/SKILL.md","term-sheet-negotiation-brief")</f>
         <v/>
       </c>
       <c r="C54" s="15" t="n">
@@ -19366,26 +19951,26 @@
         <v>1</v>
       </c>
       <c r="E54" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F54" s="15" t="n">
-        <v>1</v>
-      </c>
       <c r="G54" s="15" t="inlineStr">
         <is>
-          <t>Sourcing Operator</t>
+          <t>Legal &amp; Compliance Desk</t>
         </is>
       </c>
       <c r="H54" s="15" t="inlineStr">
         <is>
-          <t>Discover LinkedIn Founder Candidates</t>
+          <t>Track Term Sheet Negotiation</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1" s="12">
       <c r="A55" s="15" t="inlineStr"/>
       <c r="B55" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-apify-x-founder-discovery/SKILL.md","vc-apify-x-founder-discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-deal-room-import/SKILL.md","vc-affinity-deal-room-import")</f>
         <v/>
       </c>
       <c r="C55" s="15" t="n">
@@ -19402,19 +19987,19 @@
       </c>
       <c r="G55" s="15" t="inlineStr">
         <is>
-          <t>Sourcing Operator</t>
+          <t>Deal Pipeline Setup Guide</t>
         </is>
       </c>
       <c r="H55" s="15" t="inlineStr">
         <is>
-          <t>Discover X Founder Signals</t>
+          <t>Import Affinity Deal Pipeline Seed</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1" s="12">
       <c r="A56" s="15" t="inlineStr"/>
       <c r="B56" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-github-builder-signal-discovery/SKILL.md","vc-github-builder-signal-discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-apify-linkedin-founder-discovery/SKILL.md","vc-apify-linkedin-founder-discovery")</f>
         <v/>
       </c>
       <c r="C56" s="15" t="n">
@@ -19436,14 +20021,14 @@
       </c>
       <c r="H56" s="15" t="inlineStr">
         <is>
-          <t>Discover GitHub Builder Signals</t>
+          <t>Discover LinkedIn Founder Candidates</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1" s="12">
       <c r="A57" s="15" t="inlineStr"/>
       <c r="B57" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-linkedin-query-spend-audit/SKILL.md","vc-linkedin-query-spend-audit")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-apify-x-founder-discovery/SKILL.md","vc-apify-x-founder-discovery")</f>
         <v/>
       </c>
       <c r="C57" s="15" t="n">
@@ -19465,14 +20050,14 @@
       </c>
       <c r="H57" s="15" t="inlineStr">
         <is>
-          <t>Audit LinkedIn Query Spend</t>
+          <t>Discover X Founder Signals</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1" s="12">
       <c r="A58" s="15" t="inlineStr"/>
       <c r="B58" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-manual-tip-ingestion/SKILL.md","vc-manual-tip-ingestion")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-github-builder-signal-discovery/SKILL.md","vc-github-builder-signal-discovery")</f>
         <v/>
       </c>
       <c r="C58" s="15" t="n">
@@ -19482,11 +20067,11 @@
         <v>1</v>
       </c>
       <c r="E58" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F58" s="15" t="n">
-        <v>0</v>
-      </c>
       <c r="G58" s="15" t="inlineStr">
         <is>
           <t>Sourcing Operator</t>
@@ -19494,14 +20079,14 @@
       </c>
       <c r="H58" s="15" t="inlineStr">
         <is>
-          <t>Ingest Manual Sourcing Tip</t>
+          <t>Discover GitHub Builder Signals</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1" s="12">
       <c r="A59" s="15" t="inlineStr"/>
       <c r="B59" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-origination-deal-room-promotion/SKILL.md","vc-origination-deal-room-promotion")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-linkedin-query-spend-audit/SKILL.md","vc-linkedin-query-spend-audit")</f>
         <v/>
       </c>
       <c r="C59" s="15" t="n">
@@ -19511,11 +20096,11 @@
         <v>1</v>
       </c>
       <c r="E59" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F59" s="15" t="n">
-        <v>0</v>
-      </c>
       <c r="G59" s="15" t="inlineStr">
         <is>
           <t>Sourcing Operator</t>
@@ -19523,14 +20108,14 @@
       </c>
       <c r="H59" s="15" t="inlineStr">
         <is>
-          <t>Promote Candidate to Deal Pipeline</t>
+          <t>Audit LinkedIn Query Spend</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1" s="12">
       <c r="A60" s="15" t="inlineStr"/>
       <c r="B60" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-origination-ic-summary-preparation/SKILL.md","vc-origination-ic-summary-preparation")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-manual-tip-ingestion/SKILL.md","vc-manual-tip-ingestion")</f>
         <v/>
       </c>
       <c r="C60" s="15" t="n">
@@ -19547,19 +20132,19 @@
       </c>
       <c r="G60" s="15" t="inlineStr">
         <is>
-          <t>IC Prep Producer</t>
+          <t>Sourcing Operator</t>
         </is>
       </c>
       <c r="H60" s="15" t="inlineStr">
         <is>
-          <t>Prepare Sourcing IC Summary</t>
+          <t>Ingest Manual Sourcing Tip</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1" s="12">
       <c r="A61" s="15" t="inlineStr"/>
       <c r="B61" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-outreach-draft-queue/SKILL.md","vc-outreach-draft-queue")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-origination-ic-summary-preparation/SKILL.md","vc-origination-ic-summary-preparation")</f>
         <v/>
       </c>
       <c r="C61" s="15" t="n">
@@ -19569,19 +20154,19 @@
         <v>1</v>
       </c>
       <c r="E61" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F61" s="15" t="n">
-        <v>1</v>
-      </c>
       <c r="G61" s="15" t="inlineStr">
         <is>
-          <t>Sourcing Operator</t>
+          <t>IC Prep Producer</t>
         </is>
       </c>
       <c r="H61" s="15" t="inlineStr">
         <is>
-          <t>Prepare Outreach Draft Queue</t>
+          <t>Prepare Sourcing IC Summary</t>
         </is>
       </c>
     </row>
@@ -23258,7 +23843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D219"/>
+  <dimension ref="A1:D231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="12" min="1" max="1"/>
@@ -27039,15 +27624,15 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>Review Backlog</t>
+          <t>Connecting On Linkedin</t>
         </is>
       </c>
       <c r="C189" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/promote-candidate-to-deal-room.md","Promote Candidate to Deal Pipeline")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/record-linkedin-connection-attempt.md","Record LinkedIn Connection Attempt")</f>
         <v/>
       </c>
       <c r="D189" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-origination-deal-room-promotion/SKILL.md","vc-origination-deal-room-promotion")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-outreach-draft-queue/SKILL.md","vc-outreach-draft-queue")</f>
         <v/>
       </c>
     </row>
@@ -27059,15 +27644,15 @@
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>Review Backlog</t>
+          <t>Connecting On Linkedin</t>
         </is>
       </c>
       <c r="C190" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/promote-candidate-to-deal-room.md","Promote Candidate to Deal Pipeline")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/record-linkedin-connection-attempt.md","Record LinkedIn Connection Attempt")</f>
         <v/>
       </c>
       <c r="D190" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/founder-outreach-and-intro-paths/SKILL.md","founder-outreach-and-intro-paths")</f>
         <v/>
       </c>
     </row>
@@ -27079,71 +27664,71 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>Review Backlog</t>
+          <t>Connecting On Linkedin</t>
         </is>
       </c>
       <c r="C191" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/promote-candidate-to-deal-room.md","Promote Candidate to Deal Pipeline")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/record-linkedin-connection-attempt.md","Record LinkedIn Connection Attempt")</f>
         <v/>
       </c>
       <c r="D191" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/deal-room-setup-and-source-ingestion/SKILL.md","deal-room-setup-and-source-ingestion")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
         <v/>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1" s="12">
       <c r="A192" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Initial Reachout Linkedin</t>
         </is>
       </c>
       <c r="C192" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-commercial-dd.md","Run Commercial DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-linkedin-reachout.md","Prepare Initial LinkedIn Reachout")</f>
         <v/>
       </c>
       <c r="D192" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-outreach-draft-queue/SKILL.md","vc-outreach-draft-queue")</f>
         <v/>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1" s="12">
       <c r="A193" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Initial Reachout Linkedin</t>
         </is>
       </c>
       <c r="C193" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-commercial-dd.md","Run Commercial DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-linkedin-reachout.md","Prepare Initial LinkedIn Reachout")</f>
         <v/>
       </c>
       <c r="D193" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/commercial-diligence-workstream/SKILL.md","commercial-diligence-workstream")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/founder-outreach-and-intro-paths/SKILL.md","founder-outreach-and-intro-paths")</f>
         <v/>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1" s="12">
       <c r="A194" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B194" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Initial Reachout Linkedin</t>
         </is>
       </c>
       <c r="C194" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-linkedin-reachout.md","Prepare Initial LinkedIn Reachout")</f>
         <v/>
       </c>
       <c r="D194" s="16">
@@ -27154,156 +27739,156 @@
     <row r="195" ht="18" customHeight="1" s="12">
       <c r="A195" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Second Reachout Email</t>
         </is>
       </c>
       <c r="C195" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-second-reachout-email.md","Prepare Second Reachout Email")</f>
         <v/>
       </c>
       <c r="D195" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/financial-diligence-workstream/SKILL.md","financial-diligence-workstream")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-outreach-draft-queue/SKILL.md","vc-outreach-draft-queue")</f>
         <v/>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1" s="12">
       <c r="A196" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Second Reachout Email</t>
         </is>
       </c>
       <c r="C196" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-second-reachout-email.md","Prepare Second Reachout Email")</f>
         <v/>
       </c>
       <c r="D196" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/team-and-hiring-assessment/SKILL.md","team-and-hiring-assessment")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/founder-outreach-and-intro-paths/SKILL.md","founder-outreach-and-intro-paths")</f>
         <v/>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1" s="12">
       <c r="A197" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Second Reachout Email</t>
         </is>
       </c>
       <c r="C197" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-second-reachout-email.md","Prepare Second Reachout Email")</f>
         <v/>
       </c>
       <c r="D197" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/red-flags-scanner/SKILL.md","red-flags-scanner")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
         <v/>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1" s="12">
       <c r="A198" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Second Reachout Email</t>
         </is>
       </c>
       <c r="C198" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-outreach-outcome.md","Review Outreach Outcome")</f>
         <v/>
       </c>
       <c r="D198" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-origination-deal-room-promotion/SKILL.md","vc-origination-deal-room-promotion")</f>
         <v/>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1" s="12">
       <c r="A199" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Second Reachout Email</t>
         </is>
       </c>
       <c r="C199" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-outreach-outcome.md","Review Outreach Outcome")</f>
         <v/>
       </c>
       <c r="D199" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/founder-evaluation-and-reference-checking/SKILL.md","founder-evaluation-and-reference-checking")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-outreach-draft-queue/SKILL.md","vc-outreach-draft-queue")</f>
         <v/>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1" s="12">
       <c r="A200" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Second Reachout Email</t>
         </is>
       </c>
       <c r="C200" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-outreach-outcome.md","Review Outreach Outcome")</f>
         <v/>
       </c>
       <c r="D200" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/team-and-hiring-assessment/SKILL.md","team-and-hiring-assessment")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
         <v/>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1" s="12">
       <c r="A201" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Engaged Added To Deal Funnel</t>
         </is>
       </c>
       <c r="C201" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/promote-candidate-to-deal-room.md","Promote Candidate to Deal Pipeline")</f>
         <v/>
       </c>
       <c r="D201" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/red-flags-scanner/SKILL.md","red-flags-scanner")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-origination-deal-room-promotion/SKILL.md","vc-origination-deal-room-promotion")</f>
         <v/>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1" s="12">
       <c r="A202" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B202" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Engaged Added To Deal Funnel</t>
         </is>
       </c>
       <c r="C202" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/promote-candidate-to-deal-room.md","Promote Candidate to Deal Pipeline")</f>
         <v/>
       </c>
       <c r="D202" s="16">
@@ -27314,20 +27899,20 @@
     <row r="203" ht="18" customHeight="1" s="12">
       <c r="A203" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Engaged Added To Deal Funnel</t>
         </is>
       </c>
       <c r="C203" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/promote-candidate-to-deal-room.md","Promote Candidate to Deal Pipeline")</f>
         <v/>
       </c>
       <c r="D203" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/technical-diligence-workstream/SKILL.md","technical-diligence-workstream")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/deal-room-setup-and-source-ingestion/SKILL.md","deal-room-setup-and-source-ingestion")</f>
         <v/>
       </c>
     </row>
@@ -27343,11 +27928,11 @@
         </is>
       </c>
       <c r="C204" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-commercial-dd.md","Run Commercial DD")</f>
         <v/>
       </c>
       <c r="D204" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/legal-diligence-coordination/SKILL.md","legal-diligence-coordination")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
         <v/>
       </c>
     </row>
@@ -27363,11 +27948,11 @@
         </is>
       </c>
       <c r="C205" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-commercial-dd.md","Run Commercial DD")</f>
         <v/>
       </c>
       <c r="D205" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/red-flags-scanner/SKILL.md","red-flags-scanner")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/commercial-diligence-workstream/SKILL.md","commercial-diligence-workstream")</f>
         <v/>
       </c>
     </row>
@@ -27383,7 +27968,7 @@
         </is>
       </c>
       <c r="C206" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
         <v/>
       </c>
       <c r="D206" s="16">
@@ -27399,15 +27984,15 @@
       </c>
       <c r="B207" s="15" t="inlineStr">
         <is>
-          <t>Contracts</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C207" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-investment-documents.md","Review Investment Documents")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
         <v/>
       </c>
       <c r="D207" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/legal-diligence-coordination/SKILL.md","legal-diligence-coordination")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/financial-diligence-workstream/SKILL.md","financial-diligence-workstream")</f>
         <v/>
       </c>
     </row>
@@ -27419,15 +28004,15 @@
       </c>
       <c r="B208" s="15" t="inlineStr">
         <is>
-          <t>Contracts</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C208" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-investment-documents.md","Review Investment Documents")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
         <v/>
       </c>
       <c r="D208" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/closing-coordination-and-cp-tracking/SKILL.md","closing-coordination-and-cp-tracking")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/team-and-hiring-assessment/SKILL.md","team-and-hiring-assessment")</f>
         <v/>
       </c>
     </row>
@@ -27439,15 +28024,15 @@
       </c>
       <c r="B209" s="15" t="inlineStr">
         <is>
-          <t>Contracts</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C209" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-investment-documents.md","Review Investment Documents")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
         <v/>
       </c>
       <c r="D209" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/red-flags-scanner/SKILL.md","red-flags-scanner")</f>
         <v/>
       </c>
     </row>
@@ -27459,11 +28044,11 @@
       </c>
       <c r="B210" s="15" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C210" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/manage-closing-checklist.md","Manage Closing Checklist")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
         <v/>
       </c>
       <c r="D210" s="16">
@@ -27479,15 +28064,15 @@
       </c>
       <c r="B211" s="15" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C211" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/manage-closing-checklist.md","Manage Closing Checklist")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
         <v/>
       </c>
       <c r="D211" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/closing-coordination-and-cp-tracking/SKILL.md","closing-coordination-and-cp-tracking")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/founder-evaluation-and-reference-checking/SKILL.md","founder-evaluation-and-reference-checking")</f>
         <v/>
       </c>
     </row>
@@ -27499,15 +28084,15 @@
       </c>
       <c r="B212" s="15" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C212" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/manage-closing-checklist.md","Manage Closing Checklist")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
         <v/>
       </c>
       <c r="D212" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-task-and-next-step-generation/SKILL.md","vc-task-and-next-step-generation")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/team-and-hiring-assessment/SKILL.md","team-and-hiring-assessment")</f>
         <v/>
       </c>
     </row>
@@ -27519,15 +28104,15 @@
       </c>
       <c r="B213" s="15" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C213" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/verify-conditions-precedent.md","Verify Conditions Precedent")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
         <v/>
       </c>
       <c r="D213" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/red-flags-scanner/SKILL.md","red-flags-scanner")</f>
         <v/>
       </c>
     </row>
@@ -27539,15 +28124,15 @@
       </c>
       <c r="B214" s="15" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C214" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/verify-conditions-precedent.md","Verify Conditions Precedent")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
         <v/>
       </c>
       <c r="D214" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/closing-coordination-and-cp-tracking/SKILL.md","closing-coordination-and-cp-tracking")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
         <v/>
       </c>
     </row>
@@ -27559,15 +28144,15 @@
       </c>
       <c r="B215" s="15" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C215" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/coordinate-capital-call-and-completion.md","Coordinate Capital Call And Completion")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
         <v/>
       </c>
       <c r="D215" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/closing-coordination-and-cp-tracking/SKILL.md","closing-coordination-and-cp-tracking")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/technical-diligence-workstream/SKILL.md","technical-diligence-workstream")</f>
         <v/>
       </c>
     </row>
@@ -27579,15 +28164,15 @@
       </c>
       <c r="B216" s="15" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C216" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/coordinate-capital-call-and-completion.md","Coordinate Capital Call And Completion")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
         <v/>
       </c>
       <c r="D216" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-task-and-next-step-generation/SKILL.md","vc-task-and-next-step-generation")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/legal-diligence-coordination/SKILL.md","legal-diligence-coordination")</f>
         <v/>
       </c>
     </row>
@@ -27599,15 +28184,15 @@
       </c>
       <c r="B217" s="15" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C217" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/coordinate-capital-call-and-completion.md","Coordinate Capital Call And Completion")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
         <v/>
       </c>
       <c r="D217" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/red-flags-scanner/SKILL.md","red-flags-scanner")</f>
         <v/>
       </c>
     </row>
@@ -27619,11 +28204,11 @@
       </c>
       <c r="B218" s="15" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C218" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-portfolio-onboarding.md","Prepare Portfolio Onboarding")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
         <v/>
       </c>
       <c r="D218" s="16">
@@ -27639,20 +28224,260 @@
       </c>
       <c r="B219" s="15" t="inlineStr">
         <is>
+          <t>Contracts</t>
+        </is>
+      </c>
+      <c r="C219" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-investment-documents.md","Review Investment Documents")</f>
+        <v/>
+      </c>
+      <c r="D219" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/legal-diligence-coordination/SKILL.md","legal-diligence-coordination")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220" ht="18" customHeight="1" s="12">
+      <c r="A220" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B220" s="15" t="inlineStr">
+        <is>
+          <t>Contracts</t>
+        </is>
+      </c>
+      <c r="C220" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-investment-documents.md","Review Investment Documents")</f>
+        <v/>
+      </c>
+      <c r="D220" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/closing-coordination-and-cp-tracking/SKILL.md","closing-coordination-and-cp-tracking")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221" ht="18" customHeight="1" s="12">
+      <c r="A221" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B221" s="15" t="inlineStr">
+        <is>
+          <t>Contracts</t>
+        </is>
+      </c>
+      <c r="C221" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-investment-documents.md","Review Investment Documents")</f>
+        <v/>
+      </c>
+      <c r="D221" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222" ht="18" customHeight="1" s="12">
+      <c r="A222" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B222" s="15" t="inlineStr">
+        <is>
           <t>Closing</t>
         </is>
       </c>
-      <c r="C219" s="16">
+      <c r="C222" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/manage-closing-checklist.md","Manage Closing Checklist")</f>
+        <v/>
+      </c>
+      <c r="D222" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223" ht="18" customHeight="1" s="12">
+      <c r="A223" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B223" s="15" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C223" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/manage-closing-checklist.md","Manage Closing Checklist")</f>
+        <v/>
+      </c>
+      <c r="D223" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/closing-coordination-and-cp-tracking/SKILL.md","closing-coordination-and-cp-tracking")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="224" ht="18" customHeight="1" s="12">
+      <c r="A224" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B224" s="15" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C224" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/manage-closing-checklist.md","Manage Closing Checklist")</f>
+        <v/>
+      </c>
+      <c r="D224" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-task-and-next-step-generation/SKILL.md","vc-task-and-next-step-generation")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="225" ht="18" customHeight="1" s="12">
+      <c r="A225" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B225" s="15" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C225" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/verify-conditions-precedent.md","Verify Conditions Precedent")</f>
+        <v/>
+      </c>
+      <c r="D225" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="226" ht="18" customHeight="1" s="12">
+      <c r="A226" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B226" s="15" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C226" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/verify-conditions-precedent.md","Verify Conditions Precedent")</f>
+        <v/>
+      </c>
+      <c r="D226" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/closing-coordination-and-cp-tracking/SKILL.md","closing-coordination-and-cp-tracking")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227" ht="18" customHeight="1" s="12">
+      <c r="A227" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B227" s="15" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C227" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/coordinate-capital-call-and-completion.md","Coordinate Capital Call And Completion")</f>
+        <v/>
+      </c>
+      <c r="D227" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/closing-coordination-and-cp-tracking/SKILL.md","closing-coordination-and-cp-tracking")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228" ht="18" customHeight="1" s="12">
+      <c r="A228" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B228" s="15" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C228" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/coordinate-capital-call-and-completion.md","Coordinate Capital Call And Completion")</f>
+        <v/>
+      </c>
+      <c r="D228" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-task-and-next-step-generation/SKILL.md","vc-task-and-next-step-generation")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="229" ht="18" customHeight="1" s="12">
+      <c r="A229" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B229" s="15" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C229" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/coordinate-capital-call-and-completion.md","Coordinate Capital Call And Completion")</f>
+        <v/>
+      </c>
+      <c r="D229" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230" ht="18" customHeight="1" s="12">
+      <c r="A230" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B230" s="15" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C230" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-portfolio-onboarding.md","Prepare Portfolio Onboarding")</f>
         <v/>
       </c>
-      <c r="D219" s="16">
+      <c r="D230" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","citation-enforcement")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231" ht="18" customHeight="1" s="12">
+      <c r="A231" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B231" s="15" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C231" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-portfolio-onboarding.md","Prepare Portfolio Onboarding")</f>
+        <v/>
+      </c>
+      <c r="D231" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/portfolio-onboarding-and-100-day-plan/SKILL.md","portfolio-onboarding-and-100-day-plan")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D219"/>
+  <autoFilter ref="A1:D231"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -27666,7 +28491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F187"/>
+  <dimension ref="A1:F198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="12" min="1" max="1"/>
@@ -31505,15 +32330,15 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>Review Backlog</t>
+          <t>Connecting On Linkedin</t>
         </is>
       </c>
       <c r="C143" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/promote-candidate-to-deal-room.md","Promote Candidate to Deal Pipeline")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/record-linkedin-connection-attempt.md","Record LinkedIn Connection Attempt")</f>
         <v/>
       </c>
       <c r="D143" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/promotion-package-template.md","Promotion Package Template (vc.document.promotion_package_template)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/outreach-queue-template.md","Outreach Queue Template (vc.document.outreach_queue_template)")</f>
         <v/>
       </c>
       <c r="E143" s="15" t="inlineStr">
@@ -31523,7 +32348,7 @@
       </c>
       <c r="F143" s="15" t="inlineStr">
         <is>
-          <t>promotion_package_artifact_id</t>
+          <t>connection_record_artifact_id</t>
         </is>
       </c>
     </row>
@@ -31535,20 +32360,20 @@
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>Review Backlog</t>
+          <t>Connecting On Linkedin</t>
         </is>
       </c>
       <c r="C144" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/promote-candidate-to-deal-room.md","Promote Candidate to Deal Pipeline")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/record-linkedin-connection-attempt.md","Record LinkedIn Connection Attempt")</f>
         <v/>
       </c>
       <c r="D144" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/origination-source-strategy-guide.md","Origination Source Strategy Guide (vc.document.origination_source_strategy_guide)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (vc.document.template_use_guidance)")</f>
         <v/>
       </c>
       <c r="E144" s="15" t="inlineStr">
         <is>
-          <t>methodology</t>
+          <t>operating_guidance</t>
         </is>
       </c>
       <c r="F144" s="15" t="inlineStr"/>
@@ -31561,76 +32386,76 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>Review Backlog</t>
+          <t>Initial Reachout Linkedin</t>
         </is>
       </c>
       <c r="C145" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/promote-candidate-to-deal-room.md","Promote Candidate to Deal Pipeline")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-linkedin-reachout.md","Prepare Initial LinkedIn Reachout")</f>
         <v/>
       </c>
       <c r="D145" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (vc.document.template_use_guidance)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/outreach-queue-template.md","Outreach Queue Template (vc.document.outreach_queue_template)")</f>
         <v/>
       </c>
       <c r="E145" s="15" t="inlineStr">
         <is>
-          <t>operating_guidance</t>
-        </is>
-      </c>
-      <c r="F145" s="15" t="inlineStr"/>
+          <t>output_template</t>
+        </is>
+      </c>
+      <c r="F145" s="15" t="inlineStr">
+        <is>
+          <t>initial_linkedin_reachout_artifact_id</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="18" customHeight="1" s="12">
       <c r="A146" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Initial Reachout Linkedin</t>
         </is>
       </c>
       <c r="C146" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-commercial-dd.md","Run Commercial DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-linkedin-reachout.md","Prepare Initial LinkedIn Reachout")</f>
         <v/>
       </c>
       <c r="D146" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/diligence-report-template.md","Diligence Report Template (vc.document.diligence_report_template)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/origination-source-strategy-guide.md","Origination Source Strategy Guide (vc.document.origination_source_strategy_guide)")</f>
         <v/>
       </c>
       <c r="E146" s="15" t="inlineStr">
         <is>
-          <t>output_template</t>
-        </is>
-      </c>
-      <c r="F146" s="15" t="inlineStr">
-        <is>
-          <t>commercial_dd_artifact_id</t>
-        </is>
-      </c>
+          <t>methodology</t>
+        </is>
+      </c>
+      <c r="F146" s="15" t="inlineStr"/>
     </row>
     <row r="147" ht="18" customHeight="1" s="12">
       <c r="A147" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Initial Reachout Linkedin</t>
         </is>
       </c>
       <c r="C147" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-commercial-dd.md","Run Commercial DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-linkedin-reachout.md","Prepare Initial LinkedIn Reachout")</f>
         <v/>
       </c>
       <c r="D147" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/formal-diligence-workstream-guide.md","Formal Diligence Workstream Guide (vc.document.formal_diligence_workstream_guide)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (vc.document.template_use_guidance)")</f>
         <v/>
       </c>
       <c r="E147" s="15" t="inlineStr">
         <is>
-          <t>methodology</t>
+          <t>operating_guidance</t>
         </is>
       </c>
       <c r="F147" s="15" t="inlineStr"/>
@@ -31638,51 +32463,55 @@
     <row r="148" ht="18" customHeight="1" s="12">
       <c r="A148" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Second Reachout Email</t>
         </is>
       </c>
       <c r="C148" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-commercial-dd.md","Run Commercial DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-second-reachout-email.md","Prepare Second Reachout Email")</f>
         <v/>
       </c>
       <c r="D148" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/formal-diligence-checklist.md","Formal Diligence Checklist (vc.document.formal_diligence_checklist)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/outreach-queue-template.md","Outreach Queue Template (vc.document.outreach_queue_template)")</f>
         <v/>
       </c>
       <c r="E148" s="15" t="inlineStr">
         <is>
-          <t>checklist</t>
-        </is>
-      </c>
-      <c r="F148" s="15" t="inlineStr"/>
+          <t>output_template</t>
+        </is>
+      </c>
+      <c r="F148" s="15" t="inlineStr">
+        <is>
+          <t>second_reachout_email_artifact_id</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="18" customHeight="1" s="12">
       <c r="A149" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Second Reachout Email</t>
         </is>
       </c>
       <c r="C149" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-commercial-dd.md","Run Commercial DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-second-reachout-email.md","Prepare Second Reachout Email")</f>
         <v/>
       </c>
       <c r="D149" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (vc.document.evidence_citation_style_guide)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/origination-source-strategy-guide.md","Origination Source Strategy Guide (vc.document.origination_source_strategy_guide)")</f>
         <v/>
       </c>
       <c r="E149" s="15" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>methodology</t>
         </is>
       </c>
       <c r="F149" s="15" t="inlineStr"/>
@@ -31690,16 +32519,16 @@
     <row r="150" ht="18" customHeight="1" s="12">
       <c r="A150" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Second Reachout Email</t>
         </is>
       </c>
       <c r="C150" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-commercial-dd.md","Run Commercial DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-second-reachout-email.md","Prepare Second Reachout Email")</f>
         <v/>
       </c>
       <c r="D150" s="16">
@@ -31716,20 +32545,20 @@
     <row r="151" ht="18" customHeight="1" s="12">
       <c r="A151" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Second Reachout Email</t>
         </is>
       </c>
       <c r="C151" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-outreach-outcome.md","Review Outreach Outcome")</f>
         <v/>
       </c>
       <c r="D151" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/diligence-report-template.md","Diligence Report Template (vc.document.diligence_report_template)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/promotion-package-template.md","Promotion Package Template (vc.document.promotion_package_template)")</f>
         <v/>
       </c>
       <c r="E151" s="15" t="inlineStr">
@@ -31739,27 +32568,27 @@
       </c>
       <c r="F151" s="15" t="inlineStr">
         <is>
-          <t>financial_dd_artifact_id</t>
+          <t>outreach_outcome_artifact_id</t>
         </is>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1" s="12">
       <c r="A152" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Second Reachout Email</t>
         </is>
       </c>
       <c r="C152" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-outreach-outcome.md","Review Outreach Outcome")</f>
         <v/>
       </c>
       <c r="D152" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/formal-diligence-workstream-guide.md","Formal Diligence Workstream Guide (vc.document.formal_diligence_workstream_guide)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/origination-source-strategy-guide.md","Origination Source Strategy Guide (vc.document.origination_source_strategy_guide)")</f>
         <v/>
       </c>
       <c r="E152" s="15" t="inlineStr">
@@ -31772,25 +32601,25 @@
     <row r="153" ht="18" customHeight="1" s="12">
       <c r="A153" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Second Reachout Email</t>
         </is>
       </c>
       <c r="C153" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-outreach-outcome.md","Review Outreach Outcome")</f>
         <v/>
       </c>
       <c r="D153" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/formal-diligence-checklist.md","Formal Diligence Checklist (vc.document.formal_diligence_checklist)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (vc.document.template_use_guidance)")</f>
         <v/>
       </c>
       <c r="E153" s="15" t="inlineStr">
         <is>
-          <t>checklist</t>
+          <t>operating_guidance</t>
         </is>
       </c>
       <c r="F153" s="15" t="inlineStr"/>
@@ -31798,20 +32627,20 @@
     <row r="154" ht="18" customHeight="1" s="12">
       <c r="A154" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Engaged Added To Deal Funnel</t>
         </is>
       </c>
       <c r="C154" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/promote-candidate-to-deal-room.md","Promote Candidate to Deal Pipeline")</f>
         <v/>
       </c>
       <c r="D154" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/diligence-report-template.md","Diligence Report Template (vc.document.diligence_report_template)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/promotion-package-template.md","Promotion Package Template (vc.document.promotion_package_template)")</f>
         <v/>
       </c>
       <c r="E154" s="15" t="inlineStr">
@@ -31821,32 +32650,32 @@
       </c>
       <c r="F154" s="15" t="inlineStr">
         <is>
-          <t>unit_economics_artifact_id</t>
+          <t>promotion_package_artifact_id</t>
         </is>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1" s="12">
       <c r="A155" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Engaged Added To Deal Funnel</t>
         </is>
       </c>
       <c r="C155" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/promote-candidate-to-deal-room.md","Promote Candidate to Deal Pipeline")</f>
         <v/>
       </c>
       <c r="D155" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (vc.document.evidence_citation_style_guide)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/origination/origination-source-strategy-guide.md","Origination Source Strategy Guide (vc.document.origination_source_strategy_guide)")</f>
         <v/>
       </c>
       <c r="E155" s="15" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>methodology</t>
         </is>
       </c>
       <c r="F155" s="15" t="inlineStr"/>
@@ -31854,16 +32683,16 @@
     <row r="156" ht="18" customHeight="1" s="12">
       <c r="A156" s="15" t="inlineStr">
         <is>
-          <t>Investment Management</t>
+          <t>Origination Pipeline</t>
         </is>
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>Formal Diligence</t>
+          <t>Engaged Added To Deal Funnel</t>
         </is>
       </c>
       <c r="C156" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/promote-candidate-to-deal-room.md","Promote Candidate to Deal Pipeline")</f>
         <v/>
       </c>
       <c r="D156" s="16">
@@ -31889,7 +32718,7 @@
         </is>
       </c>
       <c r="C157" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-commercial-dd.md","Run Commercial DD")</f>
         <v/>
       </c>
       <c r="D157" s="16">
@@ -31903,7 +32732,7 @@
       </c>
       <c r="F157" s="15" t="inlineStr">
         <is>
-          <t>founder_evaluation_artifact_id</t>
+          <t>commercial_dd_artifact_id</t>
         </is>
       </c>
     </row>
@@ -31919,7 +32748,7 @@
         </is>
       </c>
       <c r="C158" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-commercial-dd.md","Run Commercial DD")</f>
         <v/>
       </c>
       <c r="D158" s="16">
@@ -31945,7 +32774,7 @@
         </is>
       </c>
       <c r="C159" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-commercial-dd.md","Run Commercial DD")</f>
         <v/>
       </c>
       <c r="D159" s="16">
@@ -31971,7 +32800,7 @@
         </is>
       </c>
       <c r="C160" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-commercial-dd.md","Run Commercial DD")</f>
         <v/>
       </c>
       <c r="D160" s="16">
@@ -31997,7 +32826,7 @@
         </is>
       </c>
       <c r="C161" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-commercial-dd.md","Run Commercial DD")</f>
         <v/>
       </c>
       <c r="D161" s="16">
@@ -32023,7 +32852,7 @@
         </is>
       </c>
       <c r="C162" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
         <v/>
       </c>
       <c r="D162" s="16">
@@ -32037,7 +32866,7 @@
       </c>
       <c r="F162" s="15" t="inlineStr">
         <is>
-          <t>technical_dd_artifact_id</t>
+          <t>financial_dd_artifact_id</t>
         </is>
       </c>
     </row>
@@ -32053,7 +32882,7 @@
         </is>
       </c>
       <c r="C163" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
         <v/>
       </c>
       <c r="D163" s="16">
@@ -32079,7 +32908,7 @@
         </is>
       </c>
       <c r="C164" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
         <v/>
       </c>
       <c r="D164" s="16">
@@ -32105,19 +32934,23 @@
         </is>
       </c>
       <c r="C165" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
         <v/>
       </c>
       <c r="D165" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (vc.document.evidence_citation_style_guide)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/diligence-report-template.md","Diligence Report Template (vc.document.diligence_report_template)")</f>
         <v/>
       </c>
       <c r="E165" s="15" t="inlineStr">
         <is>
-          <t>style_guide</t>
-        </is>
-      </c>
-      <c r="F165" s="15" t="inlineStr"/>
+          <t>output_template</t>
+        </is>
+      </c>
+      <c r="F165" s="15" t="inlineStr">
+        <is>
+          <t>unit_economics_artifact_id</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="18" customHeight="1" s="12">
       <c r="A166" s="15" t="inlineStr">
@@ -32131,16 +32964,16 @@
         </is>
       </c>
       <c r="C166" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
         <v/>
       </c>
       <c r="D166" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (vc.document.template_use_guidance)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (vc.document.evidence_citation_style_guide)")</f>
         <v/>
       </c>
       <c r="E166" s="15" t="inlineStr">
         <is>
-          <t>operating_guidance</t>
+          <t>style_guide</t>
         </is>
       </c>
       <c r="F166" s="15" t="inlineStr"/>
@@ -32157,23 +32990,19 @@
         </is>
       </c>
       <c r="C167" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-financial-dd.md","Run Financial DD")</f>
         <v/>
       </c>
       <c r="D167" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/legal-diligence-tracker-template.md","Legal Diligence Tracker Template (vc.document.legal_diligence_tracker_template)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (vc.document.template_use_guidance)")</f>
         <v/>
       </c>
       <c r="E167" s="15" t="inlineStr">
         <is>
-          <t>output_template</t>
-        </is>
-      </c>
-      <c r="F167" s="15" t="inlineStr">
-        <is>
-          <t>legal_diligence_artifact_id</t>
-        </is>
-      </c>
+          <t>operating_guidance</t>
+        </is>
+      </c>
+      <c r="F167" s="15" t="inlineStr"/>
     </row>
     <row r="168" ht="18" customHeight="1" s="12">
       <c r="A168" s="15" t="inlineStr">
@@ -32187,19 +33016,23 @@
         </is>
       </c>
       <c r="C168" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
         <v/>
       </c>
       <c r="D168" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/legal-diligence-guide.md","Legal Diligence Guide (vc.document.legal_diligence_guide)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/diligence-report-template.md","Diligence Report Template (vc.document.diligence_report_template)")</f>
         <v/>
       </c>
       <c r="E168" s="15" t="inlineStr">
         <is>
-          <t>methodology</t>
-        </is>
-      </c>
-      <c r="F168" s="15" t="inlineStr"/>
+          <t>output_template</t>
+        </is>
+      </c>
+      <c r="F168" s="15" t="inlineStr">
+        <is>
+          <t>founder_evaluation_artifact_id</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="18" customHeight="1" s="12">
       <c r="A169" s="15" t="inlineStr">
@@ -32213,7 +33046,7 @@
         </is>
       </c>
       <c r="C169" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
         <v/>
       </c>
       <c r="D169" s="16">
@@ -32239,7 +33072,7 @@
         </is>
       </c>
       <c r="C170" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
         <v/>
       </c>
       <c r="D170" s="16">
@@ -32265,7 +33098,7 @@
         </is>
       </c>
       <c r="C171" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
         <v/>
       </c>
       <c r="D171" s="16">
@@ -32291,7 +33124,7 @@
         </is>
       </c>
       <c r="C172" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-founder-evaluation.md","Run Founder Evaluation")</f>
         <v/>
       </c>
       <c r="D172" s="16">
@@ -32313,15 +33146,15 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>Contracts</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C173" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-investment-documents.md","Review Investment Documents")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
         <v/>
       </c>
       <c r="D173" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/investment-document-review-template.md","Investment Document Review Template (vc.document.investment_document_review_template)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/diligence-report-template.md","Diligence Report Template (vc.document.diligence_report_template)")</f>
         <v/>
       </c>
       <c r="E173" s="15" t="inlineStr">
@@ -32331,7 +33164,7 @@
       </c>
       <c r="F173" s="15" t="inlineStr">
         <is>
-          <t>investment_document_review_artifact_id</t>
+          <t>technical_dd_artifact_id</t>
         </is>
       </c>
     </row>
@@ -32343,15 +33176,15 @@
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>Contracts</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C174" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-investment-documents.md","Review Investment Documents")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
         <v/>
       </c>
       <c r="D174" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/legal-diligence-guide.md","Legal Diligence Guide (vc.document.legal_diligence_guide)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/formal-diligence-workstream-guide.md","Formal Diligence Workstream Guide (vc.document.formal_diligence_workstream_guide)")</f>
         <v/>
       </c>
       <c r="E174" s="15" t="inlineStr">
@@ -32369,20 +33202,20 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>Contracts</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C175" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-investment-documents.md","Review Investment Documents")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
         <v/>
       </c>
       <c r="D175" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (vc.document.evidence_citation_style_guide)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/formal-diligence-checklist.md","Formal Diligence Checklist (vc.document.formal_diligence_checklist)")</f>
         <v/>
       </c>
       <c r="E175" s="15" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>checklist</t>
         </is>
       </c>
       <c r="F175" s="15" t="inlineStr"/>
@@ -32395,20 +33228,20 @@
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>Contracts</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C176" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-investment-documents.md","Review Investment Documents")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
         <v/>
       </c>
       <c r="D176" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (vc.document.template_use_guidance)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (vc.document.evidence_citation_style_guide)")</f>
         <v/>
       </c>
       <c r="E176" s="15" t="inlineStr">
         <is>
-          <t>operating_guidance</t>
+          <t>style_guide</t>
         </is>
       </c>
       <c r="F176" s="15" t="inlineStr"/>
@@ -32421,27 +33254,23 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C177" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/manage-closing-checklist.md","Manage Closing Checklist")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-technical-dd.md","Run Technical DD")</f>
         <v/>
       </c>
       <c r="D177" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/closing-checklist.md","Closing Checklist (vc.document.closing_checklist)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (vc.document.template_use_guidance)")</f>
         <v/>
       </c>
       <c r="E177" s="15" t="inlineStr">
         <is>
-          <t>output_template</t>
-        </is>
-      </c>
-      <c r="F177" s="15" t="inlineStr">
-        <is>
-          <t>closing_checklist_artifact_id</t>
-        </is>
-      </c>
+          <t>operating_guidance</t>
+        </is>
+      </c>
+      <c r="F177" s="15" t="inlineStr"/>
     </row>
     <row r="178" ht="18" customHeight="1" s="12">
       <c r="A178" s="15" t="inlineStr">
@@ -32451,23 +33280,27 @@
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C178" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/manage-closing-checklist.md","Manage Closing Checklist")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
         <v/>
       </c>
       <c r="D178" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/legal-diligence-guide.md","Legal Diligence Guide (vc.document.legal_diligence_guide)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/legal-diligence-tracker-template.md","Legal Diligence Tracker Template (vc.document.legal_diligence_tracker_template)")</f>
         <v/>
       </c>
       <c r="E178" s="15" t="inlineStr">
         <is>
-          <t>methodology</t>
-        </is>
-      </c>
-      <c r="F178" s="15" t="inlineStr"/>
+          <t>output_template</t>
+        </is>
+      </c>
+      <c r="F178" s="15" t="inlineStr">
+        <is>
+          <t>legal_diligence_artifact_id</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="18" customHeight="1" s="12">
       <c r="A179" s="15" t="inlineStr">
@@ -32477,20 +33310,20 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C179" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/manage-closing-checklist.md","Manage Closing Checklist")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
         <v/>
       </c>
       <c r="D179" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (vc.document.template_use_guidance)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/legal-diligence-guide.md","Legal Diligence Guide (vc.document.legal_diligence_guide)")</f>
         <v/>
       </c>
       <c r="E179" s="15" t="inlineStr">
         <is>
-          <t>operating_guidance</t>
+          <t>methodology</t>
         </is>
       </c>
       <c r="F179" s="15" t="inlineStr"/>
@@ -32503,27 +33336,23 @@
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C180" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/verify-conditions-precedent.md","Verify Conditions Precedent")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
         <v/>
       </c>
       <c r="D180" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/conditions-precedent-tracker-template.md","Conditions Precedent Tracker Template (vc.document.conditions_precedent_tracker_template)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/formal-diligence-workstream-guide.md","Formal Diligence Workstream Guide (vc.document.formal_diligence_workstream_guide)")</f>
         <v/>
       </c>
       <c r="E180" s="15" t="inlineStr">
         <is>
-          <t>output_template</t>
-        </is>
-      </c>
-      <c r="F180" s="15" t="inlineStr">
-        <is>
-          <t>conditions_precedent_verification_artifact_id</t>
-        </is>
-      </c>
+          <t>methodology</t>
+        </is>
+      </c>
+      <c r="F180" s="15" t="inlineStr"/>
     </row>
     <row r="181" ht="18" customHeight="1" s="12">
       <c r="A181" s="15" t="inlineStr">
@@ -32533,20 +33362,20 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C181" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/verify-conditions-precedent.md","Verify Conditions Precedent")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
         <v/>
       </c>
       <c r="D181" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/legal-diligence-guide.md","Legal Diligence Guide (vc.document.legal_diligence_guide)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/formal-diligence-checklist.md","Formal Diligence Checklist (vc.document.formal_diligence_checklist)")</f>
         <v/>
       </c>
       <c r="E181" s="15" t="inlineStr">
         <is>
-          <t>methodology</t>
+          <t>checklist</t>
         </is>
       </c>
       <c r="F181" s="15" t="inlineStr"/>
@@ -32559,20 +33388,20 @@
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C182" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/verify-conditions-precedent.md","Verify Conditions Precedent")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
         <v/>
       </c>
       <c r="D182" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (vc.document.template_use_guidance)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (vc.document.evidence_citation_style_guide)")</f>
         <v/>
       </c>
       <c r="E182" s="15" t="inlineStr">
         <is>
-          <t>operating_guidance</t>
+          <t>style_guide</t>
         </is>
       </c>
       <c r="F182" s="15" t="inlineStr"/>
@@ -32585,27 +33414,23 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Formal Diligence</t>
         </is>
       </c>
       <c r="C183" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/coordinate-capital-call-and-completion.md","Coordinate Capital Call And Completion")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/run-legal-diligence.md","Run Legal Diligence")</f>
         <v/>
       </c>
       <c r="D183" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/completion-tracker-template.md","Completion Tracker Template (vc.document.completion_tracker_template)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (vc.document.template_use_guidance)")</f>
         <v/>
       </c>
       <c r="E183" s="15" t="inlineStr">
         <is>
-          <t>output_template</t>
-        </is>
-      </c>
-      <c r="F183" s="15" t="inlineStr">
-        <is>
-          <t>completion_tracker_artifact_id</t>
-        </is>
-      </c>
+          <t>operating_guidance</t>
+        </is>
+      </c>
+      <c r="F183" s="15" t="inlineStr"/>
     </row>
     <row r="184" ht="18" customHeight="1" s="12">
       <c r="A184" s="15" t="inlineStr">
@@ -32615,23 +33440,27 @@
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Contracts</t>
         </is>
       </c>
       <c r="C184" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/coordinate-capital-call-and-completion.md","Coordinate Capital Call And Completion")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-investment-documents.md","Review Investment Documents")</f>
         <v/>
       </c>
       <c r="D184" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (vc.document.evidence_citation_style_guide)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/investment-document-review-template.md","Investment Document Review Template (vc.document.investment_document_review_template)")</f>
         <v/>
       </c>
       <c r="E184" s="15" t="inlineStr">
         <is>
-          <t>style_guide</t>
-        </is>
-      </c>
-      <c r="F184" s="15" t="inlineStr"/>
+          <t>output_template</t>
+        </is>
+      </c>
+      <c r="F184" s="15" t="inlineStr">
+        <is>
+          <t>investment_document_review_artifact_id</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="18" customHeight="1" s="12">
       <c r="A185" s="15" t="inlineStr">
@@ -32641,20 +33470,20 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Contracts</t>
         </is>
       </c>
       <c r="C185" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/coordinate-capital-call-and-completion.md","Coordinate Capital Call And Completion")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-investment-documents.md","Review Investment Documents")</f>
         <v/>
       </c>
       <c r="D185" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (vc.document.template_use_guidance)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/legal-diligence-guide.md","Legal Diligence Guide (vc.document.legal_diligence_guide)")</f>
         <v/>
       </c>
       <c r="E185" s="15" t="inlineStr">
         <is>
-          <t>operating_guidance</t>
+          <t>methodology</t>
         </is>
       </c>
       <c r="F185" s="15" t="inlineStr"/>
@@ -32667,27 +33496,23 @@
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Contracts</t>
         </is>
       </c>
       <c r="C186" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-portfolio-onboarding.md","Prepare Portfolio Onboarding")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-investment-documents.md","Review Investment Documents")</f>
         <v/>
       </c>
       <c r="D186" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/portfolio-onboarding-plan-template.md","Portfolio Onboarding Plan Template (vc.document.portfolio_onboarding_plan_template)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (vc.document.evidence_citation_style_guide)")</f>
         <v/>
       </c>
       <c r="E186" s="15" t="inlineStr">
         <is>
-          <t>output_template</t>
-        </is>
-      </c>
-      <c r="F186" s="15" t="inlineStr">
-        <is>
-          <t>portfolio_onboarding_plan_artifact_id</t>
-        </is>
-      </c>
+          <t>style_guide</t>
+        </is>
+      </c>
+      <c r="F186" s="15" t="inlineStr"/>
     </row>
     <row r="187" ht="18" customHeight="1" s="12">
       <c r="A187" s="15" t="inlineStr">
@@ -32697,11 +33522,11 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Contracts</t>
         </is>
       </c>
       <c r="C187" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-portfolio-onboarding.md","Prepare Portfolio Onboarding")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-investment-documents.md","Review Investment Documents")</f>
         <v/>
       </c>
       <c r="D187" s="16">
@@ -32715,8 +33540,310 @@
       </c>
       <c r="F187" s="15" t="inlineStr"/>
     </row>
+    <row r="188" ht="18" customHeight="1" s="12">
+      <c r="A188" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B188" s="15" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C188" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/manage-closing-checklist.md","Manage Closing Checklist")</f>
+        <v/>
+      </c>
+      <c r="D188" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/closing-checklist.md","Closing Checklist (vc.document.closing_checklist)")</f>
+        <v/>
+      </c>
+      <c r="E188" s="15" t="inlineStr">
+        <is>
+          <t>output_template</t>
+        </is>
+      </c>
+      <c r="F188" s="15" t="inlineStr">
+        <is>
+          <t>closing_checklist_artifact_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="18" customHeight="1" s="12">
+      <c r="A189" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B189" s="15" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C189" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/manage-closing-checklist.md","Manage Closing Checklist")</f>
+        <v/>
+      </c>
+      <c r="D189" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/legal-diligence-guide.md","Legal Diligence Guide (vc.document.legal_diligence_guide)")</f>
+        <v/>
+      </c>
+      <c r="E189" s="15" t="inlineStr">
+        <is>
+          <t>methodology</t>
+        </is>
+      </c>
+      <c r="F189" s="15" t="inlineStr"/>
+    </row>
+    <row r="190" ht="18" customHeight="1" s="12">
+      <c r="A190" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B190" s="15" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C190" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/manage-closing-checklist.md","Manage Closing Checklist")</f>
+        <v/>
+      </c>
+      <c r="D190" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (vc.document.template_use_guidance)")</f>
+        <v/>
+      </c>
+      <c r="E190" s="15" t="inlineStr">
+        <is>
+          <t>operating_guidance</t>
+        </is>
+      </c>
+      <c r="F190" s="15" t="inlineStr"/>
+    </row>
+    <row r="191" ht="18" customHeight="1" s="12">
+      <c r="A191" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B191" s="15" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C191" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/verify-conditions-precedent.md","Verify Conditions Precedent")</f>
+        <v/>
+      </c>
+      <c r="D191" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/conditions-precedent-tracker-template.md","Conditions Precedent Tracker Template (vc.document.conditions_precedent_tracker_template)")</f>
+        <v/>
+      </c>
+      <c r="E191" s="15" t="inlineStr">
+        <is>
+          <t>output_template</t>
+        </is>
+      </c>
+      <c r="F191" s="15" t="inlineStr">
+        <is>
+          <t>conditions_precedent_verification_artifact_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="18" customHeight="1" s="12">
+      <c r="A192" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B192" s="15" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C192" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/verify-conditions-precedent.md","Verify Conditions Precedent")</f>
+        <v/>
+      </c>
+      <c r="D192" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/legal-diligence-guide.md","Legal Diligence Guide (vc.document.legal_diligence_guide)")</f>
+        <v/>
+      </c>
+      <c r="E192" s="15" t="inlineStr">
+        <is>
+          <t>methodology</t>
+        </is>
+      </c>
+      <c r="F192" s="15" t="inlineStr"/>
+    </row>
+    <row r="193" ht="18" customHeight="1" s="12">
+      <c r="A193" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B193" s="15" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C193" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/verify-conditions-precedent.md","Verify Conditions Precedent")</f>
+        <v/>
+      </c>
+      <c r="D193" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (vc.document.template_use_guidance)")</f>
+        <v/>
+      </c>
+      <c r="E193" s="15" t="inlineStr">
+        <is>
+          <t>operating_guidance</t>
+        </is>
+      </c>
+      <c r="F193" s="15" t="inlineStr"/>
+    </row>
+    <row r="194" ht="18" customHeight="1" s="12">
+      <c r="A194" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B194" s="15" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C194" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/coordinate-capital-call-and-completion.md","Coordinate Capital Call And Completion")</f>
+        <v/>
+      </c>
+      <c r="D194" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/completion-tracker-template.md","Completion Tracker Template (vc.document.completion_tracker_template)")</f>
+        <v/>
+      </c>
+      <c r="E194" s="15" t="inlineStr">
+        <is>
+          <t>output_template</t>
+        </is>
+      </c>
+      <c r="F194" s="15" t="inlineStr">
+        <is>
+          <t>completion_tracker_artifact_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="18" customHeight="1" s="12">
+      <c r="A195" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B195" s="15" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C195" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/coordinate-capital-call-and-completion.md","Coordinate Capital Call And Completion")</f>
+        <v/>
+      </c>
+      <c r="D195" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (vc.document.evidence_citation_style_guide)")</f>
+        <v/>
+      </c>
+      <c r="E195" s="15" t="inlineStr">
+        <is>
+          <t>style_guide</t>
+        </is>
+      </c>
+      <c r="F195" s="15" t="inlineStr"/>
+    </row>
+    <row r="196" ht="18" customHeight="1" s="12">
+      <c r="A196" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B196" s="15" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C196" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/coordinate-capital-call-and-completion.md","Coordinate Capital Call And Completion")</f>
+        <v/>
+      </c>
+      <c r="D196" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (vc.document.template_use_guidance)")</f>
+        <v/>
+      </c>
+      <c r="E196" s="15" t="inlineStr">
+        <is>
+          <t>operating_guidance</t>
+        </is>
+      </c>
+      <c r="F196" s="15" t="inlineStr"/>
+    </row>
+    <row r="197" ht="18" customHeight="1" s="12">
+      <c r="A197" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B197" s="15" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C197" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-portfolio-onboarding.md","Prepare Portfolio Onboarding")</f>
+        <v/>
+      </c>
+      <c r="D197" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/portfolio-onboarding-plan-template.md","Portfolio Onboarding Plan Template (vc.document.portfolio_onboarding_plan_template)")</f>
+        <v/>
+      </c>
+      <c r="E197" s="15" t="inlineStr">
+        <is>
+          <t>output_template</t>
+        </is>
+      </c>
+      <c r="F197" s="15" t="inlineStr">
+        <is>
+          <t>portfolio_onboarding_plan_artifact_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="18" customHeight="1" s="12">
+      <c r="A198" s="15" t="inlineStr">
+        <is>
+          <t>Investment Management</t>
+        </is>
+      </c>
+      <c r="B198" s="15" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="C198" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-portfolio-onboarding.md","Prepare Portfolio Onboarding")</f>
+        <v/>
+      </c>
+      <c r="D198" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (vc.document.template_use_guidance)")</f>
+        <v/>
+      </c>
+      <c r="E198" s="15" t="inlineStr">
+        <is>
+          <t>operating_guidance</t>
+        </is>
+      </c>
+      <c r="F198" s="15" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F187"/>
+  <autoFilter ref="A1:F198"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/outputs/vc-pr26-project-task-doc-map-blueprints-github-links.xlsx
+++ b/outputs/vc-pr26-project-task-doc-map-blueprints-github-links.xlsx
@@ -2460,7 +2460,7 @@
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D36" s="16">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D37" s="16">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D38" s="16">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D39" s="16">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D40" s="16">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D41" s="16">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D42" s="16">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="C43" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D43" s="16">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D44" s="16">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="C45" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D45" s="16">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D46" s="16">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D47" s="16">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D48" s="16">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D49" s="16">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D50" s="16">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="C51" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D51" s="16">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D52" s="16">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C53" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D53" s="16">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D54" s="16">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="C55" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D55" s="16">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="D56" s="16">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="D57" s="16">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D58" s="16">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="C59" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D59" s="16">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D60" s="16">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="C61" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D61" s="16">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D62" s="16">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C63" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D63" s="16">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D64" s="16">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D65" s="16">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D66" s="16">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D67" s="16">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D68" s="16">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D69" s="16">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D70" s="16">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D71" s="16">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D72" s="16">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D73" s="16">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D74" s="16">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D75" s="16">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D76" s="16">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D77" s="16">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D78" s="16">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D79" s="16">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D80" s="16">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="C184" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="D184" s="16">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="C185" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="D185" s="16">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="C186" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="D186" s="16">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="C187" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D187" s="16">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="C188" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D188" s="16">
@@ -10545,7 +10545,7 @@
       </c>
       <c r="C189" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D189" s="16">
@@ -10595,7 +10595,7 @@
       </c>
       <c r="C190" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D190" s="16">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="C191" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="D191" s="16">
@@ -10698,7 +10698,7 @@
       </c>
       <c r="C192" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="D192" s="16">
@@ -10755,7 +10755,7 @@
       </c>
       <c r="C193" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="D193" s="16">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="C194" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="D194" s="16">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="C195" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D195" s="16">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="C196" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D196" s="16">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="C197" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D197" s="16">
@@ -11009,7 +11009,7 @@
       </c>
       <c r="C198" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="D198" s="16">
@@ -25062,7 +25062,7 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C26" s="16">
@@ -25082,7 +25082,7 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C27" s="16">
@@ -25102,7 +25102,7 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C28" s="16">
@@ -25122,7 +25122,7 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C29" s="16">
@@ -25142,7 +25142,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C30" s="16">
@@ -25162,7 +25162,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C31" s="16">
@@ -25182,7 +25182,7 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C32" s="16">
@@ -25202,7 +25202,7 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C33" s="16">
@@ -25222,7 +25222,7 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C34" s="16">
@@ -25242,7 +25242,7 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C35" s="16">
@@ -25262,7 +25262,7 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C36" s="16">
@@ -25282,7 +25282,7 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C37" s="16">
@@ -25302,7 +25302,7 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C38" s="16">
@@ -25322,7 +25322,7 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C39" s="16">
@@ -25342,7 +25342,7 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C40" s="16">
@@ -25362,7 +25362,7 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C41" s="16">
@@ -25382,7 +25382,7 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C42" s="16">
@@ -25402,7 +25402,7 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C43" s="16">
@@ -25422,7 +25422,7 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C44" s="16">
@@ -25442,7 +25442,7 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C45" s="16">
@@ -25462,7 +25462,7 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="C46" s="16">
@@ -25482,7 +25482,7 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="C47" s="16">
@@ -25502,7 +25502,7 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C48" s="16">
@@ -25522,7 +25522,7 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C49" s="16">
@@ -25542,7 +25542,7 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C50" s="16">
@@ -25562,7 +25562,7 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C51" s="16">
@@ -25582,7 +25582,7 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C52" s="16">
@@ -25602,7 +25602,7 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C53" s="16">
@@ -25622,7 +25622,7 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C54" s="16">
@@ -25642,7 +25642,7 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C55" s="16">
@@ -25662,7 +25662,7 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C56" s="16">
@@ -25682,7 +25682,7 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C57" s="16">
@@ -25702,7 +25702,7 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C58" s="16">
@@ -25722,7 +25722,7 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C59" s="16">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C60" s="16">
@@ -25762,7 +25762,7 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C61" s="16">
@@ -25782,7 +25782,7 @@
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C62" s="16">
@@ -25802,7 +25802,7 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C63" s="16">
@@ -25822,7 +25822,7 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C64" s="16">
@@ -25842,7 +25842,7 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C65" s="16">
@@ -25862,7 +25862,7 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C66" s="16">
@@ -25882,7 +25882,7 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C67" s="16">
@@ -25902,7 +25902,7 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C68" s="16">
@@ -25922,7 +25922,7 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C69" s="16">
@@ -25942,7 +25942,7 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C70" s="16">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="C121" s="16">
@@ -26982,7 +26982,7 @@
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="C122" s="16">
@@ -27002,7 +27002,7 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="C123" s="16">
@@ -27022,7 +27022,7 @@
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C124" s="16">
@@ -27042,7 +27042,7 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C125" s="16">
@@ -27062,7 +27062,7 @@
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C126" s="16">
@@ -27082,7 +27082,7 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C127" s="16">
@@ -27102,7 +27102,7 @@
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="C128" s="16">
@@ -27122,7 +27122,7 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="C129" s="16">
@@ -27142,7 +27142,7 @@
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C130" s="16">
@@ -27162,7 +27162,7 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C131" s="16">
@@ -27182,7 +27182,7 @@
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C132" s="16">
@@ -27202,7 +27202,7 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C133" s="16">
@@ -32456,7 +32456,7 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="C111" s="16">
@@ -32486,7 +32486,7 @@
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="C112" s="16">
@@ -32512,7 +32512,7 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="C113" s="16">
@@ -32538,7 +32538,7 @@
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="C114" s="16">
@@ -32568,7 +32568,7 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="C115" s="16">
@@ -32594,7 +32594,7 @@
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="C116" s="16">
@@ -32620,7 +32620,7 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="C117" s="16">

--- a/outputs/vc-pr26-project-task-doc-map-blueprints-github-links.xlsx
+++ b/outputs/vc-pr26-project-task-doc-map-blueprints-github-links.xlsx
@@ -870,12 +870,8 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="135" customHeight="1" s="12">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Alex</t>
-        </is>
-      </c>
+    <row r="7" ht="18" customHeight="1" s="12">
+      <c r="A7" s="15" t="inlineStr"/>
       <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Deal Pipeline</t>
@@ -886,223 +882,186 @@
           <t>Setup</t>
         </is>
       </c>
-      <c r="D7" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
-        <v/>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Project Source Setup</t>
+        </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>Capture source context, known fields, missing information, and guided project-creation values for one venture-capital opportunity before formal screening.</t>
+          <t>Review selected source route and setup intent before writes or imports.</t>
         </is>
       </c>
       <c r="F7" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-dealflow-concierge.md","Dealflow Concierge")</f>
-        <v/>
-      </c>
-      <c r="G7" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/deal-room-setup-and-source-ingestion/SKILL.md","Deal Pipeline Setup &amp; Source Ingestion")</f>
-        <v/>
-      </c>
-      <c r="H7" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/deal-room-sop.md","Deal Pipeline Operating SOP (operating_guidance)")</f>
-        <v/>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-deal-room-setup-guide.md","Deal Pipeline Setup Guide")</f>
+        <v/>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
         <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <t>project-source-setup</t>
+        </is>
+      </c>
+      <c r="K7" s="15" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="12">
+      <c r="A8" s="15" t="inlineStr"/>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="D8" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/vc-pack-variable-discovery.md","VC Pack Variable Discovery")</f>
+        <v/>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Best-effort, review-only discovery for VC Pack Setup variables and invite suggestions.</t>
+        </is>
+      </c>
+      <c r="F8" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-deal-room-setup-guide.md","Deal Pipeline Setup Guide")</f>
+        <v/>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
           <t>alludium-platform
-harmonic-mcp-oauth
-affinity-mcp-server
-exa-mcp-hosted
-brave-search-mcp
-serpapi-mcp
-firecrawl-mcp-hosted
-dealroom-mcp
-google_drive</t>
-        </is>
-      </c>
-      <c r="J7" s="15" t="inlineStr">
-        <is>
-          <t>screen-inbound-opportunity</t>
-        </is>
-      </c>
-      <c r="K7" s="15" t="inlineStr">
+affinity-mcp-server</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>vc-pack-variable-discovery</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
         <is>
           <t>setup</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="135" customHeight="1" s="12">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>Alex</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
+    <row r="9" ht="18" customHeight="1" s="12">
+      <c r="A9" s="15" t="inlineStr"/>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="D8" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
-        <v/>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>Capture source context, known fields, missing information, and guided project-creation values for one venture-capital opportunity before formal screening.</t>
-        </is>
-      </c>
-      <c r="F8" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-dealflow-concierge.md","Dealflow Concierge")</f>
-        <v/>
-      </c>
-      <c r="G8" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/company-research-and-enrichment/SKILL.md","Company Research &amp; Enrichment")</f>
-        <v/>
-      </c>
-      <c r="H8" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (style_guide)")</f>
-        <v/>
-      </c>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>alludium-platform
-harmonic-mcp-oauth
-affinity-mcp-server
-exa-mcp-hosted
-brave-search-mcp
-serpapi-mcp
-firecrawl-mcp-hosted
-dealroom-mcp
-google_drive</t>
-        </is>
-      </c>
-      <c r="J8" s="15" t="inlineStr">
-        <is>
-          <t>screen-inbound-opportunity</t>
-        </is>
-      </c>
-      <c r="K8" s="15" t="inlineStr">
+      <c r="D9" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-setup.md","Set Up Affinity for Deal Pipelines")</f>
+        <v/>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>Coordinate Affinity connection readiness, list discovery, read-preview policy, and optional write-back proposal scope for Deal Pipeline setup.</t>
+        </is>
+      </c>
+      <c r="F9" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
+        <v/>
+      </c>
+      <c r="G9" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-discovery/SKILL.md","VC Affinity Discovery")</f>
+        <v/>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>affinity-mcp-server</t>
+        </is>
+      </c>
+      <c r="J9" s="15" t="inlineStr">
+        <is>
+          <t>affinity-setup</t>
+        </is>
+      </c>
+      <c r="K9" s="15" t="inlineStr">
         <is>
           <t>setup</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="135" customHeight="1" s="12">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>Alex</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
+    <row r="10" ht="18" customHeight="1" s="12">
+      <c r="A10" s="15" t="inlineStr"/>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="D9" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
-        <v/>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>Capture source context, known fields, missing information, and guided project-creation values for one venture-capital opportunity before formal screening.</t>
-        </is>
-      </c>
-      <c r="F9" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-dealflow-concierge.md","Dealflow Concierge")</f>
-        <v/>
-      </c>
-      <c r="G9" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
-        <v/>
-      </c>
-      <c r="H9" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
-        <v/>
-      </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>alludium-platform
-harmonic-mcp-oauth
-affinity-mcp-server
-exa-mcp-hosted
-brave-search-mcp
-serpapi-mcp
-firecrawl-mcp-hosted
-dealroom-mcp
-google_drive</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>screen-inbound-opportunity</t>
-        </is>
-      </c>
-      <c r="K9" s="15" t="inlineStr">
-        <is>
-          <t>setup</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="135" customHeight="1" s="12">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Alex</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>Setup</t>
-        </is>
-      </c>
       <c r="D10" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-setup.md","Set Up Affinity for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>Capture source context, known fields, missing information, and guided project-creation values for one venture-capital opportunity before formal screening.</t>
+          <t>Coordinate Affinity connection readiness, list discovery, read-preview policy, and optional write-back proposal scope for Deal Pipeline setup.</t>
         </is>
       </c>
       <c r="F10" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-dealflow-concierge.md","Dealflow Concierge")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/pitch-deck-explainer/SKILL.md","Pitch Deck Explainer")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-sync-read/SKILL.md","VC Affinity Sync Read")</f>
         <v/>
       </c>
       <c r="H10" s="15" t="inlineStr"/>
       <c r="I10" s="15" t="inlineStr">
         <is>
-          <t>alludium-platform
-harmonic-mcp-oauth
-affinity-mcp-server
-exa-mcp-hosted
-brave-search-mcp
-serpapi-mcp
-firecrawl-mcp-hosted
-dealroom-mcp
-google_drive</t>
+          <t>affinity-mcp-server</t>
         </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
-          <t>screen-inbound-opportunity</t>
+          <t>affinity-setup</t>
         </is>
       </c>
       <c r="K10" s="15" t="inlineStr">
@@ -1123,38 +1082,32 @@
           <t>Setup</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>Project Source Setup</t>
-        </is>
+      <c r="D11" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-setup.md","Set Up Affinity for Deal Pipelines")</f>
+        <v/>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>Review selected source route and setup intent before writes or imports.</t>
+          <t>Coordinate Affinity connection readiness, list discovery, read-preview policy, and optional write-back proposal scope for Deal Pipeline setup.</t>
         </is>
       </c>
       <c r="F11" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-deal-room-setup-guide.md","Deal Pipeline Setup Guide")</f>
-        <v/>
-      </c>
-      <c r="G11" s="15" t="inlineStr">
-        <is>
-          <t>None declared</t>
-        </is>
-      </c>
-      <c r="H11" s="15" t="inlineStr">
-        <is>
-          <t>None declared</t>
-        </is>
-      </c>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
+        <v/>
+      </c>
+      <c r="G11" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-sync-write/SKILL.md","VC Affinity Sync Write")</f>
+        <v/>
+      </c>
+      <c r="H11" s="15" t="inlineStr"/>
       <c r="I11" s="15" t="inlineStr">
         <is>
-          <t>None declared</t>
+          <t>affinity-mcp-server</t>
         </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
-          <t>project-source-setup</t>
+          <t>affinity-setup</t>
         </is>
       </c>
       <c r="K11" s="15" t="inlineStr">
@@ -1163,7 +1116,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" s="12">
+    <row r="12" ht="18" customHeight="1" s="12">
       <c r="A12" s="15" t="inlineStr"/>
       <c r="B12" s="15" t="inlineStr">
         <is>
@@ -1176,37 +1129,31 @@
         </is>
       </c>
       <c r="D12" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/vc-pack-variable-discovery.md","VC Pack Variable Discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-setup.md","Set Up Affinity for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>Best-effort, review-only discovery for VC Pack Setup variables and invite suggestions.</t>
+          <t>Coordinate Affinity connection readiness, list discovery, read-preview policy, and optional write-back proposal scope for Deal Pipeline setup.</t>
         </is>
       </c>
       <c r="F12" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-deal-room-setup-guide.md","Deal Pipeline Setup Guide")</f>
-        <v/>
-      </c>
-      <c r="G12" s="15" t="inlineStr">
-        <is>
-          <t>None declared</t>
-        </is>
-      </c>
-      <c r="H12" s="15" t="inlineStr">
-        <is>
-          <t>None declared</t>
-        </is>
-      </c>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
+        <v/>
+      </c>
+      <c r="G12" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
+        <v/>
+      </c>
+      <c r="H12" s="15" t="inlineStr"/>
       <c r="I12" s="15" t="inlineStr">
         <is>
-          <t>alludium-platform
-affinity-mcp-server</t>
+          <t>affinity-mcp-server</t>
         </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
-          <t>vc-pack-variable-discovery</t>
+          <t>affinity-setup</t>
         </is>
       </c>
       <c r="K12" s="15" t="inlineStr">
@@ -1215,7 +1162,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1" s="12">
+    <row r="13" ht="30" customHeight="1" s="12">
       <c r="A13" s="15" t="inlineStr"/>
       <c r="B13" s="15" t="inlineStr">
         <is>
@@ -1228,20 +1175,20 @@
         </is>
       </c>
       <c r="D13" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-setup.md","Set Up Affinity for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-deal-room-import.md","Import Affinity Deal Pipeline Seed")</f>
         <v/>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>Coordinate Affinity connection readiness, list discovery, read-preview policy, and optional write-back proposal scope for Deal Pipeline setup.</t>
+          <t>Import one approved Affinity seed deal into an already-created Deal Pipeline project with source provenance and approval evidence.</t>
         </is>
       </c>
       <c r="F13" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-deal-room-setup-guide.md","Deal Pipeline Setup Guide")</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-discovery/SKILL.md","VC Affinity Discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-deal-room-import/SKILL.md","VC Affinity Deal Pipeline Import")</f>
         <v/>
       </c>
       <c r="H13" s="15" t="inlineStr">
@@ -1251,12 +1198,13 @@
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
-          <t>affinity-mcp-server</t>
+          <t>affinity-mcp-server
+alludium-platform</t>
         </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
-          <t>affinity-setup</t>
+          <t>affinity-deal-room-import</t>
         </is>
       </c>
       <c r="K13" s="15" t="inlineStr">
@@ -1265,7 +1213,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1" s="12">
+    <row r="14" ht="30" customHeight="1" s="12">
       <c r="A14" s="15" t="inlineStr"/>
       <c r="B14" s="15" t="inlineStr">
         <is>
@@ -1278,16 +1226,16 @@
         </is>
       </c>
       <c r="D14" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-setup.md","Set Up Affinity for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-deal-room-import.md","Import Affinity Deal Pipeline Seed")</f>
         <v/>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>Coordinate Affinity connection readiness, list discovery, read-preview policy, and optional write-back proposal scope for Deal Pipeline setup.</t>
+          <t>Import one approved Affinity seed deal into an already-created Deal Pipeline project with source provenance and approval evidence.</t>
         </is>
       </c>
       <c r="F14" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-deal-room-setup-guide.md","Deal Pipeline Setup Guide")</f>
         <v/>
       </c>
       <c r="G14" s="16">
@@ -1297,12 +1245,13 @@
       <c r="H14" s="15" t="inlineStr"/>
       <c r="I14" s="15" t="inlineStr">
         <is>
-          <t>affinity-mcp-server</t>
+          <t>affinity-mcp-server
+alludium-platform</t>
         </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>affinity-setup</t>
+          <t>affinity-deal-room-import</t>
         </is>
       </c>
       <c r="K14" s="15" t="inlineStr">
@@ -1311,7 +1260,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1" s="12">
+    <row r="15" ht="30" customHeight="1" s="12">
       <c r="A15" s="15" t="inlineStr"/>
       <c r="B15" s="15" t="inlineStr">
         <is>
@@ -1324,31 +1273,32 @@
         </is>
       </c>
       <c r="D15" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-setup.md","Set Up Affinity for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-deal-room-import.md","Import Affinity Deal Pipeline Seed")</f>
         <v/>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>Coordinate Affinity connection readiness, list discovery, read-preview policy, and optional write-back proposal scope for Deal Pipeline setup.</t>
+          <t>Import one approved Affinity seed deal into an already-created Deal Pipeline project with source provenance and approval evidence.</t>
         </is>
       </c>
       <c r="F15" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-deal-room-setup-guide.md","Deal Pipeline Setup Guide")</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-sync-write/SKILL.md","VC Affinity Sync Write")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/deal-room-setup-and-source-ingestion/SKILL.md","Deal Pipeline Setup &amp; Source Ingestion")</f>
         <v/>
       </c>
       <c r="H15" s="15" t="inlineStr"/>
       <c r="I15" s="15" t="inlineStr">
         <is>
-          <t>affinity-mcp-server</t>
+          <t>affinity-mcp-server
+alludium-platform</t>
         </is>
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
-          <t>affinity-setup</t>
+          <t>affinity-deal-room-import</t>
         </is>
       </c>
       <c r="K15" s="15" t="inlineStr">
@@ -1357,7 +1307,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1" s="12">
+    <row r="16" ht="30" customHeight="1" s="12">
       <c r="A16" s="15" t="inlineStr"/>
       <c r="B16" s="15" t="inlineStr">
         <is>
@@ -1370,16 +1320,16 @@
         </is>
       </c>
       <c r="D16" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-setup.md","Set Up Affinity for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-deal-room-import.md","Import Affinity Deal Pipeline Seed")</f>
         <v/>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>Coordinate Affinity connection readiness, list discovery, read-preview policy, and optional write-back proposal scope for Deal Pipeline setup.</t>
+          <t>Import one approved Affinity seed deal into an already-created Deal Pipeline project with source provenance and approval evidence.</t>
         </is>
       </c>
       <c r="F16" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-deal-room-setup-guide.md","Deal Pipeline Setup Guide")</f>
         <v/>
       </c>
       <c r="G16" s="16">
@@ -1389,12 +1339,13 @@
       <c r="H16" s="15" t="inlineStr"/>
       <c r="I16" s="15" t="inlineStr">
         <is>
-          <t>affinity-mcp-server</t>
+          <t>affinity-mcp-server
+alludium-platform</t>
         </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
-          <t>affinity-setup</t>
+          <t>affinity-deal-room-import</t>
         </is>
       </c>
       <c r="K16" s="15" t="inlineStr">
@@ -1403,7 +1354,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" s="12">
+    <row r="17" ht="150" customHeight="1" s="12">
       <c r="A17" s="15" t="inlineStr"/>
       <c r="B17" s="15" t="inlineStr">
         <is>
@@ -1412,223 +1363,31 @@
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>General</t>
         </is>
       </c>
       <c r="D17" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-deal-room-import.md","Import Affinity Deal Pipeline Seed")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-call.md","Prepare Meeting")</f>
         <v/>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>Import one approved Affinity seed deal into an already-created Deal Pipeline project with source provenance and approval evidence.</t>
+          <t>Prepare a founder, management, advisor, customer, expert, partner, IC, legal, or closing meeting for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
       <c r="F17" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-deal-room-setup-guide.md","Deal Pipeline Setup Guide")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-meeting-operator.md","Meeting Operator")</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-deal-room-import/SKILL.md","VC Affinity Deal Pipeline Import")</f>
-        <v/>
-      </c>
-      <c r="H17" s="15" t="inlineStr">
-        <is>
-          <t>None declared</t>
-        </is>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/meeting-prep-and-summary/SKILL.md","Meeting Prep &amp; Summary")</f>
+        <v/>
+      </c>
+      <c r="H17" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/initial-call-brief-template.md","Initial Call Brief Template (output_template, to initial_call_brief_artifact_id)")</f>
+        <v/>
       </c>
       <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>affinity-mcp-server
-alludium-platform</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>affinity-deal-room-import</t>
-        </is>
-      </c>
-      <c r="K17" s="15" t="inlineStr">
-        <is>
-          <t>setup</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1" s="12">
-      <c r="A18" s="15" t="inlineStr"/>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>Setup</t>
-        </is>
-      </c>
-      <c r="D18" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-deal-room-import.md","Import Affinity Deal Pipeline Seed")</f>
-        <v/>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>Import one approved Affinity seed deal into an already-created Deal Pipeline project with source provenance and approval evidence.</t>
-        </is>
-      </c>
-      <c r="F18" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-deal-room-setup-guide.md","Deal Pipeline Setup Guide")</f>
-        <v/>
-      </c>
-      <c r="G18" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-sync-read/SKILL.md","VC Affinity Sync Read")</f>
-        <v/>
-      </c>
-      <c r="H18" s="15" t="inlineStr"/>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>affinity-mcp-server
-alludium-platform</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>affinity-deal-room-import</t>
-        </is>
-      </c>
-      <c r="K18" s="15" t="inlineStr">
-        <is>
-          <t>setup</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1" s="12">
-      <c r="A19" s="15" t="inlineStr"/>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C19" s="15" t="inlineStr">
-        <is>
-          <t>Setup</t>
-        </is>
-      </c>
-      <c r="D19" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-deal-room-import.md","Import Affinity Deal Pipeline Seed")</f>
-        <v/>
-      </c>
-      <c r="E19" s="15" t="inlineStr">
-        <is>
-          <t>Import one approved Affinity seed deal into an already-created Deal Pipeline project with source provenance and approval evidence.</t>
-        </is>
-      </c>
-      <c r="F19" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-deal-room-setup-guide.md","Deal Pipeline Setup Guide")</f>
-        <v/>
-      </c>
-      <c r="G19" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/deal-room-setup-and-source-ingestion/SKILL.md","Deal Pipeline Setup &amp; Source Ingestion")</f>
-        <v/>
-      </c>
-      <c r="H19" s="15" t="inlineStr"/>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>affinity-mcp-server
-alludium-platform</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>affinity-deal-room-import</t>
-        </is>
-      </c>
-      <c r="K19" s="15" t="inlineStr">
-        <is>
-          <t>setup</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1" s="12">
-      <c r="A20" s="15" t="inlineStr"/>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>Setup</t>
-        </is>
-      </c>
-      <c r="D20" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-deal-room-import.md","Import Affinity Deal Pipeline Seed")</f>
-        <v/>
-      </c>
-      <c r="E20" s="15" t="inlineStr">
-        <is>
-          <t>Import one approved Affinity seed deal into an already-created Deal Pipeline project with source provenance and approval evidence.</t>
-        </is>
-      </c>
-      <c r="F20" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-deal-room-setup-guide.md","Deal Pipeline Setup Guide")</f>
-        <v/>
-      </c>
-      <c r="G20" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
-        <v/>
-      </c>
-      <c r="H20" s="15" t="inlineStr"/>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>affinity-mcp-server
-alludium-platform</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>affinity-deal-room-import</t>
-        </is>
-      </c>
-      <c r="K20" s="15" t="inlineStr">
-        <is>
-          <t>setup</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="150" customHeight="1" s="12">
-      <c r="A21" s="15" t="inlineStr"/>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D21" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-call.md","Prepare Meeting")</f>
-        <v/>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>Prepare a founder, management, advisor, customer, expert, partner, IC, legal, or closing meeting for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
-        </is>
-      </c>
-      <c r="F21" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-meeting-operator.md","Meeting Operator")</f>
-        <v/>
-      </c>
-      <c r="G21" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/meeting-prep-and-summary/SKILL.md","Meeting Prep &amp; Summary")</f>
-        <v/>
-      </c>
-      <c r="H21" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/initial-call-brief-template.md","Initial Call Brief Template (output_template, to initial_call_brief_artifact_id)")</f>
-        <v/>
-      </c>
-      <c r="I21" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -1642,51 +1401,51 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J21" s="15" t="inlineStr">
+      <c r="J17" s="15" t="inlineStr">
         <is>
           <t>prepare-initial-call</t>
         </is>
       </c>
-      <c r="K21" s="15" t="inlineStr">
+      <c r="K17" s="15" t="inlineStr">
         <is>
           <t>general</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="150" customHeight="1" s="12">
-      <c r="A22" s="15" t="inlineStr"/>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
+    <row r="18" ht="150" customHeight="1" s="12">
+      <c r="A18" s="15" t="inlineStr"/>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D22" s="16">
+      <c r="D18" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-call.md","Prepare Meeting")</f>
         <v/>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>Prepare a founder, management, advisor, customer, expert, partner, IC, legal, or closing meeting for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F22" s="16">
+      <c r="F18" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-meeting-operator.md","Meeting Operator")</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G18" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/company-research-and-enrichment/SKILL.md","Company Research &amp; Enrichment")</f>
         <v/>
       </c>
-      <c r="H22" s="16">
+      <c r="H18" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (style_guide)")</f>
         <v/>
       </c>
-      <c r="I22" s="15" t="inlineStr">
+      <c r="I18" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -1700,51 +1459,51 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J22" s="15" t="inlineStr">
+      <c r="J18" s="15" t="inlineStr">
         <is>
           <t>prepare-initial-call</t>
         </is>
       </c>
-      <c r="K22" s="15" t="inlineStr">
+      <c r="K18" s="15" t="inlineStr">
         <is>
           <t>general</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="150" customHeight="1" s="12">
-      <c r="A23" s="15" t="inlineStr"/>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="inlineStr">
+    <row r="19" ht="150" customHeight="1" s="12">
+      <c r="A19" s="15" t="inlineStr"/>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D23" s="16">
+      <c r="D19" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-call.md","Prepare Meeting")</f>
         <v/>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>Prepare a founder, management, advisor, customer, expert, partner, IC, legal, or closing meeting for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F23" s="16">
+      <c r="F19" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-meeting-operator.md","Meeting Operator")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G19" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
         <v/>
       </c>
-      <c r="H23" s="16">
+      <c r="H19" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
         <v/>
       </c>
-      <c r="I23" s="15" t="inlineStr">
+      <c r="I19" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -1758,48 +1517,48 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J23" s="15" t="inlineStr">
+      <c r="J19" s="15" t="inlineStr">
         <is>
           <t>prepare-initial-call</t>
         </is>
       </c>
-      <c r="K23" s="15" t="inlineStr">
+      <c r="K19" s="15" t="inlineStr">
         <is>
           <t>general</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="150" customHeight="1" s="12">
-      <c r="A24" s="15" t="inlineStr"/>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
+    <row r="20" ht="150" customHeight="1" s="12">
+      <c r="A20" s="15" t="inlineStr"/>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D24" s="16">
+      <c r="D20" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-call.md","Prepare Meeting")</f>
         <v/>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>Prepare a founder, management, advisor, customer, expert, partner, IC, legal, or closing meeting for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F24" s="16">
+      <c r="F20" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-meeting-operator.md","Meeting Operator")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G20" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/pitch-deck-explainer/SKILL.md","Pitch Deck Explainer")</f>
         <v/>
       </c>
-      <c r="H24" s="15" t="inlineStr"/>
-      <c r="I24" s="15" t="inlineStr">
+      <c r="H20" s="15" t="inlineStr"/>
+      <c r="I20" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -1813,55 +1572,55 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J24" s="15" t="inlineStr">
+      <c r="J20" s="15" t="inlineStr">
         <is>
           <t>prepare-initial-call</t>
         </is>
       </c>
-      <c r="K24" s="15" t="inlineStr">
+      <c r="K20" s="15" t="inlineStr">
         <is>
           <t>general</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="135" customHeight="1" s="12">
-      <c r="A25" s="15" t="inlineStr">
+    <row r="21" ht="135" customHeight="1" s="12">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D25" s="16">
+      <c r="D21" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/request-founder-materials.md","Request Founder Materials")</f>
         <v/>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>Request Founder Materials for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F25" s="16">
+      <c r="F21" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-dealflow-concierge.md","Dealflow Concierge")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G21" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
         <v/>
       </c>
-      <c r="H25" s="16">
+      <c r="H21" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/founder-materials-request-template.md","Founder Materials Request Template (output_template, to founder_materials_request_artifact_id)")</f>
         <v/>
       </c>
-      <c r="I25" s="15" t="inlineStr">
+      <c r="I21" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -1874,55 +1633,55 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J25" s="15" t="inlineStr">
+      <c r="J21" s="15" t="inlineStr">
         <is>
           <t>request-founder-materials</t>
         </is>
       </c>
-      <c r="K25" s="15" t="inlineStr">
+      <c r="K21" s="15" t="inlineStr">
         <is>
           <t>general</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="135" customHeight="1" s="12">
-      <c r="A26" s="15" t="inlineStr">
+    <row r="22" ht="135" customHeight="1" s="12">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D26" s="16">
+      <c r="D22" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/request-founder-materials.md","Request Founder Materials")</f>
         <v/>
       </c>
-      <c r="E26" s="15" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>Request Founder Materials for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F26" s="16">
+      <c r="F22" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-dealflow-concierge.md","Dealflow Concierge")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G22" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/founder-materials-request/SKILL.md","Founder Materials Request")</f>
         <v/>
       </c>
-      <c r="H26" s="16">
+      <c r="H22" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/file-naming-source-index-sop.md","File Naming And Source Index SOP (operating_guidance)")</f>
         <v/>
       </c>
-      <c r="I26" s="15" t="inlineStr">
+      <c r="I22" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -1935,52 +1694,52 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J26" s="15" t="inlineStr">
+      <c r="J22" s="15" t="inlineStr">
         <is>
           <t>request-founder-materials</t>
         </is>
       </c>
-      <c r="K26" s="15" t="inlineStr">
+      <c r="K22" s="15" t="inlineStr">
         <is>
           <t>general</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="135" customHeight="1" s="12">
-      <c r="A27" s="15" t="inlineStr">
+    <row r="23" ht="135" customHeight="1" s="12">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D27" s="16">
+      <c r="D23" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/request-founder-materials.md","Request Founder Materials")</f>
         <v/>
       </c>
-      <c r="E27" s="15" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>Request Founder Materials for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F27" s="16">
+      <c r="F23" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-dealflow-concierge.md","Dealflow Concierge")</f>
         <v/>
       </c>
-      <c r="G27" s="15" t="inlineStr"/>
-      <c r="H27" s="16">
+      <c r="G23" s="15" t="inlineStr"/>
+      <c r="H23" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
         <v/>
       </c>
-      <c r="I27" s="15" t="inlineStr">
+      <c r="I23" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -1993,55 +1752,55 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J27" s="15" t="inlineStr">
+      <c r="J23" s="15" t="inlineStr">
         <is>
           <t>request-founder-materials</t>
         </is>
       </c>
-      <c r="K27" s="15" t="inlineStr">
+      <c r="K23" s="15" t="inlineStr">
         <is>
           <t>general</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="150" customHeight="1" s="12">
-      <c r="A28" s="15" t="inlineStr">
+    <row r="24" ht="150" customHeight="1" s="12">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D28" s="16">
+      <c r="D24" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/summarize-initial-call.md","Summarize Meeting Records")</f>
         <v/>
       </c>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>Summarize or ingest meeting records for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F28" s="16">
+      <c r="F24" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-meeting-operator.md","Meeting Operator")</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G24" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/meeting-prep-and-summary/SKILL.md","Meeting Prep &amp; Summary")</f>
         <v/>
       </c>
-      <c r="H28" s="16">
+      <c r="H24" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/customer-insights-summary-template.md","Customer Insights Summary Template (output_template, to customer_insights_artifact_id)")</f>
         <v/>
       </c>
-      <c r="I28" s="15" t="inlineStr">
+      <c r="I24" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -2055,55 +1814,55 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J28" s="15" t="inlineStr">
+      <c r="J24" s="15" t="inlineStr">
         <is>
           <t>summarize-initial-call</t>
         </is>
       </c>
-      <c r="K28" s="15" t="inlineStr">
+      <c r="K24" s="15" t="inlineStr">
         <is>
           <t>general</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="150" customHeight="1" s="12">
-      <c r="A29" s="15" t="inlineStr">
+    <row r="25" ht="150" customHeight="1" s="12">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D29" s="16">
+      <c r="D25" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/summarize-initial-call.md","Summarize Meeting Records")</f>
         <v/>
       </c>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>Summarize or ingest meeting records for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F29" s="16">
+      <c r="F25" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-meeting-operator.md","Meeting Operator")</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G25" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
         <v/>
       </c>
-      <c r="H29" s="16">
+      <c r="H25" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (style_guide)")</f>
         <v/>
       </c>
-      <c r="I29" s="15" t="inlineStr">
+      <c r="I25" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -2117,55 +1876,55 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J29" s="15" t="inlineStr">
+      <c r="J25" s="15" t="inlineStr">
         <is>
           <t>summarize-initial-call</t>
         </is>
       </c>
-      <c r="K29" s="15" t="inlineStr">
+      <c r="K25" s="15" t="inlineStr">
         <is>
           <t>general</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="150" customHeight="1" s="12">
-      <c r="A30" s="15" t="inlineStr">
+    <row r="26" ht="150" customHeight="1" s="12">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D30" s="16">
+      <c r="D26" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/summarize-initial-call.md","Summarize Meeting Records")</f>
         <v/>
       </c>
-      <c r="E30" s="15" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>Summarize or ingest meeting records for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F30" s="16">
+      <c r="F26" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-meeting-operator.md","Meeting Operator")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G26" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-task-and-next-step-generation/SKILL.md","VC Task &amp; Next-Step Generation")</f>
         <v/>
       </c>
-      <c r="H30" s="16">
+      <c r="H26" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
         <v/>
       </c>
-      <c r="I30" s="15" t="inlineStr">
+      <c r="I26" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 harmonic-mcp-oauth
@@ -2179,51 +1938,51 @@
 google_drive</t>
         </is>
       </c>
-      <c r="J30" s="15" t="inlineStr">
+      <c r="J26" s="15" t="inlineStr">
         <is>
           <t>summarize-initial-call</t>
         </is>
       </c>
-      <c r="K30" s="15" t="inlineStr">
+      <c r="K26" s="15" t="inlineStr">
         <is>
           <t>general</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="90" customHeight="1" s="12">
-      <c r="A31" s="15" t="inlineStr"/>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C31" s="15" t="inlineStr">
+    <row r="27" ht="90" customHeight="1" s="12">
+      <c r="A27" s="15" t="inlineStr"/>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D31" s="16">
+      <c r="D27" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-opportunity-status.md","Review Opportunity Status")</f>
         <v/>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>Review the current status of one venture-capital opportunity and suggest missing inputs, stage movement, and next tasks without producing a formal investment evaluation document.</t>
         </is>
       </c>
-      <c r="F31" s="16">
+      <c r="F27" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-pipeline-autopilot.md","Pipeline Autopilot")</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G27" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
         <v/>
       </c>
-      <c r="H31" s="16">
+      <c r="H27" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/deal-room-sop.md","Deal Pipeline Operating SOP (operating_guidance)")</f>
         <v/>
       </c>
-      <c r="I31" s="15" t="inlineStr">
+      <c r="I27" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -2233,51 +1992,51 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J31" s="15" t="inlineStr">
+      <c r="J27" s="15" t="inlineStr">
         <is>
           <t>review-opportunity-status</t>
         </is>
       </c>
-      <c r="K31" s="15" t="inlineStr">
+      <c r="K27" s="15" t="inlineStr">
         <is>
           <t>general</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="90" customHeight="1" s="12">
-      <c r="A32" s="15" t="inlineStr"/>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
+    <row r="28" ht="90" customHeight="1" s="12">
+      <c r="A28" s="15" t="inlineStr"/>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D32" s="16">
+      <c r="D28" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-opportunity-status.md","Review Opportunity Status")</f>
         <v/>
       </c>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>Review the current status of one venture-capital opportunity and suggest missing inputs, stage movement, and next tasks without producing a formal investment evaluation document.</t>
         </is>
       </c>
-      <c r="F32" s="16">
+      <c r="F28" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-pipeline-autopilot.md","Pipeline Autopilot")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G28" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-task-and-next-step-generation/SKILL.md","VC Task &amp; Next-Step Generation")</f>
         <v/>
       </c>
-      <c r="H32" s="16">
+      <c r="H28" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/opportunity-evaluation-framework.md","Opportunity Evaluation Framework (methodology)")</f>
         <v/>
       </c>
-      <c r="I32" s="15" t="inlineStr">
+      <c r="I28" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -2287,48 +2046,48 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J32" s="15" t="inlineStr">
+      <c r="J28" s="15" t="inlineStr">
         <is>
           <t>review-opportunity-status</t>
         </is>
       </c>
-      <c r="K32" s="15" t="inlineStr">
+      <c r="K28" s="15" t="inlineStr">
         <is>
           <t>general</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="90" customHeight="1" s="12">
-      <c r="A33" s="15" t="inlineStr"/>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C33" s="15" t="inlineStr">
+    <row r="29" ht="90" customHeight="1" s="12">
+      <c r="A29" s="15" t="inlineStr"/>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D33" s="16">
+      <c r="D29" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-opportunity-status.md","Review Opportunity Status")</f>
         <v/>
       </c>
-      <c r="E33" s="15" t="inlineStr">
+      <c r="E29" s="15" t="inlineStr">
         <is>
           <t>Review the current status of one venture-capital opportunity and suggest missing inputs, stage movement, and next tasks without producing a formal investment evaluation document.</t>
         </is>
       </c>
-      <c r="F33" s="16">
+      <c r="F29" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-pipeline-autopilot.md","Pipeline Autopilot")</f>
         <v/>
       </c>
-      <c r="G33" s="15" t="inlineStr"/>
-      <c r="H33" s="16">
+      <c r="G29" s="15" t="inlineStr"/>
+      <c r="H29" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evaluation-workstream-guide.md","Evaluation Workstream Guide (methodology)")</f>
         <v/>
       </c>
-      <c r="I33" s="15" t="inlineStr">
+      <c r="I29" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -2338,48 +2097,48 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J33" s="15" t="inlineStr">
+      <c r="J29" s="15" t="inlineStr">
         <is>
           <t>review-opportunity-status</t>
         </is>
       </c>
-      <c r="K33" s="15" t="inlineStr">
+      <c r="K29" s="15" t="inlineStr">
         <is>
           <t>general</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="90" customHeight="1" s="12">
-      <c r="A34" s="15" t="inlineStr"/>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
+    <row r="30" ht="90" customHeight="1" s="12">
+      <c r="A30" s="15" t="inlineStr"/>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D34" s="16">
+      <c r="D30" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-opportunity-status.md","Review Opportunity Status")</f>
         <v/>
       </c>
-      <c r="E34" s="15" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>Review the current status of one venture-capital opportunity and suggest missing inputs, stage movement, and next tasks without producing a formal investment evaluation document.</t>
         </is>
       </c>
-      <c r="F34" s="16">
+      <c r="F30" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-pipeline-autopilot.md","Pipeline Autopilot")</f>
         <v/>
       </c>
-      <c r="G34" s="15" t="inlineStr"/>
-      <c r="H34" s="16">
+      <c r="G30" s="15" t="inlineStr"/>
+      <c r="H30" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (style_guide)")</f>
         <v/>
       </c>
-      <c r="I34" s="15" t="inlineStr">
+      <c r="I30" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -2389,48 +2148,48 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J34" s="15" t="inlineStr">
+      <c r="J30" s="15" t="inlineStr">
         <is>
           <t>review-opportunity-status</t>
         </is>
       </c>
-      <c r="K34" s="15" t="inlineStr">
+      <c r="K30" s="15" t="inlineStr">
         <is>
           <t>general</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="90" customHeight="1" s="12">
-      <c r="A35" s="15" t="inlineStr"/>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="inlineStr">
+    <row r="31" ht="90" customHeight="1" s="12">
+      <c r="A31" s="15" t="inlineStr"/>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D35" s="16">
+      <c r="D31" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-opportunity-status.md","Review Opportunity Status")</f>
         <v/>
       </c>
-      <c r="E35" s="15" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
         <is>
           <t>Review the current status of one venture-capital opportunity and suggest missing inputs, stage movement, and next tasks without producing a formal investment evaluation document.</t>
         </is>
       </c>
-      <c r="F35" s="16">
+      <c r="F31" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-pipeline-autopilot.md","Pipeline Autopilot")</f>
         <v/>
       </c>
-      <c r="G35" s="15" t="inlineStr"/>
-      <c r="H35" s="16">
+      <c r="G31" s="15" t="inlineStr"/>
+      <c r="H31" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
         <v/>
       </c>
-      <c r="I35" s="15" t="inlineStr">
+      <c r="I31" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -2440,14 +2199,206 @@
 dealroom-mcp</t>
         </is>
       </c>
+      <c r="J31" s="15" t="inlineStr">
+        <is>
+          <t>review-opportunity-status</t>
+        </is>
+      </c>
+      <c r="K31" s="15" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" s="12">
+      <c r="A32" s="15" t="inlineStr"/>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Integration Support</t>
+        </is>
+      </c>
+      <c r="D32" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-sync-read.md","Preview Affinity Pipeline Import")</f>
+        <v/>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>Preview selected Affinity opportunity, company, person, note, and list-entry data before importing it into Deal Pipeline context.</t>
+        </is>
+      </c>
+      <c r="F32" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
+        <v/>
+      </c>
+      <c r="G32" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-sync-read/SKILL.md","VC Affinity Sync Read")</f>
+        <v/>
+      </c>
+      <c r="H32" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="J32" s="15" t="inlineStr">
+        <is>
+          <t>affinity-sync-read</t>
+        </is>
+      </c>
+      <c r="K32" s="15" t="inlineStr">
+        <is>
+          <t>project_management</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1" s="12">
+      <c r="A33" s="15" t="inlineStr"/>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Integration Support</t>
+        </is>
+      </c>
+      <c r="D33" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-sync-read.md","Preview Affinity Pipeline Import")</f>
+        <v/>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>Preview selected Affinity opportunity, company, person, note, and list-entry data before importing it into Deal Pipeline context.</t>
+        </is>
+      </c>
+      <c r="F33" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
+        <v/>
+      </c>
+      <c r="G33" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
+        <v/>
+      </c>
+      <c r="H33" s="15" t="inlineStr"/>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="J33" s="15" t="inlineStr">
+        <is>
+          <t>affinity-sync-read</t>
+        </is>
+      </c>
+      <c r="K33" s="15" t="inlineStr">
+        <is>
+          <t>project_management</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="12">
+      <c r="A34" s="15" t="inlineStr"/>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Integration Support</t>
+        </is>
+      </c>
+      <c r="D34" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-sync-write.md","Draft Affinity Write-Back Proposals")</f>
+        <v/>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>Draft reviewable Affinity note, field, and stage update proposals from VC task outputs.</t>
+        </is>
+      </c>
+      <c r="F34" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
+        <v/>
+      </c>
+      <c r="G34" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-sync-write/SKILL.md","VC Affinity Sync Write")</f>
+        <v/>
+      </c>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="J34" s="15" t="inlineStr">
+        <is>
+          <t>affinity-sync-write</t>
+        </is>
+      </c>
+      <c r="K34" s="15" t="inlineStr">
+        <is>
+          <t>project_management</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1" s="12">
+      <c r="A35" s="15" t="inlineStr"/>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>Integration Support</t>
+        </is>
+      </c>
+      <c r="D35" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-sync-write.md","Draft Affinity Write-Back Proposals")</f>
+        <v/>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>Draft reviewable Affinity note, field, and stage update proposals from VC task outputs.</t>
+        </is>
+      </c>
+      <c r="F35" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
+        <v/>
+      </c>
+      <c r="G35" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
+        <v/>
+      </c>
+      <c r="H35" s="15" t="inlineStr"/>
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
       <c r="J35" s="15" t="inlineStr">
         <is>
-          <t>review-opportunity-status</t>
+          <t>affinity-sync-write</t>
         </is>
       </c>
       <c r="K35" s="15" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>project_management</t>
         </is>
       </c>
     </row>
@@ -2464,12 +2415,12 @@
         </is>
       </c>
       <c r="D36" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-sync-read.md","Preview Affinity Pipeline Import")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-sync-write.md","Draft Google Drive File Proposals")</f>
         <v/>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>Preview selected Affinity opportunity, company, person, note, and list-entry data before importing it into Deal Pipeline context.</t>
+          <t>Draft reviewable Google Drive file or comment proposals from VC task outputs without performing broad Drive mutations.</t>
         </is>
       </c>
       <c r="F36" s="16">
@@ -2477,7 +2428,7 @@
         <v/>
       </c>
       <c r="G36" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-sync-read/SKILL.md","VC Affinity Sync Read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-sync-write/SKILL.md","VC Google Drive Sync Write")</f>
         <v/>
       </c>
       <c r="H36" s="15" t="inlineStr">
@@ -2492,7 +2443,7 @@
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
-          <t>affinity-sync-read</t>
+          <t>google-drive-sync-write</t>
         </is>
       </c>
       <c r="K36" s="15" t="inlineStr">
@@ -2514,12 +2465,12 @@
         </is>
       </c>
       <c r="D37" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-sync-read.md","Preview Affinity Pipeline Import")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-sync-write.md","Draft Google Drive File Proposals")</f>
         <v/>
       </c>
       <c r="E37" s="15" t="inlineStr">
         <is>
-          <t>Preview selected Affinity opportunity, company, person, note, and list-entry data before importing it into Deal Pipeline context.</t>
+          <t>Draft reviewable Google Drive file or comment proposals from VC task outputs without performing broad Drive mutations.</t>
         </is>
       </c>
       <c r="F37" s="16">
@@ -2538,7 +2489,7 @@
       </c>
       <c r="J37" s="15" t="inlineStr">
         <is>
-          <t>affinity-sync-read</t>
+          <t>google-drive-sync-write</t>
         </is>
       </c>
       <c r="K37" s="15" t="inlineStr">
@@ -2560,12 +2511,12 @@
         </is>
       </c>
       <c r="D38" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-sync-write.md","Draft Affinity Write-Back Proposals")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-sync-write.md","Draft Notion Update Proposals")</f>
         <v/>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>Draft reviewable Affinity note, field, and stage update proposals from VC task outputs.</t>
+          <t>Draft reviewable Notion page, database, or comment proposals from VC task outputs without performing broad workspace mutation.</t>
         </is>
       </c>
       <c r="F38" s="16">
@@ -2573,7 +2524,7 @@
         <v/>
       </c>
       <c r="G38" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-sync-write/SKILL.md","VC Affinity Sync Write")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-sync-write/SKILL.md","VC Notion Sync Write")</f>
         <v/>
       </c>
       <c r="H38" s="15" t="inlineStr">
@@ -2588,7 +2539,7 @@
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
-          <t>affinity-sync-write</t>
+          <t>notion-sync-write</t>
         </is>
       </c>
       <c r="K38" s="15" t="inlineStr">
@@ -2610,12 +2561,12 @@
         </is>
       </c>
       <c r="D39" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-sync-write.md","Draft Affinity Write-Back Proposals")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-sync-write.md","Draft Notion Update Proposals")</f>
         <v/>
       </c>
       <c r="E39" s="15" t="inlineStr">
         <is>
-          <t>Draft reviewable Affinity note, field, and stage update proposals from VC task outputs.</t>
+          <t>Draft reviewable Notion page, database, or comment proposals from VC task outputs without performing broad workspace mutation.</t>
         </is>
       </c>
       <c r="F39" s="16">
@@ -2634,7 +2585,7 @@
       </c>
       <c r="J39" s="15" t="inlineStr">
         <is>
-          <t>affinity-sync-write</t>
+          <t>notion-sync-write</t>
         </is>
       </c>
       <c r="K39" s="15" t="inlineStr">
@@ -2656,12 +2607,12 @@
         </is>
       </c>
       <c r="D40" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-sync-write.md","Draft Google Drive File Proposals")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-sync-write.md","Draft Slack Handoff Notifications")</f>
         <v/>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>Draft reviewable Google Drive file or comment proposals from VC task outputs without performing broad Drive mutations.</t>
+          <t>Draft approved Slack handoff notifications for VC workflows without broad posting.</t>
         </is>
       </c>
       <c r="F40" s="16">
@@ -2669,7 +2620,7 @@
         <v/>
       </c>
       <c r="G40" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-sync-write/SKILL.md","VC Google Drive Sync Write")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-sync-write/SKILL.md","VC Slack Sync Write")</f>
         <v/>
       </c>
       <c r="H40" s="15" t="inlineStr">
@@ -2684,7 +2635,7 @@
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
-          <t>google-drive-sync-write</t>
+          <t>slack-sync-write</t>
         </is>
       </c>
       <c r="K40" s="15" t="inlineStr">
@@ -2706,12 +2657,12 @@
         </is>
       </c>
       <c r="D41" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-sync-write.md","Draft Google Drive File Proposals")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-sync-write.md","Draft Slack Handoff Notifications")</f>
         <v/>
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>Draft reviewable Google Drive file or comment proposals from VC task outputs without performing broad Drive mutations.</t>
+          <t>Draft approved Slack handoff notifications for VC workflows without broad posting.</t>
         </is>
       </c>
       <c r="F41" s="16">
@@ -2730,7 +2681,7 @@
       </c>
       <c r="J41" s="15" t="inlineStr">
         <is>
-          <t>google-drive-sync-write</t>
+          <t>slack-sync-write</t>
         </is>
       </c>
       <c r="K41" s="15" t="inlineStr">
@@ -2752,12 +2703,12 @@
         </is>
       </c>
       <c r="D42" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-sync-write.md","Draft Notion Update Proposals")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-discovery.md","Explore Affinity Lists and Stages")</f>
         <v/>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>Draft reviewable Notion page, database, or comment proposals from VC task outputs without performing broad workspace mutation.</t>
+          <t>Discover Affinity list, stage, field, and object-count scope before Deal Pipeline import or sync.</t>
         </is>
       </c>
       <c r="F42" s="16">
@@ -2765,7 +2716,7 @@
         <v/>
       </c>
       <c r="G42" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-sync-write/SKILL.md","VC Notion Sync Write")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-discovery/SKILL.md","VC Affinity Discovery")</f>
         <v/>
       </c>
       <c r="H42" s="15" t="inlineStr">
@@ -2780,7 +2731,7 @@
       </c>
       <c r="J42" s="15" t="inlineStr">
         <is>
-          <t>notion-sync-write</t>
+          <t>affinity-discovery</t>
         </is>
       </c>
       <c r="K42" s="15" t="inlineStr">
@@ -2802,12 +2753,12 @@
         </is>
       </c>
       <c r="D43" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-sync-write.md","Draft Notion Update Proposals")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-discovery.md","Explore Affinity Lists and Stages")</f>
         <v/>
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>Draft reviewable Notion page, database, or comment proposals from VC task outputs without performing broad workspace mutation.</t>
+          <t>Discover Affinity list, stage, field, and object-count scope before Deal Pipeline import or sync.</t>
         </is>
       </c>
       <c r="F43" s="16">
@@ -2826,7 +2777,7 @@
       </c>
       <c r="J43" s="15" t="inlineStr">
         <is>
-          <t>notion-sync-write</t>
+          <t>affinity-discovery</t>
         </is>
       </c>
       <c r="K43" s="15" t="inlineStr">
@@ -2848,12 +2799,12 @@
         </is>
       </c>
       <c r="D44" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-sync-write.md","Draft Slack Handoff Notifications")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-discovery.md","Explore Google Drive Sources")</f>
         <v/>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>Draft approved Slack handoff notifications for VC workflows without broad posting.</t>
+          <t>Discover Google Drive shared drive, folder, and file scope before selected Deal Pipeline context reads.</t>
         </is>
       </c>
       <c r="F44" s="16">
@@ -2861,7 +2812,7 @@
         <v/>
       </c>
       <c r="G44" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-sync-write/SKILL.md","VC Slack Sync Write")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-discovery/SKILL.md","VC Google Drive Discovery")</f>
         <v/>
       </c>
       <c r="H44" s="15" t="inlineStr">
@@ -2876,7 +2827,7 @@
       </c>
       <c r="J44" s="15" t="inlineStr">
         <is>
-          <t>slack-sync-write</t>
+          <t>google-drive-discovery</t>
         </is>
       </c>
       <c r="K44" s="15" t="inlineStr">
@@ -2898,12 +2849,12 @@
         </is>
       </c>
       <c r="D45" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-sync-write.md","Draft Slack Handoff Notifications")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-discovery.md","Explore Google Drive Sources")</f>
         <v/>
       </c>
       <c r="E45" s="15" t="inlineStr">
         <is>
-          <t>Draft approved Slack handoff notifications for VC workflows without broad posting.</t>
+          <t>Discover Google Drive shared drive, folder, and file scope before selected Deal Pipeline context reads.</t>
         </is>
       </c>
       <c r="F45" s="16">
@@ -2922,7 +2873,7 @@
       </c>
       <c r="J45" s="15" t="inlineStr">
         <is>
-          <t>slack-sync-write</t>
+          <t>google-drive-discovery</t>
         </is>
       </c>
       <c r="K45" s="15" t="inlineStr">
@@ -2944,12 +2895,12 @@
         </is>
       </c>
       <c r="D46" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-discovery.md","Explore Affinity Lists and Stages")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-discovery.md","Explore Harmonic Source Scopes")</f>
         <v/>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>Discover Affinity list, stage, field, and object-count scope before Deal Pipeline import or sync.</t>
+          <t>Discover Harmonic saved searches, daily searches, and source scope before selected VC sourcing context reads.</t>
         </is>
       </c>
       <c r="F46" s="16">
@@ -2957,7 +2908,7 @@
         <v/>
       </c>
       <c r="G46" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-discovery/SKILL.md","VC Affinity Discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-harmonic-discovery/SKILL.md","VC Harmonic Discovery")</f>
         <v/>
       </c>
       <c r="H46" s="15" t="inlineStr">
@@ -2972,7 +2923,7 @@
       </c>
       <c r="J46" s="15" t="inlineStr">
         <is>
-          <t>affinity-discovery</t>
+          <t>harmonic-discovery</t>
         </is>
       </c>
       <c r="K46" s="15" t="inlineStr">
@@ -2994,12 +2945,12 @@
         </is>
       </c>
       <c r="D47" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-discovery.md","Explore Affinity Lists and Stages")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-discovery.md","Explore Harmonic Source Scopes")</f>
         <v/>
       </c>
       <c r="E47" s="15" t="inlineStr">
         <is>
-          <t>Discover Affinity list, stage, field, and object-count scope before Deal Pipeline import or sync.</t>
+          <t>Discover Harmonic saved searches, daily searches, and source scope before selected VC sourcing context reads.</t>
         </is>
       </c>
       <c r="F47" s="16">
@@ -3018,7 +2969,7 @@
       </c>
       <c r="J47" s="15" t="inlineStr">
         <is>
-          <t>affinity-discovery</t>
+          <t>harmonic-discovery</t>
         </is>
       </c>
       <c r="K47" s="15" t="inlineStr">
@@ -3040,12 +2991,12 @@
         </is>
       </c>
       <c r="D48" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-discovery.md","Explore Google Drive Sources")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-discovery.md","Explore Notion Pages and Databases")</f>
         <v/>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>Discover Google Drive shared drive, folder, and file scope before selected Deal Pipeline context reads.</t>
+          <t>Discover Notion page, database, and workspace scope before selected Deal Pipeline context reads.</t>
         </is>
       </c>
       <c r="F48" s="16">
@@ -3053,7 +3004,7 @@
         <v/>
       </c>
       <c r="G48" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-discovery/SKILL.md","VC Google Drive Discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-discovery/SKILL.md","VC Notion Discovery")</f>
         <v/>
       </c>
       <c r="H48" s="15" t="inlineStr">
@@ -3068,7 +3019,7 @@
       </c>
       <c r="J48" s="15" t="inlineStr">
         <is>
-          <t>google-drive-discovery</t>
+          <t>notion-discovery</t>
         </is>
       </c>
       <c r="K48" s="15" t="inlineStr">
@@ -3090,12 +3041,12 @@
         </is>
       </c>
       <c r="D49" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-discovery.md","Explore Google Drive Sources")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-discovery.md","Explore Notion Pages and Databases")</f>
         <v/>
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>Discover Google Drive shared drive, folder, and file scope before selected Deal Pipeline context reads.</t>
+          <t>Discover Notion page, database, and workspace scope before selected Deal Pipeline context reads.</t>
         </is>
       </c>
       <c r="F49" s="16">
@@ -3114,7 +3065,7 @@
       </c>
       <c r="J49" s="15" t="inlineStr">
         <is>
-          <t>google-drive-discovery</t>
+          <t>notion-discovery</t>
         </is>
       </c>
       <c r="K49" s="15" t="inlineStr">
@@ -3136,12 +3087,12 @@
         </is>
       </c>
       <c r="D50" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-discovery.md","Explore Harmonic Source Scopes")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-discovery.md","Explore Slack Channels for VC Context")</f>
         <v/>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>Discover Harmonic saved searches, daily searches, and source scope before selected VC sourcing context reads.</t>
+          <t>Discover Slack workspace and channel scope before selected VC context reads or handoff notifications.</t>
         </is>
       </c>
       <c r="F50" s="16">
@@ -3149,7 +3100,7 @@
         <v/>
       </c>
       <c r="G50" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-harmonic-discovery/SKILL.md","VC Harmonic Discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-discovery/SKILL.md","VC Slack Discovery")</f>
         <v/>
       </c>
       <c r="H50" s="15" t="inlineStr">
@@ -3164,7 +3115,7 @@
       </c>
       <c r="J50" s="15" t="inlineStr">
         <is>
-          <t>harmonic-discovery</t>
+          <t>slack-discovery</t>
         </is>
       </c>
       <c r="K50" s="15" t="inlineStr">
@@ -3186,12 +3137,12 @@
         </is>
       </c>
       <c r="D51" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-discovery.md","Explore Harmonic Source Scopes")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-discovery.md","Explore Slack Channels for VC Context")</f>
         <v/>
       </c>
       <c r="E51" s="15" t="inlineStr">
         <is>
-          <t>Discover Harmonic saved searches, daily searches, and source scope before selected VC sourcing context reads.</t>
+          <t>Discover Slack workspace and channel scope before selected VC context reads or handoff notifications.</t>
         </is>
       </c>
       <c r="F51" s="16">
@@ -3210,7 +3161,7 @@
       </c>
       <c r="J51" s="15" t="inlineStr">
         <is>
-          <t>harmonic-discovery</t>
+          <t>slack-discovery</t>
         </is>
       </c>
       <c r="K51" s="15" t="inlineStr">
@@ -3219,7 +3170,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1" s="12">
+    <row r="52" ht="90" customHeight="1" s="12">
       <c r="A52" s="15" t="inlineStr"/>
       <c r="B52" s="15" t="inlineStr">
         <is>
@@ -3228,24 +3179,24 @@
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Integration Support</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="D52" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-discovery.md","Explore Notion Pages and Databases")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-deal-flow-agenda.md","Prepare Deal Flow Agenda")</f>
         <v/>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>Discover Notion page, database, and workspace scope before selected Deal Pipeline context reads.</t>
+          <t>Prepare Deal Flow Agenda for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
       <c r="F52" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-pipeline-autopilot.md","Pipeline Autopilot")</f>
         <v/>
       </c>
       <c r="G52" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-discovery/SKILL.md","VC Notion Discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
         <v/>
       </c>
       <c r="H52" s="15" t="inlineStr">
@@ -3254,198 +3205,6 @@
         </is>
       </c>
       <c r="I52" s="15" t="inlineStr">
-        <is>
-          <t>None declared</t>
-        </is>
-      </c>
-      <c r="J52" s="15" t="inlineStr">
-        <is>
-          <t>notion-discovery</t>
-        </is>
-      </c>
-      <c r="K52" s="15" t="inlineStr">
-        <is>
-          <t>project_management</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1" s="12">
-      <c r="A53" s="15" t="inlineStr"/>
-      <c r="B53" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C53" s="15" t="inlineStr">
-        <is>
-          <t>Integration Support</t>
-        </is>
-      </c>
-      <c r="D53" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-discovery.md","Explore Notion Pages and Databases")</f>
-        <v/>
-      </c>
-      <c r="E53" s="15" t="inlineStr">
-        <is>
-          <t>Discover Notion page, database, and workspace scope before selected Deal Pipeline context reads.</t>
-        </is>
-      </c>
-      <c r="F53" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
-        <v/>
-      </c>
-      <c r="G53" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
-        <v/>
-      </c>
-      <c r="H53" s="15" t="inlineStr"/>
-      <c r="I53" s="15" t="inlineStr">
-        <is>
-          <t>None declared</t>
-        </is>
-      </c>
-      <c r="J53" s="15" t="inlineStr">
-        <is>
-          <t>notion-discovery</t>
-        </is>
-      </c>
-      <c r="K53" s="15" t="inlineStr">
-        <is>
-          <t>project_management</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1" s="12">
-      <c r="A54" s="15" t="inlineStr"/>
-      <c r="B54" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C54" s="15" t="inlineStr">
-        <is>
-          <t>Integration Support</t>
-        </is>
-      </c>
-      <c r="D54" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-discovery.md","Explore Slack Channels for VC Context")</f>
-        <v/>
-      </c>
-      <c r="E54" s="15" t="inlineStr">
-        <is>
-          <t>Discover Slack workspace and channel scope before selected VC context reads or handoff notifications.</t>
-        </is>
-      </c>
-      <c r="F54" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
-        <v/>
-      </c>
-      <c r="G54" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-discovery/SKILL.md","VC Slack Discovery")</f>
-        <v/>
-      </c>
-      <c r="H54" s="15" t="inlineStr">
-        <is>
-          <t>None declared</t>
-        </is>
-      </c>
-      <c r="I54" s="15" t="inlineStr">
-        <is>
-          <t>None declared</t>
-        </is>
-      </c>
-      <c r="J54" s="15" t="inlineStr">
-        <is>
-          <t>slack-discovery</t>
-        </is>
-      </c>
-      <c r="K54" s="15" t="inlineStr">
-        <is>
-          <t>project_management</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1" s="12">
-      <c r="A55" s="15" t="inlineStr"/>
-      <c r="B55" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C55" s="15" t="inlineStr">
-        <is>
-          <t>Integration Support</t>
-        </is>
-      </c>
-      <c r="D55" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-discovery.md","Explore Slack Channels for VC Context")</f>
-        <v/>
-      </c>
-      <c r="E55" s="15" t="inlineStr">
-        <is>
-          <t>Discover Slack workspace and channel scope before selected VC context reads or handoff notifications.</t>
-        </is>
-      </c>
-      <c r="F55" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
-        <v/>
-      </c>
-      <c r="G55" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
-        <v/>
-      </c>
-      <c r="H55" s="15" t="inlineStr"/>
-      <c r="I55" s="15" t="inlineStr">
-        <is>
-          <t>None declared</t>
-        </is>
-      </c>
-      <c r="J55" s="15" t="inlineStr">
-        <is>
-          <t>slack-discovery</t>
-        </is>
-      </c>
-      <c r="K55" s="15" t="inlineStr">
-        <is>
-          <t>project_management</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="90" customHeight="1" s="12">
-      <c r="A56" s="15" t="inlineStr"/>
-      <c r="B56" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C56" s="15" t="inlineStr">
-        <is>
-          <t>Pipeline Management</t>
-        </is>
-      </c>
-      <c r="D56" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-deal-flow-agenda.md","Prepare Deal Flow Agenda")</f>
-        <v/>
-      </c>
-      <c r="E56" s="15" t="inlineStr">
-        <is>
-          <t>Prepare Deal Flow Agenda for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
-        </is>
-      </c>
-      <c r="F56" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-pipeline-autopilot.md","Pipeline Autopilot")</f>
-        <v/>
-      </c>
-      <c r="G56" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
-        <v/>
-      </c>
-      <c r="H56" s="15" t="inlineStr">
-        <is>
-          <t>None declared</t>
-        </is>
-      </c>
-      <c r="I56" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -3455,48 +3214,48 @@
 dealroom-mcp</t>
         </is>
       </c>
-      <c r="J56" s="15" t="inlineStr">
+      <c r="J52" s="15" t="inlineStr">
         <is>
           <t>prepare-deal-flow-agenda</t>
         </is>
       </c>
-      <c r="K56" s="15" t="inlineStr">
+      <c r="K52" s="15" t="inlineStr">
         <is>
           <t>project_management</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="90" customHeight="1" s="12">
-      <c r="A57" s="15" t="inlineStr"/>
-      <c r="B57" s="15" t="inlineStr">
-        <is>
-          <t>Deal Pipeline</t>
-        </is>
-      </c>
-      <c r="C57" s="15" t="inlineStr">
+    <row r="53" ht="90" customHeight="1" s="12">
+      <c r="A53" s="15" t="inlineStr"/>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
         <is>
           <t>Pipeline Management</t>
         </is>
       </c>
-      <c r="D57" s="16">
+      <c r="D53" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-deal-flow-agenda.md","Prepare Deal Flow Agenda")</f>
         <v/>
       </c>
-      <c r="E57" s="15" t="inlineStr">
+      <c r="E53" s="15" t="inlineStr">
         <is>
           <t>Prepare Deal Flow Agenda for one venture-capital opportunity with evidence capture, human review gates, and next-action recommendations.</t>
         </is>
       </c>
-      <c r="F57" s="16">
+      <c r="F53" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-pipeline-autopilot.md","Pipeline Autopilot")</f>
         <v/>
       </c>
-      <c r="G57" s="16">
+      <c r="G53" s="16">
         <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-task-and-next-step-generation/SKILL.md","VC Task &amp; Next-Step Generation")</f>
         <v/>
       </c>
-      <c r="H57" s="15" t="inlineStr"/>
-      <c r="I57" s="15" t="inlineStr">
+      <c r="H53" s="15" t="inlineStr"/>
+      <c r="I53" s="15" t="inlineStr">
         <is>
           <t>alludium-platform
 affinity-mcp-server
@@ -3506,9 +3265,201 @@
 dealroom-mcp</t>
         </is>
       </c>
+      <c r="J53" s="15" t="inlineStr">
+        <is>
+          <t>prepare-deal-flow-agenda</t>
+        </is>
+      </c>
+      <c r="K53" s="15" t="inlineStr">
+        <is>
+          <t>project_management</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1" s="12">
+      <c r="A54" s="15" t="inlineStr"/>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>Integration Support</t>
+        </is>
+      </c>
+      <c r="D54" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-sync-read.md","Preview Google Drive Context")</f>
+        <v/>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>Preview selected Google Drive file, folder, and document context before attaching or importing it into Deal Pipeline tasks.</t>
+        </is>
+      </c>
+      <c r="F54" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
+        <v/>
+      </c>
+      <c r="G54" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-sync-read/SKILL.md","VC Google Drive Sync Read")</f>
+        <v/>
+      </c>
+      <c r="H54" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="I54" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="J54" s="15" t="inlineStr">
+        <is>
+          <t>google-drive-sync-read</t>
+        </is>
+      </c>
+      <c r="K54" s="15" t="inlineStr">
+        <is>
+          <t>project_management</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1" s="12">
+      <c r="A55" s="15" t="inlineStr"/>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="inlineStr">
+        <is>
+          <t>Integration Support</t>
+        </is>
+      </c>
+      <c r="D55" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-sync-read.md","Preview Google Drive Context")</f>
+        <v/>
+      </c>
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>Preview selected Google Drive file, folder, and document context before attaching or importing it into Deal Pipeline tasks.</t>
+        </is>
+      </c>
+      <c r="F55" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
+        <v/>
+      </c>
+      <c r="G55" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
+        <v/>
+      </c>
+      <c r="H55" s="15" t="inlineStr"/>
+      <c r="I55" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="J55" s="15" t="inlineStr">
+        <is>
+          <t>google-drive-sync-read</t>
+        </is>
+      </c>
+      <c r="K55" s="15" t="inlineStr">
+        <is>
+          <t>project_management</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1" s="12">
+      <c r="A56" s="15" t="inlineStr"/>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>Integration Support</t>
+        </is>
+      </c>
+      <c r="D56" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-sync-read.md","Preview Harmonic Search Results")</f>
+        <v/>
+      </c>
+      <c r="E56" s="15" t="inlineStr">
+        <is>
+          <t>Preview selected Harmonic company or saved-search results before using them as VC sourcing or screening context.</t>
+        </is>
+      </c>
+      <c r="F56" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
+        <v/>
+      </c>
+      <c r="G56" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-harmonic-sync-read/SKILL.md","VC Harmonic Sync Read")</f>
+        <v/>
+      </c>
+      <c r="H56" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="I56" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="J56" s="15" t="inlineStr">
+        <is>
+          <t>harmonic-sync-read</t>
+        </is>
+      </c>
+      <c r="K56" s="15" t="inlineStr">
+        <is>
+          <t>project_management</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1" s="12">
+      <c r="A57" s="15" t="inlineStr"/>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>Deal Pipeline</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="inlineStr">
+        <is>
+          <t>Integration Support</t>
+        </is>
+      </c>
+      <c r="D57" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-sync-read.md","Preview Harmonic Search Results")</f>
+        <v/>
+      </c>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>Preview selected Harmonic company or saved-search results before using them as VC sourcing or screening context.</t>
+        </is>
+      </c>
+      <c r="F57" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
+        <v/>
+      </c>
+      <c r="G57" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
+        <v/>
+      </c>
+      <c r="H57" s="15" t="inlineStr"/>
+      <c r="I57" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
       <c r="J57" s="15" t="inlineStr">
         <is>
-          <t>prepare-deal-flow-agenda</t>
+          <t>harmonic-sync-read</t>
         </is>
       </c>
       <c r="K57" s="15" t="inlineStr">
@@ -3530,12 +3481,12 @@
         </is>
       </c>
       <c r="D58" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-sync-read.md","Preview Google Drive Context")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-sync-read.md","Preview Notion Context")</f>
         <v/>
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>Preview selected Google Drive file, folder, and document context before attaching or importing it into Deal Pipeline tasks.</t>
+          <t>Preview selected Notion page, block, property, and database content before attaching it to Deal Pipeline tasks.</t>
         </is>
       </c>
       <c r="F58" s="16">
@@ -3543,7 +3494,7 @@
         <v/>
       </c>
       <c r="G58" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-sync-read/SKILL.md","VC Google Drive Sync Read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-sync-read/SKILL.md","VC Notion Sync Read")</f>
         <v/>
       </c>
       <c r="H58" s="15" t="inlineStr">
@@ -3558,7 +3509,7 @@
       </c>
       <c r="J58" s="15" t="inlineStr">
         <is>
-          <t>google-drive-sync-read</t>
+          <t>notion-sync-read</t>
         </is>
       </c>
       <c r="K58" s="15" t="inlineStr">
@@ -3580,12 +3531,12 @@
         </is>
       </c>
       <c r="D59" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-sync-read.md","Preview Google Drive Context")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-sync-read.md","Preview Notion Context")</f>
         <v/>
       </c>
       <c r="E59" s="15" t="inlineStr">
         <is>
-          <t>Preview selected Google Drive file, folder, and document context before attaching or importing it into Deal Pipeline tasks.</t>
+          <t>Preview selected Notion page, block, property, and database content before attaching it to Deal Pipeline tasks.</t>
         </is>
       </c>
       <c r="F59" s="16">
@@ -3604,7 +3555,7 @@
       </c>
       <c r="J59" s="15" t="inlineStr">
         <is>
-          <t>google-drive-sync-read</t>
+          <t>notion-sync-read</t>
         </is>
       </c>
       <c r="K59" s="15" t="inlineStr">
@@ -3626,12 +3577,12 @@
         </is>
       </c>
       <c r="D60" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-sync-read.md","Preview Harmonic Search Results")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-sync-read.md","Preview Slack Deal Context")</f>
         <v/>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>Preview selected Harmonic company or saved-search results before using them as VC sourcing or screening context.</t>
+          <t>Preview selected Slack channel, thread, message, and file context for Deal Pipeline tasks.</t>
         </is>
       </c>
       <c r="F60" s="16">
@@ -3639,7 +3590,7 @@
         <v/>
       </c>
       <c r="G60" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-harmonic-sync-read/SKILL.md","VC Harmonic Sync Read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-sync-read/SKILL.md","VC Slack Sync Read")</f>
         <v/>
       </c>
       <c r="H60" s="15" t="inlineStr">
@@ -3654,7 +3605,7 @@
       </c>
       <c r="J60" s="15" t="inlineStr">
         <is>
-          <t>harmonic-sync-read</t>
+          <t>slack-sync-read</t>
         </is>
       </c>
       <c r="K60" s="15" t="inlineStr">
@@ -3676,12 +3627,12 @@
         </is>
       </c>
       <c r="D61" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-sync-read.md","Preview Harmonic Search Results")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-sync-read.md","Preview Slack Deal Context")</f>
         <v/>
       </c>
       <c r="E61" s="15" t="inlineStr">
         <is>
-          <t>Preview selected Harmonic company or saved-search results before using them as VC sourcing or screening context.</t>
+          <t>Preview selected Slack channel, thread, message, and file context for Deal Pipeline tasks.</t>
         </is>
       </c>
       <c r="F61" s="16">
@@ -3700,7 +3651,7 @@
       </c>
       <c r="J61" s="15" t="inlineStr">
         <is>
-          <t>harmonic-sync-read</t>
+          <t>slack-sync-read</t>
         </is>
       </c>
       <c r="K61" s="15" t="inlineStr">
@@ -3722,12 +3673,12 @@
         </is>
       </c>
       <c r="D62" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-sync-read.md","Preview Notion Context")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-setup.md","Set Up Google Drive for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>Preview selected Notion page, block, property, and database content before attaching it to Deal Pipeline tasks.</t>
+          <t>Coordinate Google Drive connection readiness, folder discovery, read-preview policy, and optional file proposal scope for Deal Pipeline setup.</t>
         </is>
       </c>
       <c r="F62" s="16">
@@ -3735,7 +3686,7 @@
         <v/>
       </c>
       <c r="G62" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-sync-read/SKILL.md","VC Notion Sync Read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-discovery/SKILL.md","VC Google Drive Discovery")</f>
         <v/>
       </c>
       <c r="H62" s="15" t="inlineStr">
@@ -3745,12 +3696,12 @@
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>None declared</t>
+          <t>google_drive</t>
         </is>
       </c>
       <c r="J62" s="15" t="inlineStr">
         <is>
-          <t>notion-sync-read</t>
+          <t>google-drive-setup</t>
         </is>
       </c>
       <c r="K62" s="15" t="inlineStr">
@@ -3772,12 +3723,12 @@
         </is>
       </c>
       <c r="D63" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-sync-read.md","Preview Notion Context")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-setup.md","Set Up Google Drive for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="E63" s="15" t="inlineStr">
         <is>
-          <t>Preview selected Notion page, block, property, and database content before attaching it to Deal Pipeline tasks.</t>
+          <t>Coordinate Google Drive connection readiness, folder discovery, read-preview policy, and optional file proposal scope for Deal Pipeline setup.</t>
         </is>
       </c>
       <c r="F63" s="16">
@@ -3785,18 +3736,18 @@
         <v/>
       </c>
       <c r="G63" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-sync-read/SKILL.md","VC Google Drive Sync Read")</f>
         <v/>
       </c>
       <c r="H63" s="15" t="inlineStr"/>
       <c r="I63" s="15" t="inlineStr">
         <is>
-          <t>None declared</t>
+          <t>google_drive</t>
         </is>
       </c>
       <c r="J63" s="15" t="inlineStr">
         <is>
-          <t>notion-sync-read</t>
+          <t>google-drive-setup</t>
         </is>
       </c>
       <c r="K63" s="15" t="inlineStr">
@@ -3818,12 +3769,12 @@
         </is>
       </c>
       <c r="D64" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-sync-read.md","Preview Slack Deal Context")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-setup.md","Set Up Google Drive for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>Preview selected Slack channel, thread, message, and file context for Deal Pipeline tasks.</t>
+          <t>Coordinate Google Drive connection readiness, folder discovery, read-preview policy, and optional file proposal scope for Deal Pipeline setup.</t>
         </is>
       </c>
       <c r="F64" s="16">
@@ -3831,22 +3782,18 @@
         <v/>
       </c>
       <c r="G64" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-sync-read/SKILL.md","VC Slack Sync Read")</f>
-        <v/>
-      </c>
-      <c r="H64" s="15" t="inlineStr">
-        <is>
-          <t>None declared</t>
-        </is>
-      </c>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-sync-write/SKILL.md","VC Google Drive Sync Write")</f>
+        <v/>
+      </c>
+      <c r="H64" s="15" t="inlineStr"/>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>None declared</t>
+          <t>google_drive</t>
         </is>
       </c>
       <c r="J64" s="15" t="inlineStr">
         <is>
-          <t>slack-sync-read</t>
+          <t>google-drive-setup</t>
         </is>
       </c>
       <c r="K64" s="15" t="inlineStr">
@@ -3868,12 +3815,12 @@
         </is>
       </c>
       <c r="D65" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-sync-read.md","Preview Slack Deal Context")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-setup.md","Set Up Google Drive for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="E65" s="15" t="inlineStr">
         <is>
-          <t>Preview selected Slack channel, thread, message, and file context for Deal Pipeline tasks.</t>
+          <t>Coordinate Google Drive connection readiness, folder discovery, read-preview policy, and optional file proposal scope for Deal Pipeline setup.</t>
         </is>
       </c>
       <c r="F65" s="16">
@@ -3887,12 +3834,12 @@
       <c r="H65" s="15" t="inlineStr"/>
       <c r="I65" s="15" t="inlineStr">
         <is>
-          <t>None declared</t>
+          <t>google_drive</t>
         </is>
       </c>
       <c r="J65" s="15" t="inlineStr">
         <is>
-          <t>slack-sync-read</t>
+          <t>google-drive-setup</t>
         </is>
       </c>
       <c r="K65" s="15" t="inlineStr">
@@ -3914,12 +3861,12 @@
         </is>
       </c>
       <c r="D66" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-setup.md","Set Up Google Drive for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-setup.md","Set Up Harmonic for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>Coordinate Google Drive connection readiness, folder discovery, read-preview policy, and optional file proposal scope for Deal Pipeline setup.</t>
+          <t>Coordinate Harmonic connection readiness, saved-search discovery, and read-preview policy for Deal Pipeline setup.</t>
         </is>
       </c>
       <c r="F66" s="16">
@@ -3927,7 +3874,7 @@
         <v/>
       </c>
       <c r="G66" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-discovery/SKILL.md","VC Google Drive Discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-harmonic-discovery/SKILL.md","VC Harmonic Discovery")</f>
         <v/>
       </c>
       <c r="H66" s="15" t="inlineStr">
@@ -3937,12 +3884,12 @@
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>google_drive</t>
+          <t>harmonic-mcp-oauth</t>
         </is>
       </c>
       <c r="J66" s="15" t="inlineStr">
         <is>
-          <t>google-drive-setup</t>
+          <t>harmonic-setup</t>
         </is>
       </c>
       <c r="K66" s="15" t="inlineStr">
@@ -3964,12 +3911,12 @@
         </is>
       </c>
       <c r="D67" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-setup.md","Set Up Google Drive for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-setup.md","Set Up Harmonic for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="E67" s="15" t="inlineStr">
         <is>
-          <t>Coordinate Google Drive connection readiness, folder discovery, read-preview policy, and optional file proposal scope for Deal Pipeline setup.</t>
+          <t>Coordinate Harmonic connection readiness, saved-search discovery, and read-preview policy for Deal Pipeline setup.</t>
         </is>
       </c>
       <c r="F67" s="16">
@@ -3977,18 +3924,18 @@
         <v/>
       </c>
       <c r="G67" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-sync-read/SKILL.md","VC Google Drive Sync Read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-harmonic-sync-read/SKILL.md","VC Harmonic Sync Read")</f>
         <v/>
       </c>
       <c r="H67" s="15" t="inlineStr"/>
       <c r="I67" s="15" t="inlineStr">
         <is>
-          <t>google_drive</t>
+          <t>harmonic-mcp-oauth</t>
         </is>
       </c>
       <c r="J67" s="15" t="inlineStr">
         <is>
-          <t>google-drive-setup</t>
+          <t>harmonic-setup</t>
         </is>
       </c>
       <c r="K67" s="15" t="inlineStr">
@@ -4010,12 +3957,12 @@
         </is>
       </c>
       <c r="D68" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-setup.md","Set Up Google Drive for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-setup.md","Set Up Harmonic for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>Coordinate Google Drive connection readiness, folder discovery, read-preview policy, and optional file proposal scope for Deal Pipeline setup.</t>
+          <t>Coordinate Harmonic connection readiness, saved-search discovery, and read-preview policy for Deal Pipeline setup.</t>
         </is>
       </c>
       <c r="F68" s="16">
@@ -4023,18 +3970,18 @@
         <v/>
       </c>
       <c r="G68" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-sync-write/SKILL.md","VC Google Drive Sync Write")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
         <v/>
       </c>
       <c r="H68" s="15" t="inlineStr"/>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>google_drive</t>
+          <t>harmonic-mcp-oauth</t>
         </is>
       </c>
       <c r="J68" s="15" t="inlineStr">
         <is>
-          <t>google-drive-setup</t>
+          <t>harmonic-setup</t>
         </is>
       </c>
       <c r="K68" s="15" t="inlineStr">
@@ -4056,12 +4003,12 @@
         </is>
       </c>
       <c r="D69" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-setup.md","Set Up Google Drive for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-setup.md","Set Up Notion for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="E69" s="15" t="inlineStr">
         <is>
-          <t>Coordinate Google Drive connection readiness, folder discovery, read-preview policy, and optional file proposal scope for Deal Pipeline setup.</t>
+          <t>Coordinate Notion connection readiness, page/database discovery, read-preview policy, and optional update-proposal scope for Deal Pipeline setup.</t>
         </is>
       </c>
       <c r="F69" s="16">
@@ -4069,18 +4016,22 @@
         <v/>
       </c>
       <c r="G69" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
-        <v/>
-      </c>
-      <c r="H69" s="15" t="inlineStr"/>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-discovery/SKILL.md","VC Notion Discovery")</f>
+        <v/>
+      </c>
+      <c r="H69" s="15" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
       <c r="I69" s="15" t="inlineStr">
         <is>
-          <t>google_drive</t>
+          <t>notion</t>
         </is>
       </c>
       <c r="J69" s="15" t="inlineStr">
         <is>
-          <t>google-drive-setup</t>
+          <t>notion-setup</t>
         </is>
       </c>
       <c r="K69" s="15" t="inlineStr">
@@ -4102,12 +4053,12 @@
         </is>
       </c>
       <c r="D70" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-setup.md","Set Up Harmonic for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-setup.md","Set Up Notion for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Coordinate Harmonic connection readiness, saved-search discovery, and read-preview policy for Deal Pipeline setup.</t>
+          <t>Coordinate Notion connection readiness, page/database discovery, read-preview policy, and optional update-proposal scope for Deal Pipeline setup.</t>
         </is>
       </c>
       <c r="F70" s="16">
@@ -4115,22 +4066,18 @@
         <v/>
       </c>
       <c r="G70" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-harmonic-discovery/SKILL.md","VC Harmonic Discovery")</f>
-        <v/>
-      </c>
-      <c r="H70" s="15" t="inlineStr">
-        <is>
-          <t>None declared</t>
-        </is>
-      </c>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-sync-read/SKILL.md","VC Notion Sync Read")</f>
+        <v/>
+      </c>
+      <c r="H70" s="15" t="inlineStr"/>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>harmonic-mcp-oauth</t>
+          <t>notion</t>
         </is>
       </c>
       <c r="J70" s="15" t="inlineStr">
         <is>
-          <t>harmonic-setup</t>
+          <t>notion-setup</t>
         </is>
       </c>
       <c r="K70" s="15" t="inlineStr">
@@ -4152,12 +4099,12 @@
         </is>
       </c>
       <c r="D71" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-setup.md","Set Up Harmonic for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-setup.md","Set Up Notion for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>Coordinate Harmonic connection readiness, saved-search discovery, and read-preview policy for Deal Pipeline setup.</t>
+          <t>Coordinate Notion connection readiness, page/database discovery, read-preview policy, and optional update-proposal scope for Deal Pipeline setup.</t>
         </is>
       </c>
       <c r="F71" s="16">
@@ -4165,18 +4112,18 @@
         <v/>
       </c>
       <c r="G71" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-harmonic-sync-read/SKILL.md","VC Harmonic Sync Read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-sync-write/SKILL.md","VC Notion Sync Write")</f>
         <v/>
       </c>
       <c r="H71" s="15" t="inlineStr"/>
       <c r="I71" s="15" t="inlineStr">
         <is>
-          <t>harmonic-mcp-oauth</t>
+          <t>notion</t>
         </is>
       </c>
       <c r="J71" s="15" t="inlineStr">
         <is>
-          <t>harmonic-setup</t>
+          <t>notion-setup</t>
         </is>
       </c>
       <c r="K71" s="15" t="inlineStr">
@@ -4198,12 +4145,12 @@
         </is>
       </c>
       <c r="D72" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-setup.md","Set Up Harmonic for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-setup.md","Set Up Notion for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Coordinate Harmonic connection readiness, saved-search discovery, and read-preview policy for Deal Pipeline setup.</t>
+          <t>Coordinate Notion connection readiness, page/database discovery, read-preview policy, and optional update-proposal scope for Deal Pipeline setup.</t>
         </is>
       </c>
       <c r="F72" s="16">
@@ -4217,12 +4164,12 @@
       <c r="H72" s="15" t="inlineStr"/>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t>harmonic-mcp-oauth</t>
+          <t>notion</t>
         </is>
       </c>
       <c r="J72" s="15" t="inlineStr">
         <is>
-          <t>harmonic-setup</t>
+          <t>notion-setup</t>
         </is>
       </c>
       <c r="K72" s="15" t="inlineStr">
@@ -4244,12 +4191,12 @@
         </is>
       </c>
       <c r="D73" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-setup.md","Set Up Notion for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-setup.md","Set Up Slack for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>Coordinate Notion connection readiness, page/database discovery, read-preview policy, and optional update-proposal scope for Deal Pipeline setup.</t>
+          <t>Coordinate Slack connection readiness, channel discovery, read-preview policy, and optional notification proposal scope for Deal Pipeline setup.</t>
         </is>
       </c>
       <c r="F73" s="16">
@@ -4257,7 +4204,7 @@
         <v/>
       </c>
       <c r="G73" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-discovery/SKILL.md","VC Notion Discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-discovery/SKILL.md","VC Slack Discovery")</f>
         <v/>
       </c>
       <c r="H73" s="15" t="inlineStr">
@@ -4267,12 +4214,12 @@
       </c>
       <c r="I73" s="15" t="inlineStr">
         <is>
-          <t>notion</t>
+          <t>slack_v2</t>
         </is>
       </c>
       <c r="J73" s="15" t="inlineStr">
         <is>
-          <t>notion-setup</t>
+          <t>slack-setup</t>
         </is>
       </c>
       <c r="K73" s="15" t="inlineStr">
@@ -4294,12 +4241,12 @@
         </is>
       </c>
       <c r="D74" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-setup.md","Set Up Notion for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-setup.md","Set Up Slack for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>Coordinate Notion connection readiness, page/database discovery, read-preview policy, and optional update-proposal scope for Deal Pipeline setup.</t>
+          <t>Coordinate Slack connection readiness, channel discovery, read-preview policy, and optional notification proposal scope for Deal Pipeline setup.</t>
         </is>
       </c>
       <c r="F74" s="16">
@@ -4307,18 +4254,18 @@
         <v/>
       </c>
       <c r="G74" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-sync-read/SKILL.md","VC Notion Sync Read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-sync-read/SKILL.md","VC Slack Sync Read")</f>
         <v/>
       </c>
       <c r="H74" s="15" t="inlineStr"/>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>notion</t>
+          <t>slack_v2</t>
         </is>
       </c>
       <c r="J74" s="15" t="inlineStr">
         <is>
-          <t>notion-setup</t>
+          <t>slack-setup</t>
         </is>
       </c>
       <c r="K74" s="15" t="inlineStr">
@@ -4340,12 +4287,12 @@
         </is>
       </c>
       <c r="D75" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-setup.md","Set Up Notion for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-setup.md","Set Up Slack for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>Coordinate Notion connection readiness, page/database discovery, read-preview policy, and optional update-proposal scope for Deal Pipeline setup.</t>
+          <t>Coordinate Slack connection readiness, channel discovery, read-preview policy, and optional notification proposal scope for Deal Pipeline setup.</t>
         </is>
       </c>
       <c r="F75" s="16">
@@ -4353,18 +4300,18 @@
         <v/>
       </c>
       <c r="G75" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-sync-write/SKILL.md","VC Notion Sync Write")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-sync-write/SKILL.md","VC Slack Sync Write")</f>
         <v/>
       </c>
       <c r="H75" s="15" t="inlineStr"/>
       <c r="I75" s="15" t="inlineStr">
         <is>
-          <t>notion</t>
+          <t>slack_v2</t>
         </is>
       </c>
       <c r="J75" s="15" t="inlineStr">
         <is>
-          <t>notion-setup</t>
+          <t>slack-setup</t>
         </is>
       </c>
       <c r="K75" s="15" t="inlineStr">
@@ -4386,12 +4333,12 @@
         </is>
       </c>
       <c r="D76" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-setup.md","Set Up Notion for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-setup.md","Set Up Slack for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>Coordinate Notion connection readiness, page/database discovery, read-preview policy, and optional update-proposal scope for Deal Pipeline setup.</t>
+          <t>Coordinate Slack connection readiness, channel discovery, read-preview policy, and optional notification proposal scope for Deal Pipeline setup.</t>
         </is>
       </c>
       <c r="F76" s="16">
@@ -4405,12 +4352,12 @@
       <c r="H76" s="15" t="inlineStr"/>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>notion</t>
+          <t>slack_v2</t>
         </is>
       </c>
       <c r="J76" s="15" t="inlineStr">
         <is>
-          <t>notion-setup</t>
+          <t>slack-setup</t>
         </is>
       </c>
       <c r="K76" s="15" t="inlineStr">
@@ -4419,8 +4366,12 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="18" customHeight="1" s="12">
-      <c r="A77" s="15" t="inlineStr"/>
+    <row r="77" ht="135" customHeight="1" s="12">
+      <c r="A77" s="15" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
           <t>Deal Pipeline</t>
@@ -4428,49 +4379,60 @@
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>Integration Support</t>
+          <t>Intake</t>
         </is>
       </c>
       <c r="D77" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-setup.md","Set Up Slack for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
         <v/>
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>Coordinate Slack connection readiness, channel discovery, read-preview policy, and optional notification proposal scope for Deal Pipeline setup.</t>
+          <t>Capture source context, known fields, missing information, and guided project-creation values for one venture-capital opportunity before formal screening.</t>
         </is>
       </c>
       <c r="F77" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-dealflow-concierge.md","Dealflow Concierge")</f>
         <v/>
       </c>
       <c r="G77" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-discovery/SKILL.md","VC Slack Discovery")</f>
-        <v/>
-      </c>
-      <c r="H77" s="15" t="inlineStr">
-        <is>
-          <t>None declared</t>
-        </is>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/deal-room-setup-and-source-ingestion/SKILL.md","Deal Pipeline Setup &amp; Source Ingestion")</f>
+        <v/>
+      </c>
+      <c r="H77" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/deal-room-sop.md","Deal Pipeline Operating SOP (operating_guidance)")</f>
+        <v/>
       </c>
       <c r="I77" s="15" t="inlineStr">
         <is>
-          <t>slack_v2</t>
+          <t>alludium-platform
+harmonic-mcp-oauth
+affinity-mcp-server
+exa-mcp-hosted
+brave-search-mcp
+serpapi-mcp
+firecrawl-mcp-hosted
+dealroom-mcp
+google_drive</t>
         </is>
       </c>
       <c r="J77" s="15" t="inlineStr">
         <is>
-          <t>slack-setup</t>
+          <t>screen-inbound-opportunity</t>
         </is>
       </c>
       <c r="K77" s="15" t="inlineStr">
         <is>
-          <t>project_management</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="18" customHeight="1" s="12">
-      <c r="A78" s="15" t="inlineStr"/>
+          <t>project_instance</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="135" customHeight="1" s="12">
+      <c r="A78" s="15" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
           <t>Deal Pipeline</t>
@@ -4478,45 +4440,60 @@
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Integration Support</t>
+          <t>Intake</t>
         </is>
       </c>
       <c r="D78" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-setup.md","Set Up Slack for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
         <v/>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>Coordinate Slack connection readiness, channel discovery, read-preview policy, and optional notification proposal scope for Deal Pipeline setup.</t>
+          <t>Capture source context, known fields, missing information, and guided project-creation values for one venture-capital opportunity before formal screening.</t>
         </is>
       </c>
       <c r="F78" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-dealflow-concierge.md","Dealflow Concierge")</f>
         <v/>
       </c>
       <c r="G78" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-sync-read/SKILL.md","VC Slack Sync Read")</f>
-        <v/>
-      </c>
-      <c r="H78" s="15" t="inlineStr"/>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/company-research-and-enrichment/SKILL.md","Company Research &amp; Enrichment")</f>
+        <v/>
+      </c>
+      <c r="H78" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (style_guide)")</f>
+        <v/>
+      </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>slack_v2</t>
+          <t>alludium-platform
+harmonic-mcp-oauth
+affinity-mcp-server
+exa-mcp-hosted
+brave-search-mcp
+serpapi-mcp
+firecrawl-mcp-hosted
+dealroom-mcp
+google_drive</t>
         </is>
       </c>
       <c r="J78" s="15" t="inlineStr">
         <is>
-          <t>slack-setup</t>
+          <t>screen-inbound-opportunity</t>
         </is>
       </c>
       <c r="K78" s="15" t="inlineStr">
         <is>
-          <t>project_management</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1" s="12">
-      <c r="A79" s="15" t="inlineStr"/>
+          <t>project_instance</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="135" customHeight="1" s="12">
+      <c r="A79" s="15" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
           <t>Deal Pipeline</t>
@@ -4524,45 +4501,60 @@
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>Integration Support</t>
+          <t>Intake</t>
         </is>
       </c>
       <c r="D79" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-setup.md","Set Up Slack for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
         <v/>
       </c>
       <c r="E79" s="15" t="inlineStr">
         <is>
-          <t>Coordinate Slack connection readiness, channel discovery, read-preview policy, and optional notification proposal scope for Deal Pipeline setup.</t>
+          <t>Capture source context, known fields, missing information, and guided project-creation values for one venture-capital opportunity before formal screening.</t>
         </is>
       </c>
       <c r="F79" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-dealflow-concierge.md","Dealflow Concierge")</f>
         <v/>
       </c>
       <c r="G79" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-sync-write/SKILL.md","VC Slack Sync Write")</f>
-        <v/>
-      </c>
-      <c r="H79" s="15" t="inlineStr"/>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
+        <v/>
+      </c>
+      <c r="H79" s="16">
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (operating_guidance)")</f>
+        <v/>
+      </c>
       <c r="I79" s="15" t="inlineStr">
         <is>
-          <t>slack_v2</t>
+          <t>alludium-platform
+harmonic-mcp-oauth
+affinity-mcp-server
+exa-mcp-hosted
+brave-search-mcp
+serpapi-mcp
+firecrawl-mcp-hosted
+dealroom-mcp
+google_drive</t>
         </is>
       </c>
       <c r="J79" s="15" t="inlineStr">
         <is>
-          <t>slack-setup</t>
+          <t>screen-inbound-opportunity</t>
         </is>
       </c>
       <c r="K79" s="15" t="inlineStr">
         <is>
-          <t>project_management</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="18" customHeight="1" s="12">
-      <c r="A80" s="15" t="inlineStr"/>
+          <t>project_instance</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="135" customHeight="1" s="12">
+      <c r="A80" s="15" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
           <t>Deal Pipeline</t>
@@ -4570,40 +4562,48 @@
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Integration Support</t>
+          <t>Intake</t>
         </is>
       </c>
       <c r="D80" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-setup.md","Set Up Slack for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
         <v/>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>Coordinate Slack connection readiness, channel discovery, read-preview policy, and optional notification proposal scope for Deal Pipeline setup.</t>
+          <t>Capture source context, known fields, missing information, and guided project-creation values for one venture-capital opportunity before formal screening.</t>
         </is>
       </c>
       <c r="F80" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-integration-operator.md","Integration Operator")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/agents/vc-dealflow-concierge.md","Dealflow Concierge")</f>
         <v/>
       </c>
       <c r="G80" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/pitch-deck-explainer/SKILL.md","Pitch Deck Explainer")</f>
         <v/>
       </c>
       <c r="H80" s="15" t="inlineStr"/>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>slack_v2</t>
+          <t>alludium-platform
+harmonic-mcp-oauth
+affinity-mcp-server
+exa-mcp-hosted
+brave-search-mcp
+serpapi-mcp
+firecrawl-mcp-hosted
+dealroom-mcp
+google_drive</t>
         </is>
       </c>
       <c r="J80" s="15" t="inlineStr">
         <is>
-          <t>slack-setup</t>
+          <t>screen-inbound-opportunity</t>
         </is>
       </c>
       <c r="K80" s="15" t="inlineStr">
         <is>
-          <t>project_management</t>
+          <t>project_instance</t>
         </is>
       </c>
     </row>
@@ -18950,10 +18950,10 @@
         <v>90</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G3" s="15" t="inlineStr">
         <is>
@@ -19363,10 +19363,10 @@
         <v>4</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
@@ -19503,10 +19503,10 @@
         <v>3</v>
       </c>
       <c r="E16" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="15" t="n">
         <v>1</v>
-      </c>
-      <c r="F16" s="15" t="n">
-        <v>2</v>
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
@@ -19755,10 +19755,10 @@
         <v>2</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
@@ -24606,11 +24606,11 @@
         </is>
       </c>
       <c r="C3" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-setup.md","Set Up Affinity for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="D3" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/deal-room-setup-and-source-ingestion/SKILL.md","Deal Pipeline Setup &amp; Source Ingestion")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-discovery/SKILL.md","VC Affinity Discovery")</f>
         <v/>
       </c>
     </row>
@@ -24626,11 +24626,11 @@
         </is>
       </c>
       <c r="C4" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-setup.md","Set Up Affinity for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/company-research-and-enrichment/SKILL.md","Company Research &amp; Enrichment")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-sync-read/SKILL.md","VC Affinity Sync Read")</f>
         <v/>
       </c>
     </row>
@@ -24646,11 +24646,11 @@
         </is>
       </c>
       <c r="C5" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-setup.md","Set Up Affinity for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-sync-write/SKILL.md","VC Affinity Sync Write")</f>
         <v/>
       </c>
     </row>
@@ -24666,11 +24666,11 @@
         </is>
       </c>
       <c r="C6" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-setup.md","Set Up Affinity for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/pitch-deck-explainer/SKILL.md","Pitch Deck Explainer")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
         <v/>
       </c>
     </row>
@@ -24686,11 +24686,11 @@
         </is>
       </c>
       <c r="C7" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-setup.md","Set Up Affinity for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-deal-room-import.md","Import Affinity Deal Pipeline Seed")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-discovery/SKILL.md","VC Affinity Discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-deal-room-import/SKILL.md","VC Affinity Deal Pipeline Import")</f>
         <v/>
       </c>
     </row>
@@ -24706,7 +24706,7 @@
         </is>
       </c>
       <c r="C8" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-setup.md","Set Up Affinity for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-deal-room-import.md","Import Affinity Deal Pipeline Seed")</f>
         <v/>
       </c>
       <c r="D8" s="16">
@@ -24726,11 +24726,11 @@
         </is>
       </c>
       <c r="C9" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-setup.md","Set Up Affinity for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-deal-room-import.md","Import Affinity Deal Pipeline Seed")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-sync-write/SKILL.md","VC Affinity Sync Write")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/deal-room-setup-and-source-ingestion/SKILL.md","Deal Pipeline Setup &amp; Source Ingestion")</f>
         <v/>
       </c>
     </row>
@@ -24746,7 +24746,7 @@
         </is>
       </c>
       <c r="C10" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-setup.md","Set Up Affinity for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-deal-room-import.md","Import Affinity Deal Pipeline Seed")</f>
         <v/>
       </c>
       <c r="D10" s="16">
@@ -24762,15 +24762,15 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C11" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-deal-room-import.md","Import Affinity Deal Pipeline Seed")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-call.md","Prepare Meeting")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-deal-room-import/SKILL.md","VC Affinity Deal Pipeline Import")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/meeting-prep-and-summary/SKILL.md","Meeting Prep &amp; Summary")</f>
         <v/>
       </c>
     </row>
@@ -24782,15 +24782,15 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C12" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-deal-room-import.md","Import Affinity Deal Pipeline Seed")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-call.md","Prepare Meeting")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-sync-read/SKILL.md","VC Affinity Sync Read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/company-research-and-enrichment/SKILL.md","Company Research &amp; Enrichment")</f>
         <v/>
       </c>
     </row>
@@ -24802,15 +24802,15 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C13" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-deal-room-import.md","Import Affinity Deal Pipeline Seed")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-call.md","Prepare Meeting")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/deal-room-setup-and-source-ingestion/SKILL.md","Deal Pipeline Setup &amp; Source Ingestion")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
         <v/>
       </c>
     </row>
@@ -24822,15 +24822,15 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C14" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-deal-room-import.md","Import Affinity Deal Pipeline Seed")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-call.md","Prepare Meeting")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/pitch-deck-explainer/SKILL.md","Pitch Deck Explainer")</f>
         <v/>
       </c>
     </row>
@@ -24846,11 +24846,11 @@
         </is>
       </c>
       <c r="C15" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-call.md","Prepare Meeting")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/request-founder-materials.md","Request Founder Materials")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/meeting-prep-and-summary/SKILL.md","Meeting Prep &amp; Summary")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
         <v/>
       </c>
     </row>
@@ -24866,11 +24866,11 @@
         </is>
       </c>
       <c r="C16" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-call.md","Prepare Meeting")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/request-founder-materials.md","Request Founder Materials")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/company-research-and-enrichment/SKILL.md","Company Research &amp; Enrichment")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/founder-materials-request/SKILL.md","Founder Materials Request")</f>
         <v/>
       </c>
     </row>
@@ -24886,11 +24886,11 @@
         </is>
       </c>
       <c r="C17" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-call.md","Prepare Meeting")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/summarize-initial-call.md","Summarize Meeting Records")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/meeting-prep-and-summary/SKILL.md","Meeting Prep &amp; Summary")</f>
         <v/>
       </c>
     </row>
@@ -24906,11 +24906,11 @@
         </is>
       </c>
       <c r="C18" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-call.md","Prepare Meeting")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/summarize-initial-call.md","Summarize Meeting Records")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/pitch-deck-explainer/SKILL.md","Pitch Deck Explainer")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
         <v/>
       </c>
     </row>
@@ -24926,11 +24926,11 @@
         </is>
       </c>
       <c r="C19" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/request-founder-materials.md","Request Founder Materials")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/summarize-initial-call.md","Summarize Meeting Records")</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-task-and-next-step-generation/SKILL.md","VC Task &amp; Next-Step Generation")</f>
         <v/>
       </c>
     </row>
@@ -24946,11 +24946,11 @@
         </is>
       </c>
       <c r="C20" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/request-founder-materials.md","Request Founder Materials")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-opportunity-status.md","Review Opportunity Status")</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/founder-materials-request/SKILL.md","Founder Materials Request")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
         <v/>
       </c>
     </row>
@@ -24966,11 +24966,11 @@
         </is>
       </c>
       <c r="C21" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/summarize-initial-call.md","Summarize Meeting Records")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-opportunity-status.md","Review Opportunity Status")</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/meeting-prep-and-summary/SKILL.md","Meeting Prep &amp; Summary")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-task-and-next-step-generation/SKILL.md","VC Task &amp; Next-Step Generation")</f>
         <v/>
       </c>
     </row>
@@ -24982,15 +24982,15 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C22" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/summarize-initial-call.md","Summarize Meeting Records")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-sync-read.md","Preview Affinity Pipeline Import")</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-sync-read/SKILL.md","VC Affinity Sync Read")</f>
         <v/>
       </c>
     </row>
@@ -25002,15 +25002,15 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C23" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/summarize-initial-call.md","Summarize Meeting Records")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-sync-read.md","Preview Affinity Pipeline Import")</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-task-and-next-step-generation/SKILL.md","VC Task &amp; Next-Step Generation")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
         <v/>
       </c>
     </row>
@@ -25022,15 +25022,15 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C24" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-opportunity-status.md","Review Opportunity Status")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-sync-write.md","Draft Affinity Write-Back Proposals")</f>
         <v/>
       </c>
       <c r="D24" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-sync-write/SKILL.md","VC Affinity Sync Write")</f>
         <v/>
       </c>
     </row>
@@ -25042,15 +25042,15 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C25" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-opportunity-status.md","Review Opportunity Status")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-sync-write.md","Draft Affinity Write-Back Proposals")</f>
         <v/>
       </c>
       <c r="D25" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-task-and-next-step-generation/SKILL.md","VC Task &amp; Next-Step Generation")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
         <v/>
       </c>
     </row>
@@ -25066,11 +25066,11 @@
         </is>
       </c>
       <c r="C26" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-sync-read.md","Preview Affinity Pipeline Import")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-sync-write.md","Draft Google Drive File Proposals")</f>
         <v/>
       </c>
       <c r="D26" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-sync-read/SKILL.md","VC Affinity Sync Read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-sync-write/SKILL.md","VC Google Drive Sync Write")</f>
         <v/>
       </c>
     </row>
@@ -25086,7 +25086,7 @@
         </is>
       </c>
       <c r="C27" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-sync-read.md","Preview Affinity Pipeline Import")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-sync-write.md","Draft Google Drive File Proposals")</f>
         <v/>
       </c>
       <c r="D27" s="16">
@@ -25106,11 +25106,11 @@
         </is>
       </c>
       <c r="C28" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-sync-write.md","Draft Affinity Write-Back Proposals")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-sync-write.md","Draft Notion Update Proposals")</f>
         <v/>
       </c>
       <c r="D28" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-sync-write/SKILL.md","VC Affinity Sync Write")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-sync-write/SKILL.md","VC Notion Sync Write")</f>
         <v/>
       </c>
     </row>
@@ -25126,7 +25126,7 @@
         </is>
       </c>
       <c r="C29" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-sync-write.md","Draft Affinity Write-Back Proposals")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-sync-write.md","Draft Notion Update Proposals")</f>
         <v/>
       </c>
       <c r="D29" s="16">
@@ -25146,11 +25146,11 @@
         </is>
       </c>
       <c r="C30" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-sync-write.md","Draft Google Drive File Proposals")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-sync-write.md","Draft Slack Handoff Notifications")</f>
         <v/>
       </c>
       <c r="D30" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-sync-write/SKILL.md","VC Google Drive Sync Write")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-sync-write/SKILL.md","VC Slack Sync Write")</f>
         <v/>
       </c>
     </row>
@@ -25166,7 +25166,7 @@
         </is>
       </c>
       <c r="C31" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-sync-write.md","Draft Google Drive File Proposals")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-sync-write.md","Draft Slack Handoff Notifications")</f>
         <v/>
       </c>
       <c r="D31" s="16">
@@ -25186,11 +25186,11 @@
         </is>
       </c>
       <c r="C32" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-sync-write.md","Draft Notion Update Proposals")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-discovery.md","Explore Affinity Lists and Stages")</f>
         <v/>
       </c>
       <c r="D32" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-sync-write/SKILL.md","VC Notion Sync Write")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-discovery/SKILL.md","VC Affinity Discovery")</f>
         <v/>
       </c>
     </row>
@@ -25206,7 +25206,7 @@
         </is>
       </c>
       <c r="C33" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-sync-write.md","Draft Notion Update Proposals")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-discovery.md","Explore Affinity Lists and Stages")</f>
         <v/>
       </c>
       <c r="D33" s="16">
@@ -25226,11 +25226,11 @@
         </is>
       </c>
       <c r="C34" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-sync-write.md","Draft Slack Handoff Notifications")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-discovery.md","Explore Google Drive Sources")</f>
         <v/>
       </c>
       <c r="D34" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-sync-write/SKILL.md","VC Slack Sync Write")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-discovery/SKILL.md","VC Google Drive Discovery")</f>
         <v/>
       </c>
     </row>
@@ -25246,7 +25246,7 @@
         </is>
       </c>
       <c r="C35" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-sync-write.md","Draft Slack Handoff Notifications")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-discovery.md","Explore Google Drive Sources")</f>
         <v/>
       </c>
       <c r="D35" s="16">
@@ -25266,11 +25266,11 @@
         </is>
       </c>
       <c r="C36" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-discovery.md","Explore Affinity Lists and Stages")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-discovery.md","Explore Harmonic Source Scopes")</f>
         <v/>
       </c>
       <c r="D36" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-affinity-discovery/SKILL.md","VC Affinity Discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-harmonic-discovery/SKILL.md","VC Harmonic Discovery")</f>
         <v/>
       </c>
     </row>
@@ -25286,7 +25286,7 @@
         </is>
       </c>
       <c r="C37" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/affinity-discovery.md","Explore Affinity Lists and Stages")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-discovery.md","Explore Harmonic Source Scopes")</f>
         <v/>
       </c>
       <c r="D37" s="16">
@@ -25306,11 +25306,11 @@
         </is>
       </c>
       <c r="C38" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-discovery.md","Explore Google Drive Sources")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-discovery.md","Explore Notion Pages and Databases")</f>
         <v/>
       </c>
       <c r="D38" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-discovery/SKILL.md","VC Google Drive Discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-discovery/SKILL.md","VC Notion Discovery")</f>
         <v/>
       </c>
     </row>
@@ -25326,7 +25326,7 @@
         </is>
       </c>
       <c r="C39" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-discovery.md","Explore Google Drive Sources")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-discovery.md","Explore Notion Pages and Databases")</f>
         <v/>
       </c>
       <c r="D39" s="16">
@@ -25346,11 +25346,11 @@
         </is>
       </c>
       <c r="C40" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-discovery.md","Explore Harmonic Source Scopes")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-discovery.md","Explore Slack Channels for VC Context")</f>
         <v/>
       </c>
       <c r="D40" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-harmonic-discovery/SKILL.md","VC Harmonic Discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-discovery/SKILL.md","VC Slack Discovery")</f>
         <v/>
       </c>
     </row>
@@ -25366,7 +25366,7 @@
         </is>
       </c>
       <c r="C41" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-discovery.md","Explore Harmonic Source Scopes")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-discovery.md","Explore Slack Channels for VC Context")</f>
         <v/>
       </c>
       <c r="D41" s="16">
@@ -25382,15 +25382,15 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Integration Support</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="C42" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-discovery.md","Explore Notion Pages and Databases")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-deal-flow-agenda.md","Prepare Deal Flow Agenda")</f>
         <v/>
       </c>
       <c r="D42" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-discovery/SKILL.md","VC Notion Discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
         <v/>
       </c>
     </row>
@@ -25402,15 +25402,15 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Integration Support</t>
+          <t>Pipeline Management</t>
         </is>
       </c>
       <c r="C43" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-discovery.md","Explore Notion Pages and Databases")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-deal-flow-agenda.md","Prepare Deal Flow Agenda")</f>
         <v/>
       </c>
       <c r="D43" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-task-and-next-step-generation/SKILL.md","VC Task &amp; Next-Step Generation")</f>
         <v/>
       </c>
     </row>
@@ -25426,11 +25426,11 @@
         </is>
       </c>
       <c r="C44" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-discovery.md","Explore Slack Channels for VC Context")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-sync-read.md","Preview Google Drive Context")</f>
         <v/>
       </c>
       <c r="D44" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-discovery/SKILL.md","VC Slack Discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-sync-read/SKILL.md","VC Google Drive Sync Read")</f>
         <v/>
       </c>
     </row>
@@ -25446,7 +25446,7 @@
         </is>
       </c>
       <c r="C45" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-discovery.md","Explore Slack Channels for VC Context")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-sync-read.md","Preview Google Drive Context")</f>
         <v/>
       </c>
       <c r="D45" s="16">
@@ -25462,15 +25462,15 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>Pipeline Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C46" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-deal-flow-agenda.md","Prepare Deal Flow Agenda")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-sync-read.md","Preview Harmonic Search Results")</f>
         <v/>
       </c>
       <c r="D46" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-harmonic-sync-read/SKILL.md","VC Harmonic Sync Read")</f>
         <v/>
       </c>
     </row>
@@ -25482,15 +25482,15 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>Pipeline Management</t>
+          <t>Integration Support</t>
         </is>
       </c>
       <c r="C47" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-deal-flow-agenda.md","Prepare Deal Flow Agenda")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-sync-read.md","Preview Harmonic Search Results")</f>
         <v/>
       </c>
       <c r="D47" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-task-and-next-step-generation/SKILL.md","VC Task &amp; Next-Step Generation")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
         <v/>
       </c>
     </row>
@@ -25506,11 +25506,11 @@
         </is>
       </c>
       <c r="C48" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-sync-read.md","Preview Google Drive Context")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-sync-read.md","Preview Notion Context")</f>
         <v/>
       </c>
       <c r="D48" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-sync-read/SKILL.md","VC Google Drive Sync Read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-sync-read/SKILL.md","VC Notion Sync Read")</f>
         <v/>
       </c>
     </row>
@@ -25526,7 +25526,7 @@
         </is>
       </c>
       <c r="C49" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-sync-read.md","Preview Google Drive Context")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-sync-read.md","Preview Notion Context")</f>
         <v/>
       </c>
       <c r="D49" s="16">
@@ -25546,11 +25546,11 @@
         </is>
       </c>
       <c r="C50" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-sync-read.md","Preview Harmonic Search Results")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-sync-read.md","Preview Slack Deal Context")</f>
         <v/>
       </c>
       <c r="D50" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-harmonic-sync-read/SKILL.md","VC Harmonic Sync Read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-sync-read/SKILL.md","VC Slack Sync Read")</f>
         <v/>
       </c>
     </row>
@@ -25566,7 +25566,7 @@
         </is>
       </c>
       <c r="C51" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-sync-read.md","Preview Harmonic Search Results")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-sync-read.md","Preview Slack Deal Context")</f>
         <v/>
       </c>
       <c r="D51" s="16">
@@ -25586,11 +25586,11 @@
         </is>
       </c>
       <c r="C52" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-sync-read.md","Preview Notion Context")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-setup.md","Set Up Google Drive for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="D52" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-sync-read/SKILL.md","VC Notion Sync Read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-discovery/SKILL.md","VC Google Drive Discovery")</f>
         <v/>
       </c>
     </row>
@@ -25606,11 +25606,11 @@
         </is>
       </c>
       <c r="C53" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-sync-read.md","Preview Notion Context")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-setup.md","Set Up Google Drive for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="D53" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-sync-read/SKILL.md","VC Google Drive Sync Read")</f>
         <v/>
       </c>
     </row>
@@ -25626,11 +25626,11 @@
         </is>
       </c>
       <c r="C54" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-sync-read.md","Preview Slack Deal Context")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-setup.md","Set Up Google Drive for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="D54" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-sync-read/SKILL.md","VC Slack Sync Read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-sync-write/SKILL.md","VC Google Drive Sync Write")</f>
         <v/>
       </c>
     </row>
@@ -25646,7 +25646,7 @@
         </is>
       </c>
       <c r="C55" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-sync-read.md","Preview Slack Deal Context")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-setup.md","Set Up Google Drive for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="D55" s="16">
@@ -25666,11 +25666,11 @@
         </is>
       </c>
       <c r="C56" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-setup.md","Set Up Google Drive for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-setup.md","Set Up Harmonic for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="D56" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-discovery/SKILL.md","VC Google Drive Discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-harmonic-discovery/SKILL.md","VC Harmonic Discovery")</f>
         <v/>
       </c>
     </row>
@@ -25686,11 +25686,11 @@
         </is>
       </c>
       <c r="C57" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-setup.md","Set Up Google Drive for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-setup.md","Set Up Harmonic for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="D57" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-sync-read/SKILL.md","VC Google Drive Sync Read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-harmonic-sync-read/SKILL.md","VC Harmonic Sync Read")</f>
         <v/>
       </c>
     </row>
@@ -25706,11 +25706,11 @@
         </is>
       </c>
       <c r="C58" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-setup.md","Set Up Google Drive for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-setup.md","Set Up Harmonic for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="D58" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-google-drive-sync-write/SKILL.md","VC Google Drive Sync Write")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
         <v/>
       </c>
     </row>
@@ -25726,11 +25726,11 @@
         </is>
       </c>
       <c r="C59" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/google-drive-setup.md","Set Up Google Drive for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-setup.md","Set Up Notion for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="D59" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-discovery/SKILL.md","VC Notion Discovery")</f>
         <v/>
       </c>
     </row>
@@ -25746,11 +25746,11 @@
         </is>
       </c>
       <c r="C60" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-setup.md","Set Up Harmonic for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-setup.md","Set Up Notion for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="D60" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-harmonic-discovery/SKILL.md","VC Harmonic Discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-sync-read/SKILL.md","VC Notion Sync Read")</f>
         <v/>
       </c>
     </row>
@@ -25766,11 +25766,11 @@
         </is>
       </c>
       <c r="C61" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-setup.md","Set Up Harmonic for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-setup.md","Set Up Notion for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="D61" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-harmonic-sync-read/SKILL.md","VC Harmonic Sync Read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-sync-write/SKILL.md","VC Notion Sync Write")</f>
         <v/>
       </c>
     </row>
@@ -25786,7 +25786,7 @@
         </is>
       </c>
       <c r="C62" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/harmonic-setup.md","Set Up Harmonic for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-setup.md","Set Up Notion for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="D62" s="16">
@@ -25806,11 +25806,11 @@
         </is>
       </c>
       <c r="C63" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-setup.md","Set Up Notion for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-setup.md","Set Up Slack for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="D63" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-discovery/SKILL.md","VC Notion Discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-discovery/SKILL.md","VC Slack Discovery")</f>
         <v/>
       </c>
     </row>
@@ -25826,11 +25826,11 @@
         </is>
       </c>
       <c r="C64" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-setup.md","Set Up Notion for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-setup.md","Set Up Slack for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="D64" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-sync-read/SKILL.md","VC Notion Sync Read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-sync-read/SKILL.md","VC Slack Sync Read")</f>
         <v/>
       </c>
     </row>
@@ -25846,11 +25846,11 @@
         </is>
       </c>
       <c r="C65" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-setup.md","Set Up Notion for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-setup.md","Set Up Slack for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="D65" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-notion-sync-write/SKILL.md","VC Notion Sync Write")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-sync-write/SKILL.md","VC Slack Sync Write")</f>
         <v/>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
         </is>
       </c>
       <c r="C66" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/notion-setup.md","Set Up Notion for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-setup.md","Set Up Slack for Deal Pipelines")</f>
         <v/>
       </c>
       <c r="D66" s="16">
@@ -25882,15 +25882,15 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>Integration Support</t>
+          <t>Intake</t>
         </is>
       </c>
       <c r="C67" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-setup.md","Set Up Slack for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
         <v/>
       </c>
       <c r="D67" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-discovery/SKILL.md","VC Slack Discovery")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/deal-room-setup-and-source-ingestion/SKILL.md","Deal Pipeline Setup &amp; Source Ingestion")</f>
         <v/>
       </c>
     </row>
@@ -25902,15 +25902,15 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Integration Support</t>
+          <t>Intake</t>
         </is>
       </c>
       <c r="C68" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-setup.md","Set Up Slack for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
         <v/>
       </c>
       <c r="D68" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-sync-read/SKILL.md","VC Slack Sync Read")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/company-research-and-enrichment/SKILL.md","Company Research &amp; Enrichment")</f>
         <v/>
       </c>
     </row>
@@ -25922,15 +25922,15 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>Integration Support</t>
+          <t>Intake</t>
         </is>
       </c>
       <c r="C69" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-setup.md","Set Up Slack for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
         <v/>
       </c>
       <c r="D69" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/vc-slack-sync-write/SKILL.md","VC Slack Sync Write")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
         <v/>
       </c>
     </row>
@@ -25942,15 +25942,15 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Integration Support</t>
+          <t>Intake</t>
         </is>
       </c>
       <c r="C70" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/slack-setup.md","Set Up Slack for Deal Pipelines")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
         <v/>
       </c>
       <c r="D70" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/citation-enforcement/SKILL.md","Citation Enforcement")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/skills/pitch-deck-explainer/SKILL.md","Pitch Deck Explainer")</f>
         <v/>
       </c>
     </row>
@@ -29572,23 +29572,27 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C3" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-call.md","Prepare Meeting")</f>
         <v/>
       </c>
       <c r="D3" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/deal-room-sop.md","Deal Pipeline Operating SOP (vc.document.deal_room_sop)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/initial-call-brief-template.md","Initial Call Brief Template (vc.document.initial_call_brief_template)")</f>
         <v/>
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>
-          <t>operating_guidance</t>
-        </is>
-      </c>
-      <c r="F3" s="15" t="inlineStr"/>
+          <t>output_template</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>initial_call_brief_artifact_id</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1" s="12">
       <c r="A4" s="15" t="inlineStr">
@@ -29598,11 +29602,11 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C4" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-call.md","Prepare Meeting")</f>
         <v/>
       </c>
       <c r="D4" s="16">
@@ -29624,11 +29628,11 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C5" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-call.md","Prepare Meeting")</f>
         <v/>
       </c>
       <c r="D5" s="16">
@@ -29654,11 +29658,11 @@
         </is>
       </c>
       <c r="C6" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-call.md","Prepare Meeting")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/request-founder-materials.md","Request Founder Materials")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/initial-call-brief-template.md","Initial Call Brief Template (vc.document.initial_call_brief_template)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/founder-materials-request-template.md","Founder Materials Request Template (vc.document.founder_materials_request_template)")</f>
         <v/>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -29668,7 +29672,7 @@
       </c>
       <c r="F6" s="15" t="inlineStr">
         <is>
-          <t>initial_call_brief_artifact_id</t>
+          <t>founder_materials_request_artifact_id</t>
         </is>
       </c>
     </row>
@@ -29684,16 +29688,16 @@
         </is>
       </c>
       <c r="C7" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-call.md","Prepare Meeting")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/request-founder-materials.md","Request Founder Materials")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (vc.document.evidence_citation_style_guide)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/file-naming-source-index-sop.md","File Naming And Source Index SOP (vc.document.file_naming_source_index_sop)")</f>
         <v/>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>operating_guidance</t>
         </is>
       </c>
       <c r="F7" s="15" t="inlineStr"/>
@@ -29710,7 +29714,7 @@
         </is>
       </c>
       <c r="C8" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/prepare-initial-call.md","Prepare Meeting")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/request-founder-materials.md","Request Founder Materials")</f>
         <v/>
       </c>
       <c r="D8" s="16">
@@ -29736,11 +29740,11 @@
         </is>
       </c>
       <c r="C9" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/request-founder-materials.md","Request Founder Materials")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/summarize-initial-call.md","Summarize Meeting Records")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/founder-materials-request-template.md","Founder Materials Request Template (vc.document.founder_materials_request_template)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/customer-insights-summary-template.md","Customer Insights Summary Template (vc.document.customer_insights_summary_template)")</f>
         <v/>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -29750,7 +29754,7 @@
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>founder_materials_request_artifact_id</t>
+          <t>customer_insights_artifact_id</t>
         </is>
       </c>
     </row>
@@ -29766,16 +29770,16 @@
         </is>
       </c>
       <c r="C10" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/request-founder-materials.md","Request Founder Materials")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/summarize-initial-call.md","Summarize Meeting Records")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/file-naming-source-index-sop.md","File Naming And Source Index SOP (vc.document.file_naming_source_index_sop)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (vc.document.evidence_citation_style_guide)")</f>
         <v/>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>operating_guidance</t>
+          <t>style_guide</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr"/>
@@ -29792,7 +29796,7 @@
         </is>
       </c>
       <c r="C11" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/request-founder-materials.md","Request Founder Materials")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/summarize-initial-call.md","Summarize Meeting Records")</f>
         <v/>
       </c>
       <c r="D11" s="16">
@@ -29818,23 +29822,19 @@
         </is>
       </c>
       <c r="C12" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/summarize-initial-call.md","Summarize Meeting Records")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-opportunity-status.md","Review Opportunity Status")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/customer-insights-summary-template.md","Customer Insights Summary Template (vc.document.customer_insights_summary_template)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/deal-room-sop.md","Deal Pipeline Operating SOP (vc.document.deal_room_sop)")</f>
         <v/>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>output_template</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="inlineStr">
-        <is>
-          <t>customer_insights_artifact_id</t>
-        </is>
-      </c>
+          <t>operating_guidance</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1" s="12">
       <c r="A13" s="15" t="inlineStr">
@@ -29848,16 +29848,16 @@
         </is>
       </c>
       <c r="C13" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/summarize-initial-call.md","Summarize Meeting Records")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-opportunity-status.md","Review Opportunity Status")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (vc.document.evidence_citation_style_guide)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/opportunity-evaluation-framework.md","Opportunity Evaluation Framework (vc.document.opportunity_evaluation_framework)")</f>
         <v/>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>methodology</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr"/>
@@ -29874,16 +29874,16 @@
         </is>
       </c>
       <c r="C14" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/summarize-initial-call.md","Summarize Meeting Records")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-opportunity-status.md","Review Opportunity Status")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (vc.document.template_use_guidance)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evaluation-workstream-guide.md","Evaluation Workstream Guide (vc.document.evaluation_workstream_guide)")</f>
         <v/>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>operating_guidance</t>
+          <t>methodology</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr"/>
@@ -29904,12 +29904,12 @@
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/deal-room-sop.md","Deal Pipeline Operating SOP (vc.document.deal_room_sop)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evidence-citation-style-guide.md","Evidence And Citation Style Guide (vc.document.evidence_citation_style_guide)")</f>
         <v/>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>operating_guidance</t>
+          <t>style_guide</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr"/>
@@ -29930,12 +29930,12 @@
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/opportunity-evaluation-framework.md","Opportunity Evaluation Framework (vc.document.opportunity_evaluation_framework)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/template-use-guidance.md","Template Use Guidance (vc.document.template_use_guidance)")</f>
         <v/>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>methodology</t>
+          <t>operating_guidance</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr"/>
@@ -29948,20 +29948,20 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Intake</t>
         </is>
       </c>
       <c r="C17" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-opportunity-status.md","Review Opportunity Status")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/shared/evaluation-workstream-guide.md","Evaluation Workstream Guide (vc.document.evaluation_workstream_guide)")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/alludium/documents/deal-room/deal-room-sop.md","Deal Pipeline Operating SOP (vc.document.deal_room_sop)")</f>
         <v/>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>methodology</t>
+          <t>operating_guidance</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr"/>
@@ -29974,11 +29974,11 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Intake</t>
         </is>
       </c>
       <c r="C18" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-opportunity-status.md","Review Opportunity Status")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
         <v/>
       </c>
       <c r="D18" s="16">
@@ -30000,11 +30000,11 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Intake</t>
         </is>
       </c>
       <c r="C19" s="16">
-        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/review-opportunity-status.md","Review Opportunity Status")</f>
+        <f>HYPERLINK('Link Config'!$B$2&amp;"plugins/vc/tasks/screen-inbound-opportunity.md","Capture Opportunity Intake")</f>
         <v/>
       </c>
       <c r="D19" s="16">
